--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44792</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>46289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>46121</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46009</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>46246</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>44623</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45457</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44006</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>46009</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>45803</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45728</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45715</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>46234</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44971</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45092</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45874</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46199</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45803</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5712,7 +5712,7 @@
         <v>45442</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44532</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>45316</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>44575</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>45196</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45202</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45442</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44726</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45803</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
         <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7074,7 +7074,7 @@
         <v>45736</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>46003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45996</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44500</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>46171</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45358</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45989</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         <v>45910</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>45803</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45972</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44497</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44740</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9135,7 +9135,7 @@
         <v>46181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         <v>45989</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>44574</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>45985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>46055</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9851,7 +9851,7 @@
         <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>45853</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10311,7 +10311,7 @@
         <v>46207</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>46234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         <v>44614</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>44974</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>44966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>46155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>45097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44720</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11451,7 +11451,7 @@
         <v>45107</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>46009</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>45909</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>46167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45961</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45994</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>44610</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44719</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12700,7 +12700,7 @@
         <v>44664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>46037</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13367,7 +13367,7 @@
         <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44855</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>46155</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>46268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>46003</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14055,7 +14055,7 @@
         <v>45985</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>44495</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45273</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14616,7 +14616,7 @@
         <v>45803</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>46093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14835,7 +14835,7 @@
         <v>45679</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>44897</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45831</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>44489</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45035</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44516</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>46191</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45293</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46234</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45090</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>45687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>44984</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>44963</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45464</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45429</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>44967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>45960</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45168</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>45223</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45189</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>46267</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>45665</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44849</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>44967</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45694</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17906,7 +17906,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18122,7 +18122,7 @@
         <v>45965</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>44714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44543</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18666,7 +18666,7 @@
         <v>44831</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44847</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18876,7 +18876,7 @@
         <v>44894</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>44909</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19095,7 +19095,7 @@
         <v>44487</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>45896</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>44673</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19528,7 +19528,7 @@
         <v>45916</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>46069</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45098</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45938</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>44645</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45950</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
         <v>46106</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44958</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>45645</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>44980</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45442</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>46009</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>45736</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>44467</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45757</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>46147</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>44917</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>46153</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45107</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45316</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>46160</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45756</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21909,7 +21909,7 @@
         <v>46178</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45583</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22233,7 +22233,7 @@
         <v>45107</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>45638</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45173</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>44594</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>46212</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>45173</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>46261</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>46274</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>46274</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>46275</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>46280</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>44917</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45314</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23741,7 +23741,7 @@
         <v>45121</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>44886</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>46141</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>46141</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>44574</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45385</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25071,7 +25071,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>44567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>44489</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44609</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>44569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>44486</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>44572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44662</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>44659</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26050,7 +26050,7 @@
         <v>44603</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26123,7 +26123,7 @@
         <v>44700</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>44494</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26274,7 +26274,7 @@
         <v>44839</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26347,7 +26347,7 @@
         <v>44784</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26420,7 +26420,7 @@
         <v>44612</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26493,7 +26493,7 @@
         <v>44886</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>44883</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>44598</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         <v>44610</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>44865</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>44533</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>44704</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>44764</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27175,7 +27175,7 @@
         <v>44490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27248,7 +27248,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27321,7 +27321,7 @@
         <v>44740</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27399,7 +27399,7 @@
         <v>44816</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27472,7 +27472,7 @@
         <v>44722</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>44705</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         <v>44692</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27769,7 +27769,7 @@
         <v>44750</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>44643</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>44504</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>44846</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>44676</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28139,7 +28139,7 @@
         <v>44491</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28217,7 +28217,7 @@
         <v>44476</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44847</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28363,7 +28363,7 @@
         <v>44705</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28436,7 +28436,7 @@
         <v>44799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>44575</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>44575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>44702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>44551</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>44571</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>44634</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>44698</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>44865</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>44593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>44479</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>44543</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>44495</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>44522</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29541,7 +29541,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29614,7 +29614,7 @@
         <v>44750</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>44685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>44733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>44711</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>44743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>44623</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>44729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>44791</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>44623</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>44798</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45371</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30613,7 +30613,7 @@
         <v>44859</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>44832</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>45208</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30832,7 +30832,7 @@
         <v>44883</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30910,7 +30910,7 @@
         <v>44866</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         <v>45222</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31056,7 +31056,7 @@
         <v>45050</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31129,7 +31129,7 @@
         <v>45259</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31207,7 +31207,7 @@
         <v>45758</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31280,7 +31280,7 @@
         <v>45096</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>44809</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>44810</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31499,7 +31499,7 @@
         <v>44551</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31577,7 +31577,7 @@
         <v>45327</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31650,7 +31650,7 @@
         <v>45231</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31723,7 +31723,7 @@
         <v>45259</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>45259</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31869,7 +31869,7 @@
         <v>45525</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>45335</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>46013</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44883</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>44849</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32239,7 +32239,7 @@
         <v>46014</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45195</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32385,7 +32385,7 @@
         <v>45968</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45636</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32536,7 +32536,7 @@
         <v>46030</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32614,7 +32614,7 @@
         <v>45341</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32692,7 +32692,7 @@
         <v>45490</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>46030</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32838,7 +32838,7 @@
         <v>45341</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45439</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32989,7 +32989,7 @@
         <v>44935</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33062,7 +33062,7 @@
         <v>45798</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>44504</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46029</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>44602</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44593</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46031</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45839</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33578,7 +33578,7 @@
         <v>44977</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33651,7 +33651,7 @@
         <v>44624</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45799</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45618</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33880,7 +33880,7 @@
         <v>44637</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45453</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45733</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45524</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34182,7 +34182,7 @@
         <v>44967</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34255,7 +34255,7 @@
         <v>44599</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34328,7 +34328,7 @@
         <v>45799</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>44593</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>44593</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>45344</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34640,7 +34640,7 @@
         <v>44946</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34713,7 +34713,7 @@
         <v>45425</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34786,7 +34786,7 @@
         <v>45194</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
         <v>45903</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45903</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>46051</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44608</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35166,7 +35166,7 @@
         <v>45905</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
         <v>45799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35317,7 +35317,7 @@
         <v>45202</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35395,7 +35395,7 @@
         <v>46051</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35468,7 +35468,7 @@
         <v>45086</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>46055</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45912</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35697,7 +35697,7 @@
         <v>46055</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45552</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45744</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>46057</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45915</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>44960</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>44960</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>46062</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>45341</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>45608</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>46062</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36515,7 +36515,7 @@
         <v>46062</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36593,7 +36593,7 @@
         <v>45916</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45918</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>46062</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>46064</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36890,7 +36890,7 @@
         <v>46065</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45922</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>44553</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>46065</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37182,7 +37182,7 @@
         <v>45923</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37260,7 +37260,7 @@
         <v>45231</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37333,7 +37333,7 @@
         <v>44575</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37406,7 +37406,7 @@
         <v>45097</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37479,7 +37479,7 @@
         <v>45923</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45926</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37635,7 +37635,7 @@
         <v>44893</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37708,7 +37708,7 @@
         <v>45926</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45926</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>45926</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45369</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38015,7 +38015,7 @@
         <v>44904</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>46076</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>45614</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38244,7 +38244,7 @@
         <v>45926</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45926</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44659</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45379</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38551,7 +38551,7 @@
         <v>44912</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38624,7 +38624,7 @@
         <v>44614</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>45443</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>46080</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>45929</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45929</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>44967</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>45932</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45931</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>45932</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>45931</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>46085</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45511</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>45932</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>45215</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         <v>46065</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39759,7 +39759,7 @@
         <v>45202</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39837,7 +39837,7 @@
         <v>46090</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39910,7 +39910,7 @@
         <v>46091</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>46091</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>46090</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40129,7 +40129,7 @@
         <v>45809</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46091</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46091</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40353,7 +40353,7 @@
         <v>46091</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40426,7 +40426,7 @@
         <v>46091</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40499,7 +40499,7 @@
         <v>45937</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40572,7 +40572,7 @@
         <v>45453</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>44512</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>46093</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45938</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40874,7 +40874,7 @@
         <v>46094</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>46094</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45390</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41093,7 +41093,7 @@
         <v>44617</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41166,7 +41166,7 @@
         <v>46094</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46094</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>45940</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46097</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41458,7 +41458,7 @@
         <v>44977</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46094</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41609,7 +41609,7 @@
         <v>45942</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41682,7 +41682,7 @@
         <v>46094</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41755,7 +41755,7 @@
         <v>45446</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41833,7 +41833,7 @@
         <v>45943</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>46098</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41984,7 +41984,7 @@
         <v>45898</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42057,7 +42057,7 @@
         <v>45426</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42130,7 +42130,7 @@
         <v>44993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42203,7 +42203,7 @@
         <v>45946</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45947</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
         <v>44733</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42427,7 +42427,7 @@
         <v>45946</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42500,7 +42500,7 @@
         <v>45946</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42573,7 +42573,7 @@
         <v>45950</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42646,7 +42646,7 @@
         <v>45949</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42719,7 +42719,7 @@
         <v>45950</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>44994</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42865,7 +42865,7 @@
         <v>45812</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>44665</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45068</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>46107</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43162,7 +43162,7 @@
         <v>46107</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43235,7 +43235,7 @@
         <v>46107</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>45954</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>46111</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>46111</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45954</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45954</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45363</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43776,7 +43776,7 @@
         <v>46111</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45958</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43927,7 +43927,7 @@
         <v>44967</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>46108</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>44929</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>45958</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45958</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>45958</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45958</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>45958</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45730</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>46114</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>45614</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>46119</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>46119</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45959</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45042</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>44608</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45961</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45291,7 +45291,7 @@
         <v>45961</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45364,7 +45364,7 @@
         <v>44909</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45442,7 +45442,7 @@
         <v>46122</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45515,7 +45515,7 @@
         <v>45107</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45965</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45666,7 +45666,7 @@
         <v>45089</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45739,7 +45739,7 @@
         <v>45971</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45812,7 +45812,7 @@
         <v>45721</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45885,7 +45885,7 @@
         <v>45971</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45972</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45975</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46109,7 +46109,7 @@
         <v>45975</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46187,7 +46187,7 @@
         <v>45975</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46265,7 +46265,7 @@
         <v>46132</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46343,7 +46343,7 @@
         <v>46132</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46416,7 +46416,7 @@
         <v>46133</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46489,7 +46489,7 @@
         <v>46132</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>46132</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46645,7 +46645,7 @@
         <v>45982</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46718,7 +46718,7 @@
         <v>45981</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46791,7 +46791,7 @@
         <v>45981</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46869,7 +46869,7 @@
         <v>45981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46947,7 +46947,7 @@
         <v>46132</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>45958</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>45981</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>45939</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45983</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>45113</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47395,7 +47395,7 @@
         <v>45113</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45882</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45757</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47614,7 +47614,7 @@
         <v>45988</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>45757</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47765,7 +47765,7 @@
         <v>46135</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45992</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47911,7 +47911,7 @@
         <v>45992</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>44644</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45890</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48140,7 +48140,7 @@
         <v>46051</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>45995</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48291,7 +48291,7 @@
         <v>45863</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48364,7 +48364,7 @@
         <v>45995</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48437,7 +48437,7 @@
         <v>45876</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48510,7 +48510,7 @@
         <v>45699</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>45940</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48656,7 +48656,7 @@
         <v>45695</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>44508</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48812,7 +48812,7 @@
         <v>44519</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45769</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48958,7 +48958,7 @@
         <v>45987</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49031,7 +49031,7 @@
         <v>45817</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45098</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49177,7 +49177,7 @@
         <v>45694</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49250,7 +49250,7 @@
         <v>44820</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49328,7 +49328,7 @@
         <v>45065</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45981</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49474,7 +49474,7 @@
         <v>45817</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49552,7 +49552,7 @@
         <v>45852</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49630,7 +49630,7 @@
         <v>44532</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45838</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45456</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49849,7 +49849,7 @@
         <v>45054</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45966</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50000,7 +50000,7 @@
         <v>45047</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50073,7 +50073,7 @@
         <v>44888</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50151,7 +50151,7 @@
         <v>45901</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50229,7 +50229,7 @@
         <v>45821</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50302,7 +50302,7 @@
         <v>45821</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50375,7 +50375,7 @@
         <v>46140</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50453,7 +50453,7 @@
         <v>45127</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50526,7 +50526,7 @@
         <v>45048</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50599,7 +50599,7 @@
         <v>45880</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45293</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50745,7 +50745,7 @@
         <v>44848</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50818,7 +50818,7 @@
         <v>45259</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>45942</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50964,7 +50964,7 @@
         <v>45867</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51037,7 +51037,7 @@
         <v>45691</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>46141</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51188,7 +51188,7 @@
         <v>44993</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51261,7 +51261,7 @@
         <v>44531</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51334,7 +51334,7 @@
         <v>45831</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51407,7 +51407,7 @@
         <v>44532</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51480,7 +51480,7 @@
         <v>45831</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51558,7 +51558,7 @@
         <v>46146</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51631,7 +51631,7 @@
         <v>45832</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51709,7 +51709,7 @@
         <v>45831</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51782,7 +51782,7 @@
         <v>45757</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51855,7 +51855,7 @@
         <v>45078</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45832</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52011,7 +52011,7 @@
         <v>45831</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52089,7 +52089,7 @@
         <v>45202</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52162,7 +52162,7 @@
         <v>44900</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52235,7 +52235,7 @@
         <v>45580</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52308,7 +52308,7 @@
         <v>44944</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52381,7 +52381,7 @@
         <v>45295</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52459,7 +52459,7 @@
         <v>46155</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52537,7 +52537,7 @@
         <v>46155</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>46155</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52693,7 +52693,7 @@
         <v>46160</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52771,7 +52771,7 @@
         <v>45554</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52844,7 +52844,7 @@
         <v>45930</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52917,7 +52917,7 @@
         <v>46160</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52990,7 +52990,7 @@
         <v>46160</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53063,7 +53063,7 @@
         <v>44816</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53136,7 +53136,7 @@
         <v>46161</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53209,7 +53209,7 @@
         <v>45763</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53282,7 +53282,7 @@
         <v>45317</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53355,7 +53355,7 @@
         <v>46137</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53433,7 +53433,7 @@
         <v>45307</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53506,7 +53506,7 @@
         <v>45104</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45821</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45840</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53725,7 +53725,7 @@
         <v>45119</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53798,7 +53798,7 @@
         <v>46112</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53871,7 +53871,7 @@
         <v>46112</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53944,7 +53944,7 @@
         <v>46162</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54022,7 +54022,7 @@
         <v>45679</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54095,7 +54095,7 @@
         <v>46162</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54173,7 +54173,7 @@
         <v>45763</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54246,7 +54246,7 @@
         <v>44501</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54324,7 +54324,7 @@
         <v>45756</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54397,7 +54397,7 @@
         <v>46163</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>46167</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54548,7 +54548,7 @@
         <v>46167</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54621,7 +54621,7 @@
         <v>46167</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54694,7 +54694,7 @@
         <v>44548</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54767,7 +54767,7 @@
         <v>45644</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54840,7 +54840,7 @@
         <v>44550</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54918,7 +54918,7 @@
         <v>46167</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54991,7 +54991,7 @@
         <v>45426</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45852</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55142,7 +55142,7 @@
         <v>45852</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55215,7 +55215,7 @@
         <v>45852</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>44980</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55366,7 +55366,7 @@
         <v>45856</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55444,7 +55444,7 @@
         <v>45644</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55517,7 +55517,7 @@
         <v>45254</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55590,7 +55590,7 @@
         <v>45611</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55663,7 +55663,7 @@
         <v>45761</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55736,7 +55736,7 @@
         <v>45344</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55814,7 +55814,7 @@
         <v>46172</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55892,7 +55892,7 @@
         <v>46172</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45107</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56043,7 +56043,7 @@
         <v>45107</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56116,7 +56116,7 @@
         <v>45107</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56189,7 +56189,7 @@
         <v>45344</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56267,7 +56267,7 @@
         <v>44816</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56345,7 +56345,7 @@
         <v>45133</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56418,7 +56418,7 @@
         <v>45096</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56491,7 +56491,7 @@
         <v>45098</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56564,7 +56564,7 @@
         <v>46171</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56637,7 +56637,7 @@
         <v>46171</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56715,7 +56715,7 @@
         <v>46171</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56788,7 +56788,7 @@
         <v>44544</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56861,7 +56861,7 @@
         <v>44519</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56934,7 +56934,7 @@
         <v>45163</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45349</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>45096</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45743</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>44603</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57299,7 +57299,7 @@
         <v>45831</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57372,7 +57372,7 @@
         <v>45161</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>46176</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57518,7 +57518,7 @@
         <v>45524</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57596,7 +57596,7 @@
         <v>44629</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57674,7 +57674,7 @@
         <v>45468</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>45037</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>45134</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>46181</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>46178</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>44533</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         <v>44535</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>44637</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>46185</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58346,7 +58346,7 @@
         <v>45162</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45145</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58497,7 +58497,7 @@
         <v>46184</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45201</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>45358</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58721,7 +58721,7 @@
         <v>44522</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58794,7 +58794,7 @@
         <v>46188</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58867,7 +58867,7 @@
         <v>44616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59018,7 +59018,7 @@
         <v>46188</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>46188</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>46191</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59242,7 +59242,7 @@
         <v>45177</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>45874</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>46191</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>46191</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>46191</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>46191</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59695,7 +59695,7 @@
         <v>45763</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59768,7 +59768,7 @@
         <v>46195</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>45159</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>44678</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
         <v>44610</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45615</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45638</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45644</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45188</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>44832</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46199</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>46199</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60596,7 +60596,7 @@
         <v>45881</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60669,7 +60669,7 @@
         <v>45338</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60742,7 +60742,7 @@
         <v>45721</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>45581</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>46198</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>45148</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>45148</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45148</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46198</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>44588</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>46202</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>45882</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>45323</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61555,7 +61555,7 @@
         <v>45194</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>45601</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46202</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61784,7 +61784,7 @@
         <v>44594</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61857,7 +61857,7 @@
         <v>45371</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>45677</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>44629</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62081,7 +62081,7 @@
         <v>45351</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62159,7 +62159,7 @@
         <v>46251</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45054</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46206</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62388,7 +62388,7 @@
         <v>46251</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62466,7 +62466,7 @@
         <v>45194</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>44819</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>46206</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62695,7 +62695,7 @@
         <v>46251</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>46206</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45055</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62919,7 +62919,7 @@
         <v>46251</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62997,7 +62997,7 @@
         <v>45182</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63070,7 +63070,7 @@
         <v>45182</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63143,7 +63143,7 @@
         <v>46206</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>45093</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45958</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45407</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63450,7 +63450,7 @@
         <v>45188</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63523,7 +63523,7 @@
         <v>45231</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63596,7 +63596,7 @@
         <v>45677</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63669,7 +63669,7 @@
         <v>45695</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>46254</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63820,7 +63820,7 @@
         <v>45216</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63893,7 +63893,7 @@
         <v>45216</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63971,7 +63971,7 @@
         <v>45694</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64044,7 +64044,7 @@
         <v>44588</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64117,7 +64117,7 @@
         <v>46258</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64190,7 +64190,7 @@
         <v>45208</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64263,7 +64263,7 @@
         <v>45705</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64336,7 +64336,7 @@
         <v>45180</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64414,7 +64414,7 @@
         <v>44614</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64487,7 +64487,7 @@
         <v>44679</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64565,7 +64565,7 @@
         <v>45149</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64643,7 +64643,7 @@
         <v>46217</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>45181</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64789,7 +64789,7 @@
         <v>45254</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64862,7 +64862,7 @@
         <v>44679</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>46260</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
         <v>45182</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>46218</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>46261</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65247,7 +65247,7 @@
         <v>45694</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65320,7 +65320,7 @@
         <v>44699</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65398,7 +65398,7 @@
         <v>45225</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65471,7 +65471,7 @@
         <v>45259</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65549,7 +65549,7 @@
         <v>45236</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65622,7 +65622,7 @@
         <v>45299</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65695,7 +65695,7 @@
         <v>46205</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65768,7 +65768,7 @@
         <v>45267</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65846,7 +65846,7 @@
         <v>45236</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65919,7 +65919,7 @@
         <v>46259</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65992,7 +65992,7 @@
         <v>46266</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66070,7 +66070,7 @@
         <v>46267</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66148,7 +66148,7 @@
         <v>46267</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66221,7 +66221,7 @@
         <v>44799</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66294,7 +66294,7 @@
         <v>46224</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66372,7 +66372,7 @@
         <v>45321</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66445,7 +66445,7 @@
         <v>46267</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66518,7 +66518,7 @@
         <v>45317</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66591,7 +66591,7 @@
         <v>46267</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66664,7 +66664,7 @@
         <v>45361</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66742,7 +66742,7 @@
         <v>46272</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66815,7 +66815,7 @@
         <v>45164</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66893,7 +66893,7 @@
         <v>45351</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66966,7 +66966,7 @@
         <v>44930</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67039,7 +67039,7 @@
         <v>45310</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67112,7 +67112,7 @@
         <v>46273</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67190,7 +67190,7 @@
         <v>45254</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67263,7 +67263,7 @@
         <v>45091</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67336,7 +67336,7 @@
         <v>46274</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67414,7 +67414,7 @@
         <v>46273</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67492,7 +67492,7 @@
         <v>46274</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67570,7 +67570,7 @@
         <v>46202</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67643,7 +67643,7 @@
         <v>46265</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67721,7 +67721,7 @@
         <v>46276</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67799,7 +67799,7 @@
         <v>46276</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67877,7 +67877,7 @@
         <v>46275</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67955,7 +67955,7 @@
         <v>44788</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68028,7 +68028,7 @@
         <v>46237</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68106,7 +68106,7 @@
         <v>46237</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68184,7 +68184,7 @@
         <v>44817</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68257,7 +68257,7 @@
         <v>45216</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68330,7 +68330,7 @@
         <v>46281</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68408,7 +68408,7 @@
         <v>46234</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68481,7 +68481,7 @@
         <v>46234</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>45599</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68627,7 +68627,7 @@
         <v>46240</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68700,7 +68700,7 @@
         <v>44984</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68778,7 +68778,7 @@
         <v>46272</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68851,7 +68851,7 @@
         <v>46283</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68924,7 +68924,7 @@
         <v>45391</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68997,7 +68997,7 @@
         <v>45520</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69070,7 +69070,7 @@
         <v>44581</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69148,7 +69148,7 @@
         <v>44568</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69226,7 +69226,7 @@
         <v>44908</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69299,7 +69299,7 @@
         <v>44949</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69372,7 +69372,7 @@
         <v>44946</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69445,7 +69445,7 @@
         <v>45033</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69518,7 +69518,7 @@
         <v>44531</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69591,7 +69591,7 @@
         <v>44960</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69664,7 +69664,7 @@
         <v>44593</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69742,7 +69742,7 @@
         <v>44928</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69820,7 +69820,7 @@
         <v>44819</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69898,7 +69898,7 @@
         <v>44616</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69971,7 +69971,7 @@
         <v>46290</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70044,7 +70044,7 @@
         <v>44560</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70117,7 +70117,7 @@
         <v>44600</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70195,7 +70195,7 @@
         <v>44623</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70273,7 +70273,7 @@
         <v>44623</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70351,7 +70351,7 @@
         <v>45167</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70424,7 +70424,7 @@
         <v>44965</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70497,7 +70497,7 @@
         <v>44965</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70570,7 +70570,7 @@
         <v>45308</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70643,7 +70643,7 @@
         <v>45212</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70716,7 +70716,7 @@
         <v>44886</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70789,7 +70789,7 @@
         <v>45181</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70867,7 +70867,7 @@
         <v>44742</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70945,7 +70945,7 @@
         <v>45341</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71023,7 +71023,7 @@
         <v>45300</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71096,7 +71096,7 @@
         <v>45097</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71169,7 +71169,7 @@
         <v>44969</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71242,7 +71242,7 @@
         <v>44944</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71315,7 +71315,7 @@
         <v>45601</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71388,7 +71388,7 @@
         <v>45154</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71461,7 +71461,7 @@
         <v>44652</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71534,7 +71534,7 @@
         <v>45678</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71607,7 +71607,7 @@
         <v>44679</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71680,7 +71680,7 @@
         <v>45694</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71753,7 +71753,7 @@
         <v>44806</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71826,7 +71826,7 @@
         <v>45049</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71899,7 +71899,7 @@
         <v>44645</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71977,7 +71977,7 @@
         <v>44497</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72050,7 +72050,7 @@
         <v>45152</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72123,7 +72123,7 @@
         <v>44964</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
         <v>44599</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72269,7 +72269,7 @@
         <v>45000</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72342,7 +72342,7 @@
         <v>45762</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72415,7 +72415,7 @@
         <v>45352</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72488,7 +72488,7 @@
         <v>44944</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72561,7 +72561,7 @@
         <v>45266</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72634,7 +72634,7 @@
         <v>44872</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72707,7 +72707,7 @@
         <v>45513</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72785,7 +72785,7 @@
         <v>45049</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72858,7 +72858,7 @@
         <v>45336</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72931,7 +72931,7 @@
         <v>45169</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73009,7 +73009,7 @@
         <v>45244</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73087,7 +73087,7 @@
         <v>45435</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73165,7 +73165,7 @@
         <v>45763</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73238,7 +73238,7 @@
         <v>45548</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73311,7 +73311,7 @@
         <v>44532</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73384,7 +73384,7 @@
         <v>45190</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73457,7 +73457,7 @@
         <v>44977</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73530,7 +73530,7 @@
         <v>45336</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73603,7 +73603,7 @@
         <v>45110</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73676,7 +73676,7 @@
         <v>45194</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73754,7 +73754,7 @@
         <v>45474</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73827,7 +73827,7 @@
         <v>45300</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73900,7 +73900,7 @@
         <v>45589</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73973,7 +73973,7 @@
         <v>44609</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74051,7 +74051,7 @@
         <v>44503</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74124,7 +74124,7 @@
         <v>44624</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74202,7 +74202,7 @@
         <v>45729</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74275,7 +74275,7 @@
         <v>45729</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74348,7 +74348,7 @@
         <v>45327</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74421,7 +74421,7 @@
         <v>45014</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74494,7 +74494,7 @@
         <v>44593</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74567,7 +74567,7 @@
         <v>45685</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74640,7 +74640,7 @@
         <v>45460</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74718,7 +74718,7 @@
         <v>45345</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74791,7 +74791,7 @@
         <v>44914</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74864,7 +74864,7 @@
         <v>45061</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74937,7 +74937,7 @@
         <v>44912</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75010,7 +75010,7 @@
         <v>44967</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75083,7 +75083,7 @@
         <v>45075</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75156,7 +75156,7 @@
         <v>45699</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75229,7 +75229,7 @@
         <v>45733</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75302,7 +75302,7 @@
         <v>45426</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75375,7 +75375,7 @@
         <v>45478</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>45154</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>45729</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75599,7 +75599,7 @@
         <v>45175</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75672,7 +75672,7 @@
         <v>45644</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75745,7 +75745,7 @@
         <v>45006</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75818,7 +75818,7 @@
         <v>45307</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75891,7 +75891,7 @@
         <v>45327</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75964,7 +75964,7 @@
         <v>45300</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76037,7 +76037,7 @@
         <v>45107</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76110,7 +76110,7 @@
         <v>45520</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76183,7 +76183,7 @@
         <v>45574</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76256,7 +76256,7 @@
         <v>45779</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76334,7 +76334,7 @@
         <v>44569</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76412,7 +76412,7 @@
         <v>45329</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76485,7 +76485,7 @@
         <v>45177</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76563,7 +76563,7 @@
         <v>45558</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76636,7 +76636,7 @@
         <v>45562</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76709,7 +76709,7 @@
         <v>45368</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76787,7 +76787,7 @@
         <v>44569</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76865,7 +76865,7 @@
         <v>45684</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76938,7 +76938,7 @@
         <v>45254</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77011,7 +77011,7 @@
         <v>45371</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77084,7 +77084,7 @@
         <v>45091</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77162,7 +77162,7 @@
         <v>45583</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77240,7 +77240,7 @@
         <v>45584</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77313,7 +77313,7 @@
         <v>44602</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77391,7 +77391,7 @@
         <v>44606</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77469,7 +77469,7 @@
         <v>44645</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77547,7 +77547,7 @@
         <v>44609</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77625,7 +77625,7 @@
         <v>44623</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77703,7 +77703,7 @@
         <v>45315</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77781,7 +77781,7 @@
         <v>45173</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77854,7 +77854,7 @@
         <v>44985</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77927,7 +77927,7 @@
         <v>45398</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78005,7 +78005,7 @@
         <v>46086</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78078,7 +78078,7 @@
         <v>46093</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -78151,7 +78151,7 @@
         <v>46089</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -78229,7 +78229,7 @@
         <v>46089</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -78307,7 +78307,7 @@
         <v>46129</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>45827</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>44792</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>46289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>46121</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>46009</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>46246</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3411,7 +3411,7 @@
         <v>45457</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>44006</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>45223</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45706</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45715</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4050,7 +4050,7 @@
         <v>46009</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         <v>45803</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
         <v>46155</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45728</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4577,7 +4577,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>46099</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44971</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>46234</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>45874</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>45092</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>45086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46199</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45316</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>45442</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
         <v>45803</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>44532</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>46009</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44575</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44726</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45736</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>45715</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45803</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>46003</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45996</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44500</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7800,7 +7800,7 @@
         <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>45936</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>45853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>46171</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45358</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>45989</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>45910</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>45803</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8893,7 +8893,7 @@
         <v>44740</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>46198</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>45989</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45972</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9484,7 +9484,7 @@
         <v>44497</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>45985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>44574</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>46055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>45985</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>46207</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>46234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45688</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44614</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10879,7 +10879,7 @@
         <v>45097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>44974</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>44966</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>46155</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>44720</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45107</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11563,7 +11563,7 @@
         <v>46009</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>45909</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45721</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>45961</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12243,7 +12243,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12360,7 +12360,7 @@
         <v>45994</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44610</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44719</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44664</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45905</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>44855</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13474,7 +13474,7 @@
         <v>46037</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13591,7 +13591,7 @@
         <v>46001</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>46155</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13937,7 +13937,7 @@
         <v>46268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>46003</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14166,7 +14166,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>45687</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45803</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45679</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14843,7 +14843,7 @@
         <v>46093</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>44516</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44489</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44897</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15279,7 +15279,7 @@
         <v>45831</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45035</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         <v>46191</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>44804</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15724,7 +15724,7 @@
         <v>46234</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45293</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15942,7 +15942,7 @@
         <v>45273</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>45090</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16169,7 +16169,7 @@
         <v>44984</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16276,7 +16276,7 @@
         <v>45223</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45665</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45429</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>45694</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>45947</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45960</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>45464</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>44849</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>45904</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46267</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>44630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>45965</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>44714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>44543</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44517</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>44487</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45107</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>46009</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44594</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45335</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>45916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>46069</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45938</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45098</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19758,7 +19758,7 @@
         <v>45950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>44917</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>44958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>44886</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>45173</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>46106</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20393,7 +20393,7 @@
         <v>45121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45736</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>45638</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44909</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21042,7 +21042,7 @@
         <v>46147</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>46153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>45385</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>46160</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44645</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46178</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
         <v>46212</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44847</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44909</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46261</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45314</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22330,7 +22330,7 @@
         <v>46274</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>46275</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>46274</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>46280</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>44831</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44574</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>44673</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45756</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>45442</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>46141</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>46141</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45181</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>45107</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>44894</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>44980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45173</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45583</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45757</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44917</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44517</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>44567</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25225,7 +25225,7 @@
         <v>44602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44489</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25522,7 +25522,7 @@
         <v>44609</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25751,7 +25751,7 @@
         <v>44662</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>44486</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>44659</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>44572</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>44603</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44494</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>44700</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26277,7 +26277,7 @@
         <v>44839</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44784</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>44612</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>44886</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>44883</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44598</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>44865</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44610</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>44704</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>44533</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>44764</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>44490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>44512</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>44740</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>44816</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>44722</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>44705</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27699,7 +27699,7 @@
         <v>44692</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44504</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27850,7 +27850,7 @@
         <v>44750</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27923,7 +27923,7 @@
         <v>44846</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>44643</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28069,7 +28069,7 @@
         <v>44676</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>44491</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>44847</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>44476</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>44705</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44799</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>44575</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         <v>44575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>44702</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>44551</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28809,7 +28809,7 @@
         <v>44571</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28882,7 +28882,7 @@
         <v>44634</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>44698</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>44599</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         <v>44865</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         <v>44593</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>44479</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29325,7 +29325,7 @@
         <v>44495</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>44543</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29471,7 +29471,7 @@
         <v>44522</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29544,7 +29544,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29617,7 +29617,7 @@
         <v>44750</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44711</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>44623</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30080,7 +30080,7 @@
         <v>44729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>44791</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>44623</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44798</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>44659</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30460,7 +30460,7 @@
         <v>44593</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>44593</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>44659</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45678</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44893</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30840,7 +30840,7 @@
         <v>45695</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44637</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -30991,7 +30991,7 @@
         <v>45615</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>44637</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45091</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44581</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44967</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31366,7 +31366,7 @@
         <v>44599</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31439,7 +31439,7 @@
         <v>44993</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>44608</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>44519</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>44816</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45694</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31809,7 +31809,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>45756</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>44900</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45584</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32106,7 +32106,7 @@
         <v>44872</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32179,7 +32179,7 @@
         <v>45091</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>45371</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45212</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45684</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>44532</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>45093</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>45562</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45177</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>44969</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45033</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33075,7 +33075,7 @@
         <v>45216</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>45329</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33221,7 +33221,7 @@
         <v>45327</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33294,7 +33294,7 @@
         <v>44569</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33372,7 +33372,7 @@
         <v>45583</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>44980</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>45552</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>45981</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45425</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45244</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>44593</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>44960</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45839</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34044,7 +34044,7 @@
         <v>45295</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45369</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45733</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>46013</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34341,7 +34341,7 @@
         <v>45363</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46014</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>44809</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>45968</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34643,7 +34643,7 @@
         <v>45300</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34716,7 +34716,7 @@
         <v>44617</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>46029</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>46030</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>46031</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>45107</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45107</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>46030</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44949</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35305,7 +35305,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>45903</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45905</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45149</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35612,7 +35612,7 @@
         <v>44548</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35685,7 +35685,7 @@
         <v>45490</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>45195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35831,7 +35831,7 @@
         <v>45439</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35909,7 +35909,7 @@
         <v>45636</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>45078</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45525</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45912</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45915</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>45916</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>45733</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45799</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45799</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36591,7 +36591,7 @@
         <v>45799</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36669,7 +36669,7 @@
         <v>45182</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36742,7 +36742,7 @@
         <v>46051</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36815,7 +36815,7 @@
         <v>46051</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36888,7 +36888,7 @@
         <v>45086</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36966,7 +36966,7 @@
         <v>45918</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45608</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45341</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45744</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>44616</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37331,7 +37331,7 @@
         <v>45922</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37404,7 +37404,7 @@
         <v>46055</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37482,7 +37482,7 @@
         <v>45644</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37555,7 +37555,7 @@
         <v>46055</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37628,7 +37628,7 @@
         <v>45923</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45055</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45923</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37857,7 +37857,7 @@
         <v>44912</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45809</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>46057</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38081,7 +38081,7 @@
         <v>45926</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45614</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45926</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45407</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38383,7 +38383,7 @@
         <v>45926</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38461,7 +38461,7 @@
         <v>45307</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38534,7 +38534,7 @@
         <v>45929</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38612,7 +38612,7 @@
         <v>45929</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>45215</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44512</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38836,7 +38836,7 @@
         <v>45097</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38909,7 +38909,7 @@
         <v>45926</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38987,7 +38987,7 @@
         <v>45926</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45926</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>45931</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>46062</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39299,7 +39299,7 @@
         <v>45931</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>46062</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39455,7 +39455,7 @@
         <v>46062</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>45182</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39606,7 +39606,7 @@
         <v>45932</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39679,7 +39679,7 @@
         <v>45932</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>46062</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39830,7 +39830,7 @@
         <v>45932</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39908,7 +39908,7 @@
         <v>46065</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>44904</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40059,7 +40059,7 @@
         <v>46065</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40132,7 +40132,7 @@
         <v>46064</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40205,7 +40205,7 @@
         <v>45938</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40283,7 +40283,7 @@
         <v>44819</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40361,7 +40361,7 @@
         <v>45937</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40434,7 +40434,7 @@
         <v>44600</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>45694</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40585,7 +40585,7 @@
         <v>44806</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40658,7 +40658,7 @@
         <v>45338</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40731,7 +40731,7 @@
         <v>45453</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45940</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40882,7 +40882,7 @@
         <v>45943</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40960,7 +40960,7 @@
         <v>45236</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45511</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41106,7 +41106,7 @@
         <v>45942</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>46076</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>44883</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>45898</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>44799</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>45946</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45946</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>45946</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45202</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45947</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>46080</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41924,7 +41924,7 @@
         <v>44602</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41997,7 +41997,7 @@
         <v>45164</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42075,7 +42075,7 @@
         <v>45950</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42148,7 +42148,7 @@
         <v>45950</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42221,7 +42221,7 @@
         <v>45812</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42294,7 +42294,7 @@
         <v>45949</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>46065</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>45208</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>45065</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42586,7 +42586,7 @@
         <v>45954</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42659,7 +42659,7 @@
         <v>45699</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>44967</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42805,7 +42805,7 @@
         <v>45954</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42878,7 +42878,7 @@
         <v>45954</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>46085</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43024,7 +43024,7 @@
         <v>46090</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43097,7 +43097,7 @@
         <v>45958</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>45958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43253,7 +43253,7 @@
         <v>45958</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43331,7 +43331,7 @@
         <v>45958</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43409,7 +43409,7 @@
         <v>45959</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43487,7 +43487,7 @@
         <v>45958</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43565,7 +43565,7 @@
         <v>45958</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>46090</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45958</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43794,7 +43794,7 @@
         <v>44503</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43867,7 +43867,7 @@
         <v>45961</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43940,7 +43940,7 @@
         <v>45721</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44013,7 +44013,7 @@
         <v>45000</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44086,7 +44086,7 @@
         <v>46091</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44159,7 +44159,7 @@
         <v>46091</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44232,7 +44232,7 @@
         <v>45961</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45965</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44383,7 +44383,7 @@
         <v>46091</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44456,7 +44456,7 @@
         <v>45188</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>45177</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>46091</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>46091</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>46091</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>46094</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>46094</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45817</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45045,7 +45045,7 @@
         <v>46094</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45118,7 +45118,7 @@
         <v>46094</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45191,7 +45191,7 @@
         <v>46093</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>46094</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>46094</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>44699</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45188</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>45721</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>45971</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45712,7 +45712,7 @@
         <v>46097</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45785,7 +45785,7 @@
         <v>45300</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45858,7 +45858,7 @@
         <v>45971</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45931,7 +45931,7 @@
         <v>46098</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45208</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45972</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45194</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46228,7 +46228,7 @@
         <v>45231</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46301,7 +46301,7 @@
         <v>45975</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45975</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>44886</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45520</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45201</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45817</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>44810</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>46107</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46993,7 +46993,7 @@
         <v>46107</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47066,7 +47066,7 @@
         <v>46107</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45981</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45981</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>45981</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47368,7 +47368,7 @@
         <v>46108</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47441,7 +47441,7 @@
         <v>45958</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45729</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>46111</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>46111</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>46111</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45982</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45983</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45821</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45391</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>44832</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>46114</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48254,7 +48254,7 @@
         <v>45317</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45988</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45763</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48478,7 +48478,7 @@
         <v>46119</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>46119</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48624,7 +48624,7 @@
         <v>45821</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48697,7 +48697,7 @@
         <v>46122</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>44935</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48843,7 +48843,7 @@
         <v>45992</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45216</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49062,7 +49062,7 @@
         <v>45995</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45995</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49208,7 +49208,7 @@
         <v>44678</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49286,7 +49286,7 @@
         <v>45987</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49359,7 +49359,7 @@
         <v>44501</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49437,7 +49437,7 @@
         <v>44588</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49510,7 +49510,7 @@
         <v>45259</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49583,7 +49583,7 @@
         <v>45831</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45231</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45705</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45259</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>46133</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>45831</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>46132</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>45831</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>46132</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50265,7 +50265,7 @@
         <v>45831</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50338,7 +50338,7 @@
         <v>46132</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>46132</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50489,7 +50489,7 @@
         <v>46132</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45832</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50645,7 +50645,7 @@
         <v>45390</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50718,7 +50718,7 @@
         <v>45832</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50796,7 +50796,7 @@
         <v>45054</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>44575</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>44994</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>44679</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>46135</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>44733</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51239,7 +51239,7 @@
         <v>45049</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>45202</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51390,7 +51390,7 @@
         <v>45259</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51468,7 +51468,7 @@
         <v>45901</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51546,7 +51546,7 @@
         <v>45456</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51619,7 +51619,7 @@
         <v>45821</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51692,7 +51692,7 @@
         <v>45942</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51765,7 +51765,7 @@
         <v>45876</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45880</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>45757</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51984,7 +51984,7 @@
         <v>45840</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52057,7 +52057,7 @@
         <v>45267</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52135,7 +52135,7 @@
         <v>45758</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52208,7 +52208,7 @@
         <v>45679</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45939</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52354,7 +52354,7 @@
         <v>45763</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52427,7 +52427,7 @@
         <v>45966</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>45699</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>45940</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>45763</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>45695</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>45113</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>45644</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>45426</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53021,7 +53021,7 @@
         <v>45852</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>44964</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53172,7 +53172,7 @@
         <v>45852</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>45852</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53323,7 +53323,7 @@
         <v>45113</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>44788</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53469,7 +53469,7 @@
         <v>45098</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>46051</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53620,7 +53620,7 @@
         <v>45361</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53698,7 +53698,7 @@
         <v>45769</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53771,7 +53771,7 @@
         <v>45259</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>45460</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45763</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45890</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>45882</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>44816</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>45308</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45107</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45852</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45856</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>44535</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>44629</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>45863</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>44608</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54823,7 +54823,7 @@
         <v>44497</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>44946</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -54969,7 +54969,7 @@
         <v>44965</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55042,7 +55042,7 @@
         <v>44965</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55115,7 +55115,7 @@
         <v>44679</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55188,7 +55188,7 @@
         <v>45336</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55261,7 +55261,7 @@
         <v>45336</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55334,7 +55334,7 @@
         <v>45349</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>44614</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>45259</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>46140</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>45691</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55709,7 +55709,7 @@
         <v>45589</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55782,7 +55782,7 @@
         <v>45293</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45838</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>45194</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56001,7 +56001,7 @@
         <v>46141</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>45194</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45599</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>45867</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>44665</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>45345</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>45154</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56527,7 +56527,7 @@
         <v>46146</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56600,7 +56600,7 @@
         <v>45443</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>44599</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>45310</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45831</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>45327</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45321</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>46155</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57121,7 +57121,7 @@
         <v>46155</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57199,7 +57199,7 @@
         <v>46155</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>45554</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57350,7 +57350,7 @@
         <v>45677</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45730</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>45930</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>46160</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57652,7 +57652,7 @@
         <v>46160</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57725,7 +57725,7 @@
         <v>44593</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57798,7 +57798,7 @@
         <v>45175</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57871,7 +57871,7 @@
         <v>44909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57949,7 +57949,7 @@
         <v>45729</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58022,7 +58022,7 @@
         <v>45729</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58095,7 +58095,7 @@
         <v>45181</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58168,7 +58168,7 @@
         <v>46160</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58241,7 +58241,7 @@
         <v>46161</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>45874</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45190</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58460,7 +58460,7 @@
         <v>46112</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>44550</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45048</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>46163</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>46137</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58835,7 +58835,7 @@
         <v>46162</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58913,7 +58913,7 @@
         <v>46162</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -58991,7 +58991,7 @@
         <v>45107</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59064,7 +59064,7 @@
         <v>46112</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59137,7 +59137,7 @@
         <v>44928</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59215,7 +59215,7 @@
         <v>46167</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59288,7 +59288,7 @@
         <v>46167</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59366,7 +59366,7 @@
         <v>45061</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59439,7 +59439,7 @@
         <v>46167</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59512,7 +59512,7 @@
         <v>46167</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59585,7 +59585,7 @@
         <v>44977</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59658,7 +59658,7 @@
         <v>45167</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59731,7 +59731,7 @@
         <v>45468</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59804,7 +59804,7 @@
         <v>44679</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59882,7 +59882,7 @@
         <v>45119</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59955,7 +59955,7 @@
         <v>45761</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60028,7 +60028,7 @@
         <v>44531</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60101,7 +60101,7 @@
         <v>45644</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60174,7 +60174,7 @@
         <v>45344</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60252,7 +60252,7 @@
         <v>45694</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60325,7 +60325,7 @@
         <v>46171</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60398,7 +60398,7 @@
         <v>45881</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60471,7 +60471,7 @@
         <v>46172</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>46172</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60627,7 +60627,7 @@
         <v>44508</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60705,7 +60705,7 @@
         <v>44644</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60783,7 +60783,7 @@
         <v>46171</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60861,7 +60861,7 @@
         <v>46171</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60934,7 +60934,7 @@
         <v>45426</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61007,7 +61007,7 @@
         <v>45882</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61080,7 +61080,7 @@
         <v>46176</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45187</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61231,7 +61231,7 @@
         <v>45743</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>46178</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61377,7 +61377,7 @@
         <v>45222</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61450,7 +61450,7 @@
         <v>44531</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61523,7 +61523,7 @@
         <v>44532</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61596,7 +61596,7 @@
         <v>44944</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61669,7 +61669,7 @@
         <v>45161</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61742,7 +61742,7 @@
         <v>46181</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61820,7 +61820,7 @@
         <v>45618</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61893,7 +61893,7 @@
         <v>45548</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61966,7 +61966,7 @@
         <v>46184</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62044,7 +62044,7 @@
         <v>44742</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62122,7 +62122,7 @@
         <v>44519</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62195,7 +62195,7 @@
         <v>44967</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62268,7 +62268,7 @@
         <v>46188</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62341,7 +62341,7 @@
         <v>46188</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62414,7 +62414,7 @@
         <v>46188</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62487,7 +62487,7 @@
         <v>46185</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62560,7 +62560,7 @@
         <v>46188</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62633,7 +62633,7 @@
         <v>44568</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62711,7 +62711,7 @@
         <v>45054</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62784,7 +62784,7 @@
         <v>44859</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62857,7 +62857,7 @@
         <v>44832</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62930,7 +62930,7 @@
         <v>45601</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63003,7 +63003,7 @@
         <v>46191</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63081,7 +63081,7 @@
         <v>45133</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63154,7 +63154,7 @@
         <v>46191</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63232,7 +63232,7 @@
         <v>46191</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63310,7 +63310,7 @@
         <v>46191</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63388,7 +63388,7 @@
         <v>46191</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63461,7 +63461,7 @@
         <v>44645</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63539,7 +63539,7 @@
         <v>45371</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63617,7 +63617,7 @@
         <v>46195</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63690,7 +63690,7 @@
         <v>44616</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63768,7 +63768,7 @@
         <v>45042</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63841,7 +63841,7 @@
         <v>45047</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63914,7 +63914,7 @@
         <v>44624</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -63992,7 +63992,7 @@
         <v>46198</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64065,7 +64065,7 @@
         <v>45327</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64138,7 +64138,7 @@
         <v>45050</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64211,7 +64211,7 @@
         <v>46198</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64289,7 +64289,7 @@
         <v>45037</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64367,7 +64367,7 @@
         <v>45300</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64440,7 +64440,7 @@
         <v>44533</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64513,7 +64513,7 @@
         <v>46199</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64591,7 +64591,7 @@
         <v>45581</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64664,7 +64664,7 @@
         <v>45162</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64742,7 +64742,7 @@
         <v>46202</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64815,7 +64815,7 @@
         <v>45154</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64888,7 +64888,7 @@
         <v>46202</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64961,7 +64961,7 @@
         <v>44849</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65034,7 +65034,7 @@
         <v>45677</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65107,7 +65107,7 @@
         <v>45757</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65180,7 +65180,7 @@
         <v>44977</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65258,7 +65258,7 @@
         <v>46206</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         <v>46206</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65409,7 +65409,7 @@
         <v>46206</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65487,7 +65487,7 @@
         <v>46206</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>44993</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>45068</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>45958</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65789,7 +65789,7 @@
         <v>44929</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65862,7 +65862,7 @@
         <v>45601</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65940,7 +65940,7 @@
         <v>44544</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66013,7 +66013,7 @@
         <v>45159</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66086,7 +66086,7 @@
         <v>46258</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66159,7 +66159,7 @@
         <v>45127</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66232,7 +66232,7 @@
         <v>45216</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66310,7 +66310,7 @@
         <v>46217</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66383,7 +66383,7 @@
         <v>46218</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66461,7 +66461,7 @@
         <v>45614</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66539,7 +66539,7 @@
         <v>45145</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66612,7 +66612,7 @@
         <v>45254</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66685,7 +66685,7 @@
         <v>46260</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66763,7 +66763,7 @@
         <v>46261</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66841,7 +66841,7 @@
         <v>44551</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66919,7 +66919,7 @@
         <v>46259</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66992,7 +66992,7 @@
         <v>45236</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67065,7 +67065,7 @@
         <v>46205</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67138,7 +67138,7 @@
         <v>45341</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67216,7 +67216,7 @@
         <v>46267</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67289,7 +67289,7 @@
         <v>45006</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67362,7 +67362,7 @@
         <v>45202</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67435,7 +67435,7 @@
         <v>46266</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67513,7 +67513,7 @@
         <v>44946</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67586,7 +67586,7 @@
         <v>46224</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>44522</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67737,7 +67737,7 @@
         <v>44593</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67815,7 +67815,7 @@
         <v>46267</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67888,7 +67888,7 @@
         <v>46267</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>46267</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>45299</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>45307</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>45351</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>46202</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68331,7 +68331,7 @@
         <v>45371</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68409,7 +68409,7 @@
         <v>45254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68482,7 +68482,7 @@
         <v>46272</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68555,7 +68555,7 @@
         <v>44908</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68628,7 +68628,7 @@
         <v>45163</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68701,7 +68701,7 @@
         <v>46273</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68779,7 +68779,7 @@
         <v>45181</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68857,7 +68857,7 @@
         <v>46275</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68935,7 +68935,7 @@
         <v>45134</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69013,7 +69013,7 @@
         <v>46273</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69091,7 +69091,7 @@
         <v>46274</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69169,7 +69169,7 @@
         <v>46274</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69247,7 +69247,7 @@
         <v>46265</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69325,7 +69325,7 @@
         <v>44866</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69398,7 +69398,7 @@
         <v>45152</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69471,7 +69471,7 @@
         <v>46276</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69549,7 +69549,7 @@
         <v>46276</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69627,7 +69627,7 @@
         <v>46281</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69705,7 +69705,7 @@
         <v>46234</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69778,7 +69778,7 @@
         <v>46234</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69851,7 +69851,7 @@
         <v>46237</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69929,7 +69929,7 @@
         <v>45341</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70002,7 +70002,7 @@
         <v>45446</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70080,7 +70080,7 @@
         <v>45524</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70158,7 +70158,7 @@
         <v>46237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70236,7 +70236,7 @@
         <v>45344</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70314,7 +70314,7 @@
         <v>46283</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70387,7 +70387,7 @@
         <v>44817</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70460,7 +70460,7 @@
         <v>46240</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70533,7 +70533,7 @@
         <v>44629</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70606,7 +70606,7 @@
         <v>45096</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70679,7 +70679,7 @@
         <v>45580</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70752,7 +70752,7 @@
         <v>45757</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70825,7 +70825,7 @@
         <v>44560</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70898,7 +70898,7 @@
         <v>44594</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70971,7 +70971,7 @@
         <v>45426</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71044,7 +71044,7 @@
         <v>44912</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71117,7 +71117,7 @@
         <v>44967</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71190,7 +71190,7 @@
         <v>44614</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71263,7 +71263,7 @@
         <v>44930</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71336,7 +71336,7 @@
         <v>45098</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71409,7 +71409,7 @@
         <v>45014</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71482,7 +71482,7 @@
         <v>45474</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71555,7 +71555,7 @@
         <v>45194</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71633,7 +71633,7 @@
         <v>44819</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71706,7 +71706,7 @@
         <v>45341</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71784,7 +71784,7 @@
         <v>46272</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71857,7 +71857,7 @@
         <v>46290</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71930,7 +71930,7 @@
         <v>44914</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72003,7 +72003,7 @@
         <v>44984</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72081,7 +72081,7 @@
         <v>45524</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72159,7 +72159,7 @@
         <v>44623</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72237,7 +72237,7 @@
         <v>44960</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72310,7 +72310,7 @@
         <v>44960</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72383,7 +72383,7 @@
         <v>46251</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72461,7 +72461,7 @@
         <v>46251</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72539,7 +72539,7 @@
         <v>46251</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72617,7 +72617,7 @@
         <v>44532</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72690,7 +72690,7 @@
         <v>44820</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72768,7 +72768,7 @@
         <v>45352</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72841,7 +72841,7 @@
         <v>45358</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72914,7 +72914,7 @@
         <v>44944</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72987,7 +72987,7 @@
         <v>44504</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73060,7 +73060,7 @@
         <v>45225</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73133,7 +73133,7 @@
         <v>44603</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73206,7 +73206,7 @@
         <v>45513</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73284,7 +73284,7 @@
         <v>44848</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73357,7 +73357,7 @@
         <v>45379</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73430,7 +73430,7 @@
         <v>45323</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73508,7 +73508,7 @@
         <v>44588</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73581,7 +73581,7 @@
         <v>44883</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73659,7 +73659,7 @@
         <v>44553</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73732,7 +73732,7 @@
         <v>46251</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73810,7 +73810,7 @@
         <v>46254</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73883,7 +73883,7 @@
         <v>45096</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73956,7 +73956,7 @@
         <v>45148</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74029,7 +74029,7 @@
         <v>45104</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74102,7 +74102,7 @@
         <v>45478</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74180,7 +74180,7 @@
         <v>45096</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74253,7 +74253,7 @@
         <v>44977</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74326,7 +74326,7 @@
         <v>45231</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74399,7 +74399,7 @@
         <v>44609</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74477,7 +74477,7 @@
         <v>44888</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74555,7 +74555,7 @@
         <v>45110</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74628,7 +74628,7 @@
         <v>44623</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74706,7 +74706,7 @@
         <v>45644</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74779,7 +74779,7 @@
         <v>45075</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74852,7 +74852,7 @@
         <v>45148</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74925,7 +74925,7 @@
         <v>45148</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -74998,7 +74998,7 @@
         <v>45182</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75071,7 +75071,7 @@
         <v>45266</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75144,7 +75144,7 @@
         <v>45089</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75217,7 +75217,7 @@
         <v>44652</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75290,7 +75290,7 @@
         <v>45694</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75363,7 +75363,7 @@
         <v>44624</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75441,7 +75441,7 @@
         <v>45685</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75514,7 +75514,7 @@
         <v>45097</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75587,7 +75587,7 @@
         <v>45435</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75665,7 +75665,7 @@
         <v>45317</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75738,7 +75738,7 @@
         <v>45180</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75816,7 +75816,7 @@
         <v>45611</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75889,7 +75889,7 @@
         <v>45049</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75962,7 +75962,7 @@
         <v>45254</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76035,7 +76035,7 @@
         <v>45344</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76113,7 +76113,7 @@
         <v>45762</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76186,7 +76186,7 @@
         <v>44610</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76264,7 +76264,7 @@
         <v>45453</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76337,7 +76337,7 @@
         <v>45638</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76410,7 +76410,7 @@
         <v>45520</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76483,7 +76483,7 @@
         <v>45107</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76556,7 +76556,7 @@
         <v>45574</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76629,7 +76629,7 @@
         <v>45779</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76707,7 +76707,7 @@
         <v>45558</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76780,7 +76780,7 @@
         <v>44569</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76858,7 +76858,7 @@
         <v>45254</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76931,7 +76931,7 @@
         <v>45368</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77009,7 +77009,7 @@
         <v>44602</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77087,7 +77087,7 @@
         <v>44606</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77165,7 +77165,7 @@
         <v>45315</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77243,7 +77243,7 @@
         <v>45173</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77316,7 +77316,7 @@
         <v>44985</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77389,7 +77389,7 @@
         <v>45398</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77467,7 +77467,7 @@
         <v>44645</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77545,7 +77545,7 @@
         <v>44609</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77623,7 +77623,7 @@
         <v>44623</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77701,7 +77701,7 @@
         <v>46086</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77774,7 +77774,7 @@
         <v>46093</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77847,7 +77847,7 @@
         <v>46089</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77925,7 +77925,7 @@
         <v>46089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78003,7 +78003,7 @@
         <v>46129</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44792</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>46289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45853</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>46009</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>46009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>46155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45728</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>46099</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>46303</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>46234</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>45092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45874</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>46199</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>45316</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45803</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45442</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>46009</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45715</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>46163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45996</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44500</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>46100</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45358</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45803</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45989</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44574</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45985</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45974</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45985</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46207</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44791</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>44974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>46155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44720</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45107</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>46009</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>45961</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44610</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44719</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44664</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44855</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45371</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45905</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45905</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45726</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>46037</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44495</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46003</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45273</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45035</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44516</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45687</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45803</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45679</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44489</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>46191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>46234</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44984</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44963</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45464</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45694</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45429</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45960</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45168</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45665</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45223</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>44849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46267</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45965</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44917</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44847</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45107</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44831</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45316</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44487</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45385</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45583</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44673</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45335</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45638</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45173</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44594</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45098</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45173</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45736</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45645</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44980</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45442</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45314</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>46106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44886</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>44574</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46147</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>46069</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>46153</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46160</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>46212</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>46275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>46234</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>46141</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46141</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>46280</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44489</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44609</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44486</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>44572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44659</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44662</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44494</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>44700</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44784</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44612</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44886</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44598</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>44883</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44610</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44865</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44704</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44533</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44764</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44491</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44676</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44479</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44512</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44543</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44495</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44847</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>44740</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44705</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44522</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>44705</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44705</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44722</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44692</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44847</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44799</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44750</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44575</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44575</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44504</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44698</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>44643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>44750</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>44599</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44733</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44711</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44846</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44865</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44702</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44593</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>44743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44623</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44729</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44883</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>44866</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44791</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45757</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44872</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45222</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45513</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45259</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45336</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45096</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44900</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45580</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>44944</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45295</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45554</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45187</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45371</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44816</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45169</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45763</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45317</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45758</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44809</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>44810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45435</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45763</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45548</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45119</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>44532</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45190</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44551</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45208</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44977</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44501</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45231</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>44859</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45336</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44548</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>44550</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45110</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45194</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45259</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45474</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45300</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45589</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44883</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>44609</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44849</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>44503</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44624</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45254</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45611</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>44593</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45344</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45107</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45107</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45107</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>45344</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44816</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>45729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45729</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45096</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45341</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45839</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45327</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45014</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>44544</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>44593</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44519</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45685</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45341</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45163</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45345</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45096</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44935</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44914</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45061</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44912</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44504</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44602</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44967</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45075</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45699</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45733</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45426</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>44977</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45154</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45729</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45903</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44624</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45175</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45618</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45644</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44637</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45006</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45307</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45453</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45524</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45327</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>44603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45905</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>44967</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45300</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44599</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>44593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>44593</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45524</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44629</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45468</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45344</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45037</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45107</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44946</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45425</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45912</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45134</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45194</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45520</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45574</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45779</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45915</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44608</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44535</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44637</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>45202</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45916</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45162</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44569</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45552</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45145</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45329</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45918</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45558</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45562</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45201</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45368</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45358</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>44960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>44569</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44522</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44616</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45684</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45922</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45177</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45923</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44553</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45371</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45091</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45583</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45923</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45231</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45584</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>44575</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45926</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45097</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45926</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45926</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45926</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45614</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45926</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>44893</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45926</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45159</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45369</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44904</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>44678</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45615</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>44659</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45638</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45525</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>45188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         <v>45379</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>44912</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>44614</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>45636</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45929</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45929</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45443</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>44967</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44832</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45490</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45932</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45931</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45338</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45932</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45721</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45439</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45931</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45148</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45148</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45148</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>44588</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45932</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45202</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45323</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45194</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45601</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>45799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45733</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>44594</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44512</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45799</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45371</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45677</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45799</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>44629</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45390</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>44617</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45086</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45744</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45341</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45608</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45351</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>44977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45446</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45054</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45426</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>44993</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45511</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45937</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45194</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>44819</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>45215</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>44733</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>45055</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>45182</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45182</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45093</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45809</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45938</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45453</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>44994</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45940</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45942</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45812</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45407</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>45188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44665</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45231</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45068</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45677</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45898</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45721</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45695</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45363</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45946</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>44967</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>44929</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>45817</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50647,7 +50647,7 @@
         <v>45730</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45614</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45817</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45946</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45946</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45216</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>45216</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45950</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45694</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>45821</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45821</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>45949</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44608</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>44588</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>44909</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45208</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45705</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>45950</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45180</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>45107</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44614</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>44679</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45149</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45831</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45831</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45181</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45089</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45831</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>44679</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45832</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>45831</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45954</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45954</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>45954</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         <v>45958</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>45958</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>45958</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45958</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45958</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45958</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45958</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45959</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45182</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>45961</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45961</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45821</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>44699</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45840</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45965</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45225</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45259</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45113</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45113</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45971</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45679</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45236</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45757</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45971</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45763</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45972</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45299</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55444,7 +55444,7 @@
         <v>45267</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>45236</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45644</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55668,7 +55668,7 @@
         <v>44644</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45426</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45852</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>45852</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45852</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45975</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45856</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56199,7 +56199,7 @@
         <v>44508</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>44799</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>44519</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45321</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>45317</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45349</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45361</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45098</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45975</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45694</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45164</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>45831</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>44820</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45351</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>44930</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45065</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57392,7 +57392,7 @@
         <v>45310</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>44532</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57538,7 +57538,7 @@
         <v>45874</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57611,7 +57611,7 @@
         <v>45054</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57684,7 +57684,7 @@
         <v>45091</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45982</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45047</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>44888</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45981</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45127</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         <v>45881</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>45882</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45981</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45981</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>45048</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>46097</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>46094</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>46094</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58721,7 +58721,7 @@
         <v>45958</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45981</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>44788</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46098</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59018,7 +59018,7 @@
         <v>44848</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>45259</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>44817</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>45216</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>44993</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
         <v>45983</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59456,7 +59456,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>44531</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>46107</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59675,7 +59675,7 @@
         <v>46107</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45599</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>45988</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46111</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46111</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>44532</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45992</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45992</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46111</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>44984</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45391</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46114</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46119</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45520</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>44581</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>44568</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>46119</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>44908</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46122</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45995</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45995</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>44949</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45987</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>44946</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>45033</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>44531</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46132</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46132</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>44960</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46132</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>44593</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>46132</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45939</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>44819</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>44616</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45981</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45882</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44560</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>44600</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62831,7 +62831,7 @@
         <v>44623</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>44623</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45167</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45757</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>46135</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>44965</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>44965</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>45308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45212</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>44886</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>45181</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63649,7 +63649,7 @@
         <v>45890</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>46051</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>44742</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63883,7 +63883,7 @@
         <v>46013</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>46014</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45968</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64107,7 +64107,7 @@
         <v>45863</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>45341</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64258,7 +64258,7 @@
         <v>45876</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64331,7 +64331,7 @@
         <v>45699</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>45940</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45695</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45300</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>45769</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46030</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46030</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64852,7 +64852,7 @@
         <v>45097</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64925,7 +64925,7 @@
         <v>46029</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64998,7 +64998,7 @@
         <v>44969</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65071,7 +65071,7 @@
         <v>44944</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65144,7 +65144,7 @@
         <v>45601</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65217,7 +65217,7 @@
         <v>45154</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65290,7 +65290,7 @@
         <v>44652</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>45678</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44679</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>46031</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>45852</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>45838</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65733,7 +65733,7 @@
         <v>45694</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>45456</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>44806</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65952,7 +65952,7 @@
         <v>45049</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66025,7 +66025,7 @@
         <v>45966</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>45901</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>44645</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>44497</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45152</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>44964</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>44599</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45880</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>45000</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45293</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>45762</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>45942</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>45867</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>45691</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>45352</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>44944</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46141</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67286,7 +67286,7 @@
         <v>46051</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67359,7 +67359,7 @@
         <v>46051</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67432,7 +67432,7 @@
         <v>46055</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>46055</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>46057</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67656,7 +67656,7 @@
         <v>46062</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67729,7 +67729,7 @@
         <v>46062</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67807,7 +67807,7 @@
         <v>46062</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67885,7 +67885,7 @@
         <v>46062</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>46064</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>46146</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>46065</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         <v>46065</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68255,7 +68255,7 @@
         <v>46076</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68333,7 +68333,7 @@
         <v>46080</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68406,7 +68406,7 @@
         <v>46085</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68479,7 +68479,7 @@
         <v>46065</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68552,7 +68552,7 @@
         <v>46155</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68630,7 +68630,7 @@
         <v>46155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68708,7 +68708,7 @@
         <v>46155</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68786,7 +68786,7 @@
         <v>46090</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>46091</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68932,7 +68932,7 @@
         <v>46091</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69005,7 +69005,7 @@
         <v>46090</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>46091</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45930</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69224,7 +69224,7 @@
         <v>46160</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69297,7 +69297,7 @@
         <v>46160</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69370,7 +69370,7 @@
         <v>46091</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69443,7 +69443,7 @@
         <v>46091</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69516,7 +69516,7 @@
         <v>46091</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69589,7 +69589,7 @@
         <v>46161</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>46093</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>46137</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69813,7 +69813,7 @@
         <v>46094</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69886,7 +69886,7 @@
         <v>46094</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69959,7 +69959,7 @@
         <v>46094</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70032,7 +70032,7 @@
         <v>46094</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70105,7 +70105,7 @@
         <v>46112</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70178,7 +70178,7 @@
         <v>46112</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70251,7 +70251,7 @@
         <v>46162</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46162</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70407,7 +70407,7 @@
         <v>46163</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70480,7 +70480,7 @@
         <v>46167</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70558,7 +70558,7 @@
         <v>46167</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70631,7 +70631,7 @@
         <v>46167</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70704,7 +70704,7 @@
         <v>46167</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70777,7 +70777,7 @@
         <v>45644</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70850,7 +70850,7 @@
         <v>45761</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70923,7 +70923,7 @@
         <v>46171</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70996,7 +70996,7 @@
         <v>46171</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71074,7 +71074,7 @@
         <v>46171</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71147,7 +71147,7 @@
         <v>45743</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71220,7 +71220,7 @@
         <v>46176</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>46181</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71371,7 +71371,7 @@
         <v>46178</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71444,7 +71444,7 @@
         <v>46185</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71517,7 +71517,7 @@
         <v>46184</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71595,7 +71595,7 @@
         <v>46188</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71668,7 +71668,7 @@
         <v>46188</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71741,7 +71741,7 @@
         <v>46188</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71814,7 +71814,7 @@
         <v>46188</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
         <v>46191</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>46191</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72043,7 +72043,7 @@
         <v>46191</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72116,7 +72116,7 @@
         <v>46191</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72194,7 +72194,7 @@
         <v>46191</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72272,7 +72272,7 @@
         <v>46195</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72345,7 +72345,7 @@
         <v>46199</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>45581</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72496,7 +72496,7 @@
         <v>46198</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72574,7 +72574,7 @@
         <v>46198</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72647,7 +72647,7 @@
         <v>46202</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72720,7 +72720,7 @@
         <v>46202</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72793,7 +72793,7 @@
         <v>46206</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72871,7 +72871,7 @@
         <v>46206</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72949,7 +72949,7 @@
         <v>46206</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73022,7 +73022,7 @@
         <v>46206</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73100,7 +73100,7 @@
         <v>45958</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73178,7 +73178,7 @@
         <v>46217</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73251,7 +73251,7 @@
         <v>45254</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73324,7 +73324,7 @@
         <v>46218</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73402,7 +73402,7 @@
         <v>46205</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73475,7 +73475,7 @@
         <v>46266</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73553,7 +73553,7 @@
         <v>46267</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46267</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46224</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46267</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73855,7 +73855,7 @@
         <v>46267</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73928,7 +73928,7 @@
         <v>46272</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74001,7 +74001,7 @@
         <v>46273</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74079,7 +74079,7 @@
         <v>45254</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74152,7 +74152,7 @@
         <v>46274</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74230,7 +74230,7 @@
         <v>46274</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74308,7 +74308,7 @@
         <v>46202</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>46265</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46276</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74537,7 +74537,7 @@
         <v>46276</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74615,7 +74615,7 @@
         <v>46275</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74693,7 +74693,7 @@
         <v>46237</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74771,7 +74771,7 @@
         <v>46237</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74849,7 +74849,7 @@
         <v>46281</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46234</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46240</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>46290</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75219,7 +75219,7 @@
         <v>46251</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>46251</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75375,7 +75375,7 @@
         <v>46251</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>46300</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>46251</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75604,7 +75604,7 @@
         <v>46254</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75677,7 +75677,7 @@
         <v>46300</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75750,7 +75750,7 @@
         <v>46300</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75823,7 +75823,7 @@
         <v>46258</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75896,7 +75896,7 @@
         <v>46302</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75969,7 +75969,7 @@
         <v>46259</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76042,7 +76042,7 @@
         <v>46303</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76120,7 +76120,7 @@
         <v>46272</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76193,7 +76193,7 @@
         <v>46160</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76271,7 +76271,7 @@
         <v>46140</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76349,7 +76349,7 @@
         <v>46260</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76427,7 +76427,7 @@
         <v>46273</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76505,7 +76505,7 @@
         <v>46303</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76583,7 +76583,7 @@
         <v>46303</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76661,7 +76661,7 @@
         <v>46261</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
         <v>45943</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45947</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76895,7 +76895,7 @@
         <v>46172</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76973,7 +76973,7 @@
         <v>44602</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77051,7 +77051,7 @@
         <v>44606</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77129,7 +77129,7 @@
         <v>44645</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77207,7 +77207,7 @@
         <v>44609</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77285,7 +77285,7 @@
         <v>44623</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77363,7 +77363,7 @@
         <v>45315</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77441,7 +77441,7 @@
         <v>45173</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77514,7 +77514,7 @@
         <v>44985</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77587,7 +77587,7 @@
         <v>45398</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>46086</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>46093</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>46089</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>46089</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77967,7 +77967,7 @@
         <v>46129</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>44792</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>46289</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45853</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         <v>46009</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3403,7 +3403,7 @@
         <v>46246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
         <v>46009</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         <v>45803</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>46155</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>45728</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>46099</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>46303</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>44971</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5212,7 +5212,7 @@
         <v>46234</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>45092</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>45086</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         <v>45874</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>46199</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>45316</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>44532</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45803</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>45196</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44575</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>45442</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         <v>46009</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44726</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7204,7 +7204,7 @@
         <v>45715</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45803</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>46163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>45996</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44500</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8177,7 +8177,7 @@
         <v>46100</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>45358</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45910</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         <v>44497</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9151,7 +9151,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45803</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>46181</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>46198</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45989</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44574</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>45985</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>45974</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>46055</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>45985</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>46234</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>46207</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44791</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44966</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>44974</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45097</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>46155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>44720</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45107</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>45820</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>46009</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12044,7 +12044,7 @@
         <v>45721</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12267,7 +12267,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>45961</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>44610</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>44719</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44886</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12952,7 +12952,7 @@
         <v>44664</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>44855</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>45371</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45905</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         <v>45905</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45726</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>45167</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>46037</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44495</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14070,7 +14070,7 @@
         <v>46155</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>46003</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14419,7 +14419,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>45273</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45035</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>44516</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45687</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15097,7 +15097,7 @@
         <v>45803</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45679</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15321,7 +15321,7 @@
         <v>44489</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15539,7 +15539,7 @@
         <v>44804</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45831</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46093</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>46191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>46234</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44984</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16304,7 +16304,7 @@
         <v>44963</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45464</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>45694</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45776</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45429</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>45960</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>45168</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45665</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>45223</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>44849</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>46267</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>44630</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>45965</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>44714</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>44651</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44517</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18587,7 +18587,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>44917</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>44847</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>45107</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>44831</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19131,7 +19131,7 @@
         <v>45316</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>44894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44487</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19569,7 +19569,7 @@
         <v>45385</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45896</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44909</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45583</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20007,7 +20007,7 @@
         <v>45916</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>44673</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>45181</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45107</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45335</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20551,7 +20551,7 @@
         <v>45638</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>45190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45938</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45173</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44594</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45098</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21296,7 +21296,7 @@
         <v>45950</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45173</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21506,7 +21506,7 @@
         <v>45736</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44958</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>45645</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21831,7 +21831,7 @@
         <v>44980</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45442</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44917</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22155,7 +22155,7 @@
         <v>45314</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>46106</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22365,7 +22365,7 @@
         <v>45757</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22470,7 +22470,7 @@
         <v>45121</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>44886</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46009</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>44574</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46147</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>46069</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>46153</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46160</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>46212</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23658,7 +23658,7 @@
         <v>46274</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>46275</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>46234</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>46141</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46141</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>46280</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24955,7 +24955,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25033,7 +25033,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25106,7 +25106,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25179,7 +25179,7 @@
         <v>44517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25252,7 +25252,7 @@
         <v>44567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25330,7 +25330,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25403,7 +25403,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25481,7 +25481,7 @@
         <v>44489</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>44609</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>44491</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25705,7 +25705,7 @@
         <v>44569</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25783,7 +25783,7 @@
         <v>44486</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>44572</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>44659</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>44662</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>44494</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>44700</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>44839</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>44603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>44784</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>44612</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44886</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>44598</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26679,7 +26679,7 @@
         <v>44883</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>44610</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44865</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>44704</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>44533</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>44764</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44609</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>44490</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27283,7 +27283,7 @@
         <v>44551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27356,7 +27356,7 @@
         <v>44491</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44676</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>44479</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>44512</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>44543</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>44571</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>44495</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>44847</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>44740</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>44705</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44522</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>44816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>44705</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28315,7 +28315,7 @@
         <v>44705</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>44722</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44692</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44847</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44799</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>44750</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>44575</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>44575</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>44685</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>44504</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>44698</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>44643</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29294,7 +29294,7 @@
         <v>44750</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>44599</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>44733</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>44711</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44846</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>44865</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29742,7 +29742,7 @@
         <v>44702</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29815,7 +29815,7 @@
         <v>44593</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29888,7 +29888,7 @@
         <v>44743</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29961,7 +29961,7 @@
         <v>44623</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30039,7 +30039,7 @@
         <v>44729</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>44883</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>44866</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>44659</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>44791</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45757</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30492,7 +30492,7 @@
         <v>45078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30570,7 +30570,7 @@
         <v>45266</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>44872</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45222</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30789,7 +30789,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30867,7 +30867,7 @@
         <v>44798</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>45202</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31013,7 +31013,7 @@
         <v>45513</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45259</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31242,7 +31242,7 @@
         <v>45336</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31315,7 +31315,7 @@
         <v>45096</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31388,7 +31388,7 @@
         <v>45050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44900</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45580</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>44944</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>45295</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31758,7 +31758,7 @@
         <v>45554</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45187</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>45371</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -31987,7 +31987,7 @@
         <v>44816</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>45169</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32138,7 +32138,7 @@
         <v>45763</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32211,7 +32211,7 @@
         <v>45317</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>45758</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32357,7 +32357,7 @@
         <v>44809</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32430,7 +32430,7 @@
         <v>44810</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32503,7 +32503,7 @@
         <v>45244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32581,7 +32581,7 @@
         <v>45435</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32659,7 +32659,7 @@
         <v>45307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>45763</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45104</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>45548</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>45119</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>44532</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33097,7 +33097,7 @@
         <v>45190</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>44551</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33248,7 +33248,7 @@
         <v>45208</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>44977</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>44501</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45231</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>44859</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33691,7 +33691,7 @@
         <v>45336</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33764,7 +33764,7 @@
         <v>44832</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33837,7 +33837,7 @@
         <v>44548</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33910,7 +33910,7 @@
         <v>44550</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>45110</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45194</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34212,7 +34212,7 @@
         <v>45259</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34285,7 +34285,7 @@
         <v>45259</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>45474</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34431,7 +34431,7 @@
         <v>45300</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34504,7 +34504,7 @@
         <v>45589</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34577,7 +34577,7 @@
         <v>44883</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>44609</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34728,7 +34728,7 @@
         <v>44849</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>44503</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>44624</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45254</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35025,7 +35025,7 @@
         <v>45611</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35098,7 +35098,7 @@
         <v>44593</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45344</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45107</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45107</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45107</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>45344</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35551,7 +35551,7 @@
         <v>44816</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35629,7 +35629,7 @@
         <v>45729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45729</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45133</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45096</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>45341</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36072,7 +36072,7 @@
         <v>45839</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45327</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36218,7 +36218,7 @@
         <v>45014</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36291,7 +36291,7 @@
         <v>44544</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36364,7 +36364,7 @@
         <v>44593</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44519</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45685</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45341</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36656,7 +36656,7 @@
         <v>45163</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45460</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>45345</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45096</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -36953,7 +36953,7 @@
         <v>44935</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37026,7 +37026,7 @@
         <v>44914</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37099,7 +37099,7 @@
         <v>45061</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37172,7 +37172,7 @@
         <v>44912</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>44504</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>44602</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37391,7 +37391,7 @@
         <v>44967</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45075</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37537,7 +37537,7 @@
         <v>45699</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45733</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37683,7 +37683,7 @@
         <v>45426</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45478</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         <v>44977</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -37907,7 +37907,7 @@
         <v>45154</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>45729</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45903</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44624</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38209,7 +38209,7 @@
         <v>45175</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38282,7 +38282,7 @@
         <v>45618</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45644</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38428,7 +38428,7 @@
         <v>44637</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45006</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38579,7 +38579,7 @@
         <v>45307</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45453</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
         <v>45524</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38803,7 +38803,7 @@
         <v>45327</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38876,7 +38876,7 @@
         <v>44603</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -38949,7 +38949,7 @@
         <v>45905</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39022,7 +39022,7 @@
         <v>44967</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>45161</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>45300</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>44599</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39314,7 +39314,7 @@
         <v>44593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>44593</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>45524</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>44629</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39626,7 +39626,7 @@
         <v>45468</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>45344</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39777,7 +39777,7 @@
         <v>45037</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45107</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>44946</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40001,7 +40001,7 @@
         <v>45425</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40074,7 +40074,7 @@
         <v>45912</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45134</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40230,7 +40230,7 @@
         <v>45194</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>45520</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         <v>45574</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45779</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44533</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>45915</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40678,7 +40678,7 @@
         <v>44608</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>44535</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40829,7 +40829,7 @@
         <v>44637</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>45202</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>45916</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41053,7 +41053,7 @@
         <v>45162</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>44569</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45552</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>45145</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41355,7 +41355,7 @@
         <v>45329</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41428,7 +41428,7 @@
         <v>45918</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41501,7 +41501,7 @@
         <v>45177</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41579,7 +41579,7 @@
         <v>45558</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41652,7 +41652,7 @@
         <v>45562</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41725,7 +41725,7 @@
         <v>45201</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41798,7 +41798,7 @@
         <v>45368</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>45358</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>44960</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>44960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>44569</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>44522</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>44616</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42324,7 +42324,7 @@
         <v>45684</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45254</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>45922</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>45177</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>45923</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44553</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45371</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45091</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45583</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45923</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43074,7 +43074,7 @@
         <v>45231</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>45584</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>44575</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45926</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43371,7 +43371,7 @@
         <v>45097</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45926</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>45926</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45926</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>45614</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43751,7 +43751,7 @@
         <v>45926</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43829,7 +43829,7 @@
         <v>44893</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45926</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -43980,7 +43980,7 @@
         <v>45159</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45369</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44126,7 +44126,7 @@
         <v>44904</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44204,7 +44204,7 @@
         <v>44678</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>44610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45615</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>44659</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>45638</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45525</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>45188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44735,7 +44735,7 @@
         <v>45379</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>44912</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>44614</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45195</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>45636</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45929</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>45929</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45261,7 +45261,7 @@
         <v>45443</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45339,7 +45339,7 @@
         <v>44967</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>44832</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>45490</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45558,7 +45558,7 @@
         <v>45932</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>45931</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>45338</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45932</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45860,7 +45860,7 @@
         <v>45721</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45933,7 +45933,7 @@
         <v>45439</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>45931</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45148</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45148</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>45148</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>44588</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46381,7 +46381,7 @@
         <v>45932</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46459,7 +46459,7 @@
         <v>45202</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46537,7 +46537,7 @@
         <v>45323</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45194</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46693,7 +46693,7 @@
         <v>45601</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>45799</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>45733</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46922,7 +46922,7 @@
         <v>44594</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44512</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47068,7 +47068,7 @@
         <v>45799</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>45371</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>45677</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45799</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47375,7 +47375,7 @@
         <v>44629</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45390</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47521,7 +47521,7 @@
         <v>44617</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47594,7 +47594,7 @@
         <v>45086</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47672,7 +47672,7 @@
         <v>45744</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47745,7 +47745,7 @@
         <v>45341</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>45608</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45351</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -47969,7 +47969,7 @@
         <v>44977</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48047,7 +48047,7 @@
         <v>45446</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>45054</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45426</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>44993</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>45511</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45937</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45194</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48568,7 +48568,7 @@
         <v>44819</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48641,7 +48641,7 @@
         <v>45215</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48714,7 +48714,7 @@
         <v>44733</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48787,7 +48787,7 @@
         <v>45055</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>45182</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45182</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49006,7 +49006,7 @@
         <v>45093</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49084,7 +49084,7 @@
         <v>45809</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49162,7 +49162,7 @@
         <v>45938</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49240,7 +49240,7 @@
         <v>45453</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49318,7 +49318,7 @@
         <v>44994</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49391,7 +49391,7 @@
         <v>45940</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49464,7 +49464,7 @@
         <v>45942</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49537,7 +49537,7 @@
         <v>45812</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45407</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>45188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44665</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45231</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45068</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>45677</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50053,7 +50053,7 @@
         <v>45898</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50126,7 +50126,7 @@
         <v>45721</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50199,7 +50199,7 @@
         <v>45695</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50277,7 +50277,7 @@
         <v>45363</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50355,7 +50355,7 @@
         <v>45946</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>44967</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>44929</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50574,7 +50574,7 @@
         <v>45817</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50647,7 +50647,7 @@
         <v>45730</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45614</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50803,7 +50803,7 @@
         <v>45817</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50881,7 +50881,7 @@
         <v>45946</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -50954,7 +50954,7 @@
         <v>45946</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51027,7 +51027,7 @@
         <v>45216</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51100,7 +51100,7 @@
         <v>45216</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         <v>45950</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45694</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51324,7 +51324,7 @@
         <v>45821</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45821</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51470,7 +51470,7 @@
         <v>45949</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51543,7 +51543,7 @@
         <v>45042</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51616,7 +51616,7 @@
         <v>44608</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>44588</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>44909</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45208</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51913,7 +51913,7 @@
         <v>45705</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -51986,7 +51986,7 @@
         <v>45950</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52059,7 +52059,7 @@
         <v>45180</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>45107</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>44614</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52283,7 +52283,7 @@
         <v>44679</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52361,7 +52361,7 @@
         <v>45149</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52439,7 +52439,7 @@
         <v>45831</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52512,7 +52512,7 @@
         <v>45831</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45181</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52663,7 +52663,7 @@
         <v>45089</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52736,7 +52736,7 @@
         <v>45832</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52814,7 +52814,7 @@
         <v>45831</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52887,7 +52887,7 @@
         <v>44679</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -52965,7 +52965,7 @@
         <v>45832</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53043,7 +53043,7 @@
         <v>45831</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53121,7 +53121,7 @@
         <v>45954</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53194,7 +53194,7 @@
         <v>45954</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53267,7 +53267,7 @@
         <v>45954</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53340,7 +53340,7 @@
         <v>45958</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53418,7 +53418,7 @@
         <v>45958</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53496,7 +53496,7 @@
         <v>45958</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53574,7 +53574,7 @@
         <v>45958</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53652,7 +53652,7 @@
         <v>45958</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45958</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>45958</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>45959</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>45182</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>45961</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54110,7 +54110,7 @@
         <v>45961</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54183,7 +54183,7 @@
         <v>45694</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54256,7 +54256,7 @@
         <v>45821</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54329,7 +54329,7 @@
         <v>44699</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54407,7 +54407,7 @@
         <v>45840</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54480,7 +54480,7 @@
         <v>45965</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54558,7 +54558,7 @@
         <v>45225</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54631,7 +54631,7 @@
         <v>45259</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45113</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>45113</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>45971</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>45679</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>45236</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>45757</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45971</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55225,7 +55225,7 @@
         <v>45763</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55298,7 +55298,7 @@
         <v>45972</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45299</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55444,7 +55444,7 @@
         <v>45267</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>45236</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>45644</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55668,7 +55668,7 @@
         <v>44644</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55746,7 +55746,7 @@
         <v>45426</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55819,7 +55819,7 @@
         <v>45852</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55897,7 +55897,7 @@
         <v>45852</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55970,7 +55970,7 @@
         <v>45852</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56048,7 +56048,7 @@
         <v>45975</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56121,7 +56121,7 @@
         <v>45856</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56199,7 +56199,7 @@
         <v>44508</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56277,7 +56277,7 @@
         <v>44799</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56350,7 +56350,7 @@
         <v>44519</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56423,7 +56423,7 @@
         <v>45321</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56496,7 +56496,7 @@
         <v>45317</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56569,7 +56569,7 @@
         <v>45349</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56642,7 +56642,7 @@
         <v>45361</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56720,7 +56720,7 @@
         <v>45098</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56793,7 +56793,7 @@
         <v>45975</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56871,7 +56871,7 @@
         <v>45694</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56944,7 +56944,7 @@
         <v>45164</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57022,7 +57022,7 @@
         <v>45831</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57095,7 +57095,7 @@
         <v>44820</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57173,7 +57173,7 @@
         <v>45351</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57246,7 +57246,7 @@
         <v>44930</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>45065</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57392,7 +57392,7 @@
         <v>45310</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57465,7 +57465,7 @@
         <v>44532</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57538,7 +57538,7 @@
         <v>45874</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57611,7 +57611,7 @@
         <v>45054</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57684,7 +57684,7 @@
         <v>45091</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45982</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>45047</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57903,7 +57903,7 @@
         <v>44888</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>45981</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>45127</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         <v>45881</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58200,7 +58200,7 @@
         <v>45882</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58273,7 +58273,7 @@
         <v>45981</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45981</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58429,7 +58429,7 @@
         <v>45048</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>46097</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>46094</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58648,7 +58648,7 @@
         <v>46094</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58721,7 +58721,7 @@
         <v>45958</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58799,7 +58799,7 @@
         <v>45981</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58872,7 +58872,7 @@
         <v>44788</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58945,7 +58945,7 @@
         <v>46098</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59018,7 +59018,7 @@
         <v>44848</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59091,7 +59091,7 @@
         <v>45259</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>44817</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>45216</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59310,7 +59310,7 @@
         <v>44993</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59383,7 +59383,7 @@
         <v>45983</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59456,7 +59456,7 @@
         <v>46107</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59529,7 +59529,7 @@
         <v>44531</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59602,7 +59602,7 @@
         <v>46107</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59675,7 +59675,7 @@
         <v>46107</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45599</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59846,7 +59846,7 @@
         <v>45988</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>46111</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>46111</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>44532</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45992</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45992</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>46111</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>44984</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45391</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>46114</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46119</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>45520</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>44581</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>44568</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60893,7 +60893,7 @@
         <v>46119</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -60966,7 +60966,7 @@
         <v>44908</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46122</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45995</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>45995</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61258,7 +61258,7 @@
         <v>44949</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61331,7 +61331,7 @@
         <v>45987</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61404,7 +61404,7 @@
         <v>44946</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61477,7 +61477,7 @@
         <v>45033</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61550,7 +61550,7 @@
         <v>44531</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61701,7 +61701,7 @@
         <v>46132</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46133</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61847,7 +61847,7 @@
         <v>46132</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>44960</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>46132</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62076,7 +62076,7 @@
         <v>44593</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62154,7 +62154,7 @@
         <v>44928</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62232,7 +62232,7 @@
         <v>46132</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>45939</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>44819</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62461,7 +62461,7 @@
         <v>44616</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62534,7 +62534,7 @@
         <v>45981</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>45882</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>44560</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>44600</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62831,7 +62831,7 @@
         <v>44623</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>44623</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -62987,7 +62987,7 @@
         <v>45167</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63060,7 +63060,7 @@
         <v>45757</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63133,7 +63133,7 @@
         <v>46135</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>44965</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63279,7 +63279,7 @@
         <v>44965</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63352,7 +63352,7 @@
         <v>45308</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63425,7 +63425,7 @@
         <v>45212</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>44886</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>45181</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63649,7 +63649,7 @@
         <v>45890</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63727,7 +63727,7 @@
         <v>46051</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63805,7 +63805,7 @@
         <v>44742</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63883,7 +63883,7 @@
         <v>46013</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -63956,7 +63956,7 @@
         <v>46014</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64029,7 +64029,7 @@
         <v>45968</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64107,7 +64107,7 @@
         <v>45863</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>45341</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64258,7 +64258,7 @@
         <v>45876</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64331,7 +64331,7 @@
         <v>45699</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64404,7 +64404,7 @@
         <v>45940</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64477,7 +64477,7 @@
         <v>45695</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64555,7 +64555,7 @@
         <v>45300</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64628,7 +64628,7 @@
         <v>45769</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64701,7 +64701,7 @@
         <v>46030</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64779,7 +64779,7 @@
         <v>46030</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64852,7 +64852,7 @@
         <v>45097</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64925,7 +64925,7 @@
         <v>46029</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -64998,7 +64998,7 @@
         <v>44969</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65071,7 +65071,7 @@
         <v>44944</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65144,7 +65144,7 @@
         <v>45601</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65217,7 +65217,7 @@
         <v>45154</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65290,7 +65290,7 @@
         <v>44652</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65363,7 +65363,7 @@
         <v>45678</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65436,7 +65436,7 @@
         <v>44679</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65509,7 +65509,7 @@
         <v>46031</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65582,7 +65582,7 @@
         <v>45852</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65660,7 +65660,7 @@
         <v>45838</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65733,7 +65733,7 @@
         <v>45694</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65806,7 +65806,7 @@
         <v>45456</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>44806</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -65952,7 +65952,7 @@
         <v>45049</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66025,7 +66025,7 @@
         <v>45966</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66103,7 +66103,7 @@
         <v>45901</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66181,7 +66181,7 @@
         <v>44645</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>44497</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45152</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>44964</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>44599</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45880</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>45000</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>45293</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>45762</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>45942</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>45867</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>45691</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>45352</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>44944</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46141</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67286,7 +67286,7 @@
         <v>46051</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67359,7 +67359,7 @@
         <v>46051</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67432,7 +67432,7 @@
         <v>46055</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67505,7 +67505,7 @@
         <v>46055</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67583,7 +67583,7 @@
         <v>46057</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67656,7 +67656,7 @@
         <v>46062</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67729,7 +67729,7 @@
         <v>46062</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67807,7 +67807,7 @@
         <v>46062</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67885,7 +67885,7 @@
         <v>46062</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -67963,7 +67963,7 @@
         <v>46064</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>46146</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68109,7 +68109,7 @@
         <v>46065</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68182,7 +68182,7 @@
         <v>46065</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68255,7 +68255,7 @@
         <v>46076</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68333,7 +68333,7 @@
         <v>46080</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68406,7 +68406,7 @@
         <v>46085</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68479,7 +68479,7 @@
         <v>46065</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68552,7 +68552,7 @@
         <v>46155</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68630,7 +68630,7 @@
         <v>46155</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68708,7 +68708,7 @@
         <v>46155</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68786,7 +68786,7 @@
         <v>46090</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68859,7 +68859,7 @@
         <v>46091</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -68932,7 +68932,7 @@
         <v>46091</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69005,7 +69005,7 @@
         <v>46090</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69078,7 +69078,7 @@
         <v>46091</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69151,7 +69151,7 @@
         <v>45930</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69224,7 +69224,7 @@
         <v>46160</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69297,7 +69297,7 @@
         <v>46160</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69370,7 +69370,7 @@
         <v>46091</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69443,7 +69443,7 @@
         <v>46091</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69516,7 +69516,7 @@
         <v>46091</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69589,7 +69589,7 @@
         <v>46161</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69662,7 +69662,7 @@
         <v>46093</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69735,7 +69735,7 @@
         <v>46137</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69813,7 +69813,7 @@
         <v>46094</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69886,7 +69886,7 @@
         <v>46094</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -69959,7 +69959,7 @@
         <v>46094</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70032,7 +70032,7 @@
         <v>46094</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70105,7 +70105,7 @@
         <v>46112</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70178,7 +70178,7 @@
         <v>46112</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70251,7 +70251,7 @@
         <v>46162</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70329,7 +70329,7 @@
         <v>46162</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70407,7 +70407,7 @@
         <v>46163</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70480,7 +70480,7 @@
         <v>46167</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70558,7 +70558,7 @@
         <v>46167</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70631,7 +70631,7 @@
         <v>46167</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70704,7 +70704,7 @@
         <v>46167</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70777,7 +70777,7 @@
         <v>45644</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70850,7 +70850,7 @@
         <v>45761</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -70923,7 +70923,7 @@
         <v>46171</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -70996,7 +70996,7 @@
         <v>46171</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71074,7 +71074,7 @@
         <v>46171</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71147,7 +71147,7 @@
         <v>45743</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71220,7 +71220,7 @@
         <v>46176</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71293,7 +71293,7 @@
         <v>46181</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71371,7 +71371,7 @@
         <v>46178</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71444,7 +71444,7 @@
         <v>46185</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71517,7 +71517,7 @@
         <v>46184</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71595,7 +71595,7 @@
         <v>46188</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71668,7 +71668,7 @@
         <v>46188</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71741,7 +71741,7 @@
         <v>46188</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71814,7 +71814,7 @@
         <v>46188</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71887,7 +71887,7 @@
         <v>46191</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -71965,7 +71965,7 @@
         <v>46191</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72043,7 +72043,7 @@
         <v>46191</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72116,7 +72116,7 @@
         <v>46191</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72194,7 +72194,7 @@
         <v>46191</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72272,7 +72272,7 @@
         <v>46195</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72345,7 +72345,7 @@
         <v>46199</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72423,7 +72423,7 @@
         <v>45581</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72496,7 +72496,7 @@
         <v>46198</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72574,7 +72574,7 @@
         <v>46198</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72647,7 +72647,7 @@
         <v>46202</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72720,7 +72720,7 @@
         <v>46202</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72793,7 +72793,7 @@
         <v>46206</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72871,7 +72871,7 @@
         <v>46206</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -72949,7 +72949,7 @@
         <v>46206</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73022,7 +73022,7 @@
         <v>46206</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73100,7 +73100,7 @@
         <v>45958</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73178,7 +73178,7 @@
         <v>46217</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73251,7 +73251,7 @@
         <v>45254</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73324,7 +73324,7 @@
         <v>46218</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73402,7 +73402,7 @@
         <v>46205</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73475,7 +73475,7 @@
         <v>46266</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73553,7 +73553,7 @@
         <v>46267</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73631,7 +73631,7 @@
         <v>46267</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73704,7 +73704,7 @@
         <v>46224</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73782,7 +73782,7 @@
         <v>46267</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73855,7 +73855,7 @@
         <v>46267</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -73928,7 +73928,7 @@
         <v>46272</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74001,7 +74001,7 @@
         <v>46273</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74079,7 +74079,7 @@
         <v>45254</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74152,7 +74152,7 @@
         <v>46274</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74230,7 +74230,7 @@
         <v>46274</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74308,7 +74308,7 @@
         <v>46202</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74381,7 +74381,7 @@
         <v>46265</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74459,7 +74459,7 @@
         <v>46276</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74537,7 +74537,7 @@
         <v>46276</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74615,7 +74615,7 @@
         <v>46275</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74693,7 +74693,7 @@
         <v>46237</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74771,7 +74771,7 @@
         <v>46237</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74849,7 +74849,7 @@
         <v>46281</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74927,7 +74927,7 @@
         <v>46234</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75000,7 +75000,7 @@
         <v>46240</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75073,7 +75073,7 @@
         <v>46283</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75146,7 +75146,7 @@
         <v>46290</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75219,7 +75219,7 @@
         <v>46251</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75297,7 +75297,7 @@
         <v>46251</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75375,7 +75375,7 @@
         <v>46251</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75453,7 +75453,7 @@
         <v>46300</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75526,7 +75526,7 @@
         <v>46251</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75604,7 +75604,7 @@
         <v>46254</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75677,7 +75677,7 @@
         <v>46300</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75750,7 +75750,7 @@
         <v>46300</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75823,7 +75823,7 @@
         <v>46258</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75896,7 +75896,7 @@
         <v>46302</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -75969,7 +75969,7 @@
         <v>46259</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76042,7 +76042,7 @@
         <v>46303</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76120,7 +76120,7 @@
         <v>46272</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76193,7 +76193,7 @@
         <v>46160</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76271,7 +76271,7 @@
         <v>46140</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76349,7 +76349,7 @@
         <v>46260</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76427,7 +76427,7 @@
         <v>46273</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76505,7 +76505,7 @@
         <v>46303</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76583,7 +76583,7 @@
         <v>46303</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76661,7 +76661,7 @@
         <v>46261</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76739,7 +76739,7 @@
         <v>45943</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76817,7 +76817,7 @@
         <v>45947</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76895,7 +76895,7 @@
         <v>46172</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76973,7 +76973,7 @@
         <v>44602</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77051,7 +77051,7 @@
         <v>44606</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77129,7 +77129,7 @@
         <v>44645</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77207,7 +77207,7 @@
         <v>44609</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77285,7 +77285,7 @@
         <v>44623</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77363,7 +77363,7 @@
         <v>45315</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77441,7 +77441,7 @@
         <v>45173</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77514,7 +77514,7 @@
         <v>44985</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77587,7 +77587,7 @@
         <v>45398</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77665,7 +77665,7 @@
         <v>46086</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77738,7 +77738,7 @@
         <v>46093</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77811,7 +77811,7 @@
         <v>46089</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77889,7 +77889,7 @@
         <v>46089</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77967,7 +77967,7 @@
         <v>46129</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>44792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>46121</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>45853</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3072,10 +3072,10 @@
         <v>20</v>
       </c>
       <c r="T19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="U19" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>46009</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
         <v>46246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>45728</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         <v>46303</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>46099</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>46303</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5220,7 +5220,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>46234</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>46199</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>45086</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>45316</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45803</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44532</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6467,7 +6467,7 @@
         <v>45442</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6713,7 +6713,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45202</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45442</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44726</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>46163</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7829,7 +7829,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7948,7 +7948,7 @@
         <v>45715</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>46100</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8676,7 +8676,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>45358</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>46181</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>45803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9756,7 +9756,7 @@
         <v>45989</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44574</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>46055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45985</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>46234</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>46207</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>45688</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11041,7 +11041,7 @@
         <v>44614</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
         <v>45097</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>44966</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>44974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>46155</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11726,7 +11726,7 @@
         <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>46009</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>45961</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12409,7 +12409,7 @@
         <v>46167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45820</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>45994</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44664</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44855</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>45167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45905</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>46155</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14092,7 +14092,7 @@
         <v>46037</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14321,7 +14321,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>46003</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>44588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14667,7 +14667,7 @@
         <v>44516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>45831</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14889,7 +14889,7 @@
         <v>45035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15005,7 +15005,7 @@
         <v>44804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>46191</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>44897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15437,7 +15437,7 @@
         <v>45293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>46234</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46234</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45273</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>45090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>45687</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>45803</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>46311</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45679</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>44489</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16546,7 +16546,7 @@
         <v>44984</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>44967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45665</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45694</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45464</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>44849</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45960</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17836,7 +17836,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45429</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>46267</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45189</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44630</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18502,7 +18502,7 @@
         <v>45965</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>44714</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44651</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44543</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>44517</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>44487</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44594</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19476,7 +19476,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>45173</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45121</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45896</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45190</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45916</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20226,7 +20226,7 @@
         <v>46147</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45638</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>46153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>45950</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45645</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>46160</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21080,7 +21080,7 @@
         <v>45385</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>45316</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>44645</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>46009</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21523,7 +21523,7 @@
         <v>46178</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>46106</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>45314</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>44831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44574</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44673</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>46212</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45442</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>46275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46274</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>44894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>44980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>45173</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>46141</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>46141</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45757</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>44917</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>46280</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45335</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>46261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         <v>45736</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44630</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>44678</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44984</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         <v>44583</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25346,7 +25346,7 @@
         <v>44602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25419,7 +25419,7 @@
         <v>44567</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>44517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>44544</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>44526</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44489</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>44609</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>44491</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26023,7 +26023,7 @@
         <v>44569</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26101,7 +26101,7 @@
         <v>44486</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>44659</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>44494</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>44603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>44700</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>44839</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44784</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>44612</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26768,7 +26768,7 @@
         <v>44886</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44883</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44598</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26997,7 +26997,7 @@
         <v>44610</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>44865</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>44704</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>44533</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>44764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27450,7 +27450,7 @@
         <v>44490</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27523,7 +27523,7 @@
         <v>44512</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44740</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27674,7 +27674,7 @@
         <v>44816</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>44705</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>44705</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>44692</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28044,7 +28044,7 @@
         <v>44504</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>44750</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28195,7 +28195,7 @@
         <v>44643</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>44846</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28341,7 +28341,7 @@
         <v>44676</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>44491</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>44847</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>44705</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44799</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>44575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>44575</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44702</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44551</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>44571</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>44634</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>44698</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29232,7 +29232,7 @@
         <v>44599</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29305,7 +29305,7 @@
         <v>44865</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>44593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>44543</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29524,7 +29524,7 @@
         <v>44495</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44522</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29670,7 +29670,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>44750</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>44685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>44733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>44711</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>44743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>44623</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>44729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>44791</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44623</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30435,7 +30435,7 @@
         <v>44798</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30508,7 +30508,7 @@
         <v>44659</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>44593</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30742,7 +30742,7 @@
         <v>44593</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45678</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>44893</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>44581</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45695</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>44637</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45615</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31341,7 +31341,7 @@
         <v>44637</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>44599</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31492,7 +31492,7 @@
         <v>44519</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31638,7 +31638,7 @@
         <v>44993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>45756</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31784,7 +31784,7 @@
         <v>44816</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31862,7 +31862,7 @@
         <v>45694</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>44967</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>44900</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>44872</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45212</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>44532</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>44944</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32451,7 +32451,7 @@
         <v>45093</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>45169</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>44980</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45216</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45552</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45244</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32904,7 +32904,7 @@
         <v>45327</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32977,7 +32977,7 @@
         <v>44960</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45425</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33123,7 +33123,7 @@
         <v>45295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>44969</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33274,7 +33274,7 @@
         <v>44809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45369</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45733</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>45363</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44617</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45107</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45107</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45300</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>44949</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45149</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>44548</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34087,7 +34087,7 @@
         <v>45033</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>45078</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>44616</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>45055</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44912</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34530,7 +34530,7 @@
         <v>45407</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34603,7 +34603,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34676,7 +34676,7 @@
         <v>44512</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34749,7 +34749,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34822,7 +34822,7 @@
         <v>44904</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34900,7 +34900,7 @@
         <v>44819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44883</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>44600</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45694</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35202,7 +35202,7 @@
         <v>44806</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35275,7 +35275,7 @@
         <v>45236</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35348,7 +35348,7 @@
         <v>44799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35421,7 +35421,7 @@
         <v>45338</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35494,7 +35494,7 @@
         <v>45164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35572,7 +35572,7 @@
         <v>45208</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45065</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45202</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>44602</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35869,7 +35869,7 @@
         <v>44503</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35942,7 +35942,7 @@
         <v>45182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36015,7 +36015,7 @@
         <v>45699</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36088,7 +36088,7 @@
         <v>44967</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36161,7 +36161,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
         <v>45000</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36312,7 +36312,7 @@
         <v>45177</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36385,7 +36385,7 @@
         <v>44699</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45300</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45188</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>45208</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45721</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36833,7 +36833,7 @@
         <v>45231</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36906,7 +36906,7 @@
         <v>44886</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36979,7 +36979,7 @@
         <v>45520</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37052,7 +37052,7 @@
         <v>45201</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>44810</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37198,7 +37198,7 @@
         <v>45729</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37271,7 +37271,7 @@
         <v>45882</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37344,7 +37344,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37417,7 +37417,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37495,7 +37495,7 @@
         <v>45699</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45940</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>45391</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>44832</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>44593</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45317</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45839</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>45695</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45763</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>44935</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>45216</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44678</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>45769</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>44501</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38615,7 +38615,7 @@
         <v>44588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45259</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38761,7 +38761,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>45705</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>45259</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38985,7 +38985,7 @@
         <v>45890</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45882</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39209,7 +39209,7 @@
         <v>45852</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>45054</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>45863</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>44575</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>44679</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39657,7 +39657,7 @@
         <v>44733</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39730,7 +39730,7 @@
         <v>45691</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45293</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45838</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>46141</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45903</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45905</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45049</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45202</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40407,7 +40407,7 @@
         <v>45867</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40480,7 +40480,7 @@
         <v>45912</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40558,7 +40558,7 @@
         <v>45915</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45267</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40714,7 +40714,7 @@
         <v>45916</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45918</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40860,7 +40860,7 @@
         <v>45758</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45922</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>45923</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>46146</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45113</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>44964</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>45926</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45926</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45926</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41688,7 +41688,7 @@
         <v>45929</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41766,7 +41766,7 @@
         <v>45929</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41844,7 +41844,7 @@
         <v>45113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41917,7 +41917,7 @@
         <v>45926</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41995,7 +41995,7 @@
         <v>45926</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42073,7 +42073,7 @@
         <v>45926</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45931</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42229,7 +42229,7 @@
         <v>44788</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>45098</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42375,7 +42375,7 @@
         <v>45931</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42453,7 +42453,7 @@
         <v>45932</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42526,7 +42526,7 @@
         <v>45932</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45932</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42682,7 +42682,7 @@
         <v>45361</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42760,7 +42760,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42838,7 +42838,7 @@
         <v>45937</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42911,7 +42911,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>45460</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43062,7 +43062,7 @@
         <v>45763</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45940</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43208,7 +43208,7 @@
         <v>44816</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45308</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45942</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43500,7 +43500,7 @@
         <v>44535</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>45898</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>44629</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>44608</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44497</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43875,7 +43875,7 @@
         <v>45946</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>44946</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44021,7 +44021,7 @@
         <v>45946</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44094,7 +44094,7 @@
         <v>44965</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>44965</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>45946</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>44679</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45336</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45336</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45950</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45949</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>45954</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>46155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44980,7 +44980,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45058,7 +45058,7 @@
         <v>45954</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>45954</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>44614</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>45958</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45360,7 +45360,7 @@
         <v>45259</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>45958</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45511,7 +45511,7 @@
         <v>45958</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45589,7 +45589,7 @@
         <v>45958</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45667,7 +45667,7 @@
         <v>45959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45958</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45589</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46125,7 +46125,7 @@
         <v>45961</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>46160</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>45961</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>45965</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45194</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46495,7 +46495,7 @@
         <v>45194</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45599</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>46160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44665</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45345</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45971</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45971</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45972</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>46112</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45443</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>44599</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>45975</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45975</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46163</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>46137</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45310</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45327</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>46162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47990,7 +47990,7 @@
         <v>46162</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45981</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>46167</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>46167</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45981</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48443,7 +48443,7 @@
         <v>45981</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>45981</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>45321</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45958</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45982</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45983</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45554</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>46167</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>45677</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45730</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45988</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>44593</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>45175</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44909</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49563,7 +49563,7 @@
         <v>45729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45729</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49709,7 +49709,7 @@
         <v>45181</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49782,7 +49782,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>45992</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45761</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50001,7 +50001,7 @@
         <v>45190</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50074,7 +50074,7 @@
         <v>44550</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50152,7 +50152,7 @@
         <v>45995</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>45995</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>45048</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45987</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50517,7 +50517,7 @@
         <v>44928</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50595,7 +50595,7 @@
         <v>45061</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50668,7 +50668,7 @@
         <v>45644</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50741,7 +50741,7 @@
         <v>44977</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50814,7 +50814,7 @@
         <v>45167</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50887,7 +50887,7 @@
         <v>45468</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50960,7 +50960,7 @@
         <v>44679</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45119</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>44531</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>46171</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51330,7 +51330,7 @@
         <v>45344</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45694</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>44508</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51559,7 +51559,7 @@
         <v>44644</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>45426</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>46013</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>46014</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>45187</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>45222</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52007,7 +52007,7 @@
         <v>46171</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>44531</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>46171</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52231,7 +52231,7 @@
         <v>44532</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52304,7 +52304,7 @@
         <v>45968</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52382,7 +52382,7 @@
         <v>44944</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52455,7 +52455,7 @@
         <v>46029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45618</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>45548</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52747,7 +52747,7 @@
         <v>46030</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52820,7 +52820,7 @@
         <v>46031</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52893,7 +52893,7 @@
         <v>44742</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>46030</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>44519</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>44967</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>46176</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53268,7 +53268,7 @@
         <v>45743</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53341,7 +53341,7 @@
         <v>46178</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53414,7 +53414,7 @@
         <v>44568</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53492,7 +53492,7 @@
         <v>45054</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53565,7 +53565,7 @@
         <v>44859</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53638,7 +53638,7 @@
         <v>44832</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53711,7 +53711,7 @@
         <v>45601</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53784,7 +53784,7 @@
         <v>45133</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53857,7 +53857,7 @@
         <v>44645</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>45371</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>46051</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>46051</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>44616</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54237,7 +54237,7 @@
         <v>46055</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54315,7 +54315,7 @@
         <v>46055</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>45042</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54461,7 +54461,7 @@
         <v>46181</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54539,7 +54539,7 @@
         <v>45047</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54612,7 +54612,7 @@
         <v>46057</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54685,7 +54685,7 @@
         <v>44624</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54763,7 +54763,7 @@
         <v>46184</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54841,7 +54841,7 @@
         <v>45050</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54914,7 +54914,7 @@
         <v>46062</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54992,7 +54992,7 @@
         <v>46062</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55070,7 +55070,7 @@
         <v>46062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>45037</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46062</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>46065</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46065</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>46064</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>45300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55591,7 +55591,7 @@
         <v>44533</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>45162</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>45154</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>46188</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>44849</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56034,7 +56034,7 @@
         <v>45677</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56107,7 +56107,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56180,7 +56180,7 @@
         <v>46076</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>46188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>44977</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>46185</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>46188</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>46080</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>46065</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>44993</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46085</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>46090</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>45068</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56993,7 +56993,7 @@
         <v>46090</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>44929</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57139,7 +57139,7 @@
         <v>46091</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57212,7 +57212,7 @@
         <v>46091</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57285,7 +57285,7 @@
         <v>46091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57358,7 +57358,7 @@
         <v>46091</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57431,7 +57431,7 @@
         <v>46191</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>46091</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>46091</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>46094</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>46094</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>45601</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>46094</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57952,7 +57952,7 @@
         <v>46094</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58025,7 +58025,7 @@
         <v>46191</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>46093</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>46094</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>44544</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>46094</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46191</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46191</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>45159</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58697,7 +58697,7 @@
         <v>46097</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58770,7 +58770,7 @@
         <v>46098</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58843,7 +58843,7 @@
         <v>45127</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58916,7 +58916,7 @@
         <v>46195</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58989,7 +58989,7 @@
         <v>45216</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59067,7 +59067,7 @@
         <v>45614</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45145</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>44551</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59296,7 +59296,7 @@
         <v>46107</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59394,7 +59394,7 @@
         <v>46107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59467,7 +59467,7 @@
         <v>46107</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59540,7 +59540,7 @@
         <v>46198</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59613,7 +59613,7 @@
         <v>46111</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59686,7 +59686,7 @@
         <v>46111</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>46111</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>46198</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45236</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59983,7 +59983,7 @@
         <v>45341</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60061,7 +60061,7 @@
         <v>46114</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45006</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45202</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>44946</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60358,7 +60358,7 @@
         <v>46119</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60431,7 +60431,7 @@
         <v>46119</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60504,7 +60504,7 @@
         <v>46122</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60577,7 +60577,7 @@
         <v>46199</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60655,7 +60655,7 @@
         <v>44522</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60728,7 +60728,7 @@
         <v>45581</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60801,7 +60801,7 @@
         <v>44593</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60879,7 +60879,7 @@
         <v>45299</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>46202</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>46202</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61098,7 +61098,7 @@
         <v>45307</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61171,7 +61171,7 @@
         <v>45351</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61244,7 +61244,7 @@
         <v>45371</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61322,7 +61322,7 @@
         <v>46133</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61395,7 +61395,7 @@
         <v>46132</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61473,7 +61473,7 @@
         <v>46132</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61551,7 +61551,7 @@
         <v>46132</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61624,7 +61624,7 @@
         <v>46132</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61702,7 +61702,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61780,7 +61780,7 @@
         <v>44908</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61853,7 +61853,7 @@
         <v>45163</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61926,7 +61926,7 @@
         <v>45181</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62004,7 +62004,7 @@
         <v>46135</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62077,7 +62077,7 @@
         <v>45134</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62155,7 +62155,7 @@
         <v>44866</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62228,7 +62228,7 @@
         <v>45152</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62301,7 +62301,7 @@
         <v>45901</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62379,7 +62379,7 @@
         <v>45456</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62452,7 +62452,7 @@
         <v>45942</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62525,7 +62525,7 @@
         <v>45876</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62598,7 +62598,7 @@
         <v>45341</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62671,7 +62671,7 @@
         <v>45446</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62749,7 +62749,7 @@
         <v>45880</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62822,7 +62822,7 @@
         <v>45524</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62900,7 +62900,7 @@
         <v>46206</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62973,7 +62973,7 @@
         <v>45757</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63046,7 +63046,7 @@
         <v>46206</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63124,7 +63124,7 @@
         <v>46206</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63202,7 +63202,7 @@
         <v>46206</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63280,7 +63280,7 @@
         <v>45344</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63358,7 +63358,7 @@
         <v>44817</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63431,7 +63431,7 @@
         <v>44629</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63504,7 +63504,7 @@
         <v>45958</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63582,7 +63582,7 @@
         <v>45096</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63655,7 +63655,7 @@
         <v>45580</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>45757</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63801,7 +63801,7 @@
         <v>44560</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63874,7 +63874,7 @@
         <v>44594</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63947,7 +63947,7 @@
         <v>45426</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64020,7 +64020,7 @@
         <v>44912</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>44967</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64166,7 +64166,7 @@
         <v>46217</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
         <v>46218</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>44614</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64390,7 +64390,7 @@
         <v>44930</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64463,7 +64463,7 @@
         <v>45254</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64536,7 +64536,7 @@
         <v>45098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64609,7 +64609,7 @@
         <v>45014</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45474</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64755,7 +64755,7 @@
         <v>46205</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64828,7 +64828,7 @@
         <v>45194</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64906,7 +64906,7 @@
         <v>46224</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64984,7 +64984,7 @@
         <v>44819</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65057,7 +65057,7 @@
         <v>46202</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65130,7 +65130,7 @@
         <v>45341</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65208,7 +65208,7 @@
         <v>45254</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65281,7 +65281,7 @@
         <v>46272</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65354,7 +65354,7 @@
         <v>46275</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65432,7 +65432,7 @@
         <v>46273</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>44914</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65583,7 +65583,7 @@
         <v>46274</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65661,7 +65661,7 @@
         <v>44984</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65739,7 +65739,7 @@
         <v>46274</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65817,7 +65817,7 @@
         <v>45524</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65895,7 +65895,7 @@
         <v>44623</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65973,7 +65973,7 @@
         <v>44960</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66046,7 +66046,7 @@
         <v>44960</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66119,7 +66119,7 @@
         <v>44532</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66192,7 +66192,7 @@
         <v>44820</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66270,7 +66270,7 @@
         <v>46276</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66348,7 +66348,7 @@
         <v>46276</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66426,7 +66426,7 @@
         <v>45352</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66499,7 +66499,7 @@
         <v>46281</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66577,7 +66577,7 @@
         <v>45358</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66650,7 +66650,7 @@
         <v>46234</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66723,7 +66723,7 @@
         <v>44944</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66796,7 +66796,7 @@
         <v>44504</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66869,7 +66869,7 @@
         <v>46237</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66947,7 +66947,7 @@
         <v>45225</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67020,7 +67020,7 @@
         <v>46237</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>44603</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67171,7 +67171,7 @@
         <v>45513</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67249,7 +67249,7 @@
         <v>44848</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67322,7 +67322,7 @@
         <v>45379</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67395,7 +67395,7 @@
         <v>45323</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67473,7 +67473,7 @@
         <v>46283</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67546,7 +67546,7 @@
         <v>46240</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67619,7 +67619,7 @@
         <v>44588</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67692,7 +67692,7 @@
         <v>44883</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>44553</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67843,7 +67843,7 @@
         <v>45096</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67916,7 +67916,7 @@
         <v>45148</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67989,7 +67989,7 @@
         <v>45104</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68062,7 +68062,7 @@
         <v>45478</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68140,7 +68140,7 @@
         <v>45096</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68213,7 +68213,7 @@
         <v>44977</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68286,7 +68286,7 @@
         <v>45231</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68359,7 +68359,7 @@
         <v>44609</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68437,7 +68437,7 @@
         <v>44888</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68515,7 +68515,7 @@
         <v>45110</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68588,7 +68588,7 @@
         <v>44623</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68666,7 +68666,7 @@
         <v>45644</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68739,7 +68739,7 @@
         <v>45075</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68812,7 +68812,7 @@
         <v>45148</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68885,7 +68885,7 @@
         <v>45148</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68958,7 +68958,7 @@
         <v>45182</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69031,7 +69031,7 @@
         <v>45266</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69104,7 +69104,7 @@
         <v>45089</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69177,7 +69177,7 @@
         <v>44652</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69250,7 +69250,7 @@
         <v>45694</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69323,7 +69323,7 @@
         <v>44624</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69401,7 +69401,7 @@
         <v>45685</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69474,7 +69474,7 @@
         <v>46290</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69547,7 +69547,7 @@
         <v>45097</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69620,7 +69620,7 @@
         <v>45435</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69698,7 +69698,7 @@
         <v>45317</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69771,7 +69771,7 @@
         <v>45180</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69849,7 +69849,7 @@
         <v>46251</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69927,7 +69927,7 @@
         <v>45611</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70000,7 +70000,7 @@
         <v>46251</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70078,7 +70078,7 @@
         <v>46251</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70156,7 +70156,7 @@
         <v>45049</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70229,7 +70229,7 @@
         <v>45254</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70302,7 +70302,7 @@
         <v>45344</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70380,7 +70380,7 @@
         <v>45762</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70453,7 +70453,7 @@
         <v>44610</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70531,7 +70531,7 @@
         <v>46251</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70609,7 +70609,7 @@
         <v>46254</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70682,7 +70682,7 @@
         <v>46258</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70755,7 +70755,7 @@
         <v>45453</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70828,7 +70828,7 @@
         <v>45638</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70901,7 +70901,7 @@
         <v>45520</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70974,7 +70974,7 @@
         <v>45107</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71047,7 +71047,7 @@
         <v>45574</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71120,7 +71120,7 @@
         <v>46300</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71193,7 +71193,7 @@
         <v>45779</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71271,7 +71271,7 @@
         <v>46300</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71344,7 +71344,7 @@
         <v>46300</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71417,7 +71417,7 @@
         <v>45558</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71490,7 +71490,7 @@
         <v>44569</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71568,7 +71568,7 @@
         <v>45254</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71641,7 +71641,7 @@
         <v>45368</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71719,7 +71719,7 @@
         <v>46140</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71797,7 +71797,7 @@
         <v>45584</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71870,7 +71870,7 @@
         <v>46160</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71948,7 +71948,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72021,7 +72021,7 @@
         <v>45091</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72099,7 +72099,7 @@
         <v>45371</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72172,7 +72172,7 @@
         <v>45684</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72245,7 +72245,7 @@
         <v>45562</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72318,7 +72318,7 @@
         <v>45177</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72396,7 +72396,7 @@
         <v>45329</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72469,7 +72469,7 @@
         <v>44569</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72547,7 +72547,7 @@
         <v>45583</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72625,7 +72625,7 @@
         <v>46260</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72703,7 +72703,7 @@
         <v>46303</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72781,7 +72781,7 @@
         <v>46302</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72854,7 +72854,7 @@
         <v>46303</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72932,7 +72932,7 @@
         <v>45490</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73005,7 +73005,7 @@
         <v>46303</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73083,7 +73083,7 @@
         <v>45195</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73156,7 +73156,7 @@
         <v>46272</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73229,7 +73229,7 @@
         <v>46261</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73307,7 +73307,7 @@
         <v>46273</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73385,7 +73385,7 @@
         <v>45439</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73463,7 +73463,7 @@
         <v>45943</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73541,7 +73541,7 @@
         <v>45636</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73614,7 +73614,7 @@
         <v>45525</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73687,7 +73687,7 @@
         <v>45947</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73765,7 +73765,7 @@
         <v>46172</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73843,7 +73843,7 @@
         <v>45733</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73916,7 +73916,7 @@
         <v>45799</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73994,7 +73994,7 @@
         <v>45799</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74072,7 +74072,7 @@
         <v>45799</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74150,7 +74150,7 @@
         <v>45086</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74228,7 +74228,7 @@
         <v>46309</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74301,7 +74301,7 @@
         <v>45608</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74374,7 +74374,7 @@
         <v>45341</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74447,7 +74447,7 @@
         <v>45744</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74520,7 +74520,7 @@
         <v>46309</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74593,7 +74593,7 @@
         <v>46309</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74666,7 +74666,7 @@
         <v>45809</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74744,7 +74744,7 @@
         <v>45215</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74817,7 +74817,7 @@
         <v>46266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74895,7 +74895,7 @@
         <v>45453</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74973,7 +74973,7 @@
         <v>45511</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75046,7 +75046,7 @@
         <v>45812</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75119,7 +75119,7 @@
         <v>46311</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75192,7 +75192,7 @@
         <v>45721</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75265,7 +75265,7 @@
         <v>45817</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75338,7 +75338,7 @@
         <v>46267</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75411,7 +75411,7 @@
         <v>46265</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75489,7 +75489,7 @@
         <v>45817</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75567,7 +75567,7 @@
         <v>46267</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75645,7 +75645,7 @@
         <v>46311</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75718,7 +75718,7 @@
         <v>46311</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75791,7 +75791,7 @@
         <v>45821</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75864,7 +75864,7 @@
         <v>45821</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75937,7 +75937,7 @@
         <v>45831</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76010,7 +76010,7 @@
         <v>45831</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76088,7 +76088,7 @@
         <v>45831</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76166,7 +76166,7 @@
         <v>45831</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76239,7 +76239,7 @@
         <v>45832</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76317,7 +76317,7 @@
         <v>45832</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76395,7 +76395,7 @@
         <v>45821</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76468,7 +76468,7 @@
         <v>45840</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76541,7 +76541,7 @@
         <v>45679</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76614,7 +76614,7 @@
         <v>45763</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76687,7 +76687,7 @@
         <v>45644</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76760,7 +76760,7 @@
         <v>45426</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76833,7 +76833,7 @@
         <v>45852</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76911,7 +76911,7 @@
         <v>45852</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76989,7 +76989,7 @@
         <v>45852</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77062,7 +77062,7 @@
         <v>45856</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77140,7 +77140,7 @@
         <v>45349</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77213,7 +77213,7 @@
         <v>45831</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77286,7 +77286,7 @@
         <v>45874</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77359,7 +77359,7 @@
         <v>45881</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77432,7 +77432,7 @@
         <v>44602</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77510,7 +77510,7 @@
         <v>44606</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77588,7 +77588,7 @@
         <v>45315</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77666,7 +77666,7 @@
         <v>45173</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77739,7 +77739,7 @@
         <v>44985</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77812,7 +77812,7 @@
         <v>45398</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77890,7 +77890,7 @@
         <v>44645</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77968,7 +77968,7 @@
         <v>44609</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78046,7 +78046,7 @@
         <v>44623</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78124,7 +78124,7 @@
         <v>46086</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78197,7 +78197,7 @@
         <v>46093</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -78270,7 +78270,7 @@
         <v>46089</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -78348,7 +78348,7 @@
         <v>46089</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -78426,7 +78426,7 @@
         <v>46129</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44659</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>46289</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>15.4</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
         <v>9</v>
@@ -1432,13 +1432,13 @@
         <v>3</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="U7" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
@@ -1470,7 +1470,9 @@
 Mattlummer
 Spillkråka
 Tjäder
+Tofsmes
 Vanlig padda
+Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1531,7 +1533,7 @@
         <v>45827</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1671,7 +1673,7 @@
         <v>44792</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1812,7 +1814,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1950,7 +1952,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2088,7 +2090,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2224,7 +2226,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2359,7 +2361,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2495,7 +2497,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2625,7 +2627,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2760,7 +2762,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2898,7 +2900,7 @@
         <v>46121</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3026,7 +3028,7 @@
         <v>45853</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3150,7 +3152,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3278,7 +3280,7 @@
         <v>46009</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3405,7 +3407,7 @@
         <v>46246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3537,7 +3539,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3664,7 +3666,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3790,7 +3792,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3916,7 +3918,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4042,7 +4044,7 @@
         <v>45715</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4176,7 +4178,7 @@
         <v>46155</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4306,7 +4308,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4435,7 +4437,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4569,7 +4571,7 @@
         <v>45728</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4703,7 +4705,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4833,7 +4835,7 @@
         <v>46303</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4962,7 +4964,7 @@
         <v>46099</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5095,7 +5097,7 @@
         <v>46303</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5220,7 +5222,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5343,7 +5345,7 @@
         <v>46234</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5470,7 +5472,7 @@
         <v>46268</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5598,7 +5600,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5720,7 +5722,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5842,7 +5844,7 @@
         <v>46199</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5968,7 +5970,7 @@
         <v>45086</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6090,7 +6092,7 @@
         <v>45316</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6216,7 +6218,7 @@
         <v>45803</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6346,7 +6348,7 @@
         <v>44532</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6467,7 +6469,7 @@
         <v>45442</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6593,7 +6595,7 @@
         <v>44575</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6713,7 +6715,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6837,7 +6839,7 @@
         <v>45196</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6957,7 +6959,7 @@
         <v>45202</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7086,7 +7088,7 @@
         <v>45442</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7206,7 +7208,7 @@
         <v>44726</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7335,7 +7337,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7459,7 +7461,7 @@
         <v>46163</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7578,7 +7580,7 @@
         <v>45803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7706,7 +7708,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7829,7 +7831,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7948,7 +7950,7 @@
         <v>45715</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8067,7 +8069,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8186,7 +8188,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8308,7 +8310,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8435,7 +8437,7 @@
         <v>46100</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8549,7 +8551,7 @@
         <v>46171</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8676,7 +8678,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8798,7 +8800,7 @@
         <v>45358</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8925,7 +8927,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9043,7 +9045,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9161,7 +9163,7 @@
         <v>44740</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9274,7 +9276,7 @@
         <v>46181</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9392,7 +9394,7 @@
         <v>46198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9509,7 +9511,7 @@
         <v>45803</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9635,7 +9637,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9756,7 +9758,7 @@
         <v>45989</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9877,7 +9879,7 @@
         <v>44574</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9993,7 +9995,7 @@
         <v>45985</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10113,7 +10115,7 @@
         <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10228,7 +10230,7 @@
         <v>46055</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10352,7 +10354,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10467,7 +10469,7 @@
         <v>45985</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10586,7 +10588,7 @@
         <v>46234</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10705,7 +10707,7 @@
         <v>46207</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10820,7 +10822,7 @@
         <v>45688</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10931,7 +10933,7 @@
         <v>44791</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11041,7 +11043,7 @@
         <v>44614</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11151,7 +11153,7 @@
         <v>45097</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11265,7 +11267,7 @@
         <v>44966</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11380,7 +11382,7 @@
         <v>44974</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11494,7 +11496,7 @@
         <v>46155</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11617,7 +11619,7 @@
         <v>44720</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11726,7 +11728,7 @@
         <v>45107</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11835,7 +11837,7 @@
         <v>45721</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11944,7 +11946,7 @@
         <v>46009</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12057,7 +12059,7 @@
         <v>45909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12175,7 +12177,7 @@
         <v>45961</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12292,7 +12294,7 @@
         <v>45961</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12409,7 +12411,7 @@
         <v>46167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12523,7 +12525,7 @@
         <v>45820</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12632,7 +12634,7 @@
         <v>45994</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12750,7 +12752,7 @@
         <v>44610</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12867,7 +12869,7 @@
         <v>44719</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12975,7 +12977,7 @@
         <v>44664</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13083,7 +13085,7 @@
         <v>44886</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13191,7 +13193,7 @@
         <v>45726</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13299,7 +13301,7 @@
         <v>44855</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13412,7 +13414,7 @@
         <v>44495</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13520,7 +13522,7 @@
         <v>45167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13632,7 +13634,7 @@
         <v>45905</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13745,7 +13747,7 @@
         <v>45905</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13858,7 +13860,7 @@
         <v>46155</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13979,7 +13981,7 @@
         <v>46001</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14092,7 +14094,7 @@
         <v>46037</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14209,7 +14211,7 @@
         <v>45985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14321,7 +14323,7 @@
         <v>45371</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14434,7 +14436,7 @@
         <v>46003</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14550,7 +14552,7 @@
         <v>44588</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14667,7 +14669,7 @@
         <v>44516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14774,7 +14776,7 @@
         <v>45831</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14889,7 +14891,7 @@
         <v>45035</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -15005,7 +15007,7 @@
         <v>44804</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15112,7 +15114,7 @@
         <v>46093</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15219,7 +15221,7 @@
         <v>46191</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15326,7 +15328,7 @@
         <v>44897</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15437,7 +15439,7 @@
         <v>45293</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15544,7 +15546,7 @@
         <v>46234</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15655,7 +15657,7 @@
         <v>46234</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15766,7 +15768,7 @@
         <v>45273</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15877,7 +15879,7 @@
         <v>45090</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15993,7 +15995,7 @@
         <v>45687</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16104,7 +16106,7 @@
         <v>45803</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16216,7 +16218,7 @@
         <v>46311</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16323,7 +16325,7 @@
         <v>45679</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16435,7 +16437,7 @@
         <v>44489</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16546,7 +16548,7 @@
         <v>44984</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16653,7 +16655,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16759,7 +16761,7 @@
         <v>44967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16865,7 +16867,7 @@
         <v>45665</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16975,7 +16977,7 @@
         <v>45694</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17081,7 +17083,7 @@
         <v>44967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17191,7 +17193,7 @@
         <v>45464</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17297,7 +17299,7 @@
         <v>45947</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17408,7 +17410,7 @@
         <v>44963</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17514,7 +17516,7 @@
         <v>44849</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17620,7 +17622,7 @@
         <v>45960</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17730,7 +17732,7 @@
         <v>45904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17836,7 +17838,7 @@
         <v>45168</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17951,7 +17953,7 @@
         <v>45776</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18057,7 +18059,7 @@
         <v>45429</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18167,7 +18169,7 @@
         <v>46267</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18278,7 +18280,7 @@
         <v>45189</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18392,7 +18394,7 @@
         <v>44630</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18502,7 +18504,7 @@
         <v>45965</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18612,7 +18614,7 @@
         <v>44714</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18721,7 +18723,7 @@
         <v>44651</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18831,7 +18833,7 @@
         <v>44543</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18941,7 +18943,7 @@
         <v>44517</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19046,7 +19048,7 @@
         <v>44487</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19151,7 +19153,7 @@
         <v>45107</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19261,7 +19263,7 @@
         <v>44594</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19366,7 +19368,7 @@
         <v>44917</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19476,7 +19478,7 @@
         <v>44958</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19581,7 +19583,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19686,7 +19688,7 @@
         <v>45173</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19791,7 +19793,7 @@
         <v>45121</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19901,7 +19903,7 @@
         <v>45896</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20011,7 +20013,7 @@
         <v>45190</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20116,7 +20118,7 @@
         <v>45916</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20226,7 +20228,7 @@
         <v>46147</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20331,7 +20333,7 @@
         <v>45638</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20436,7 +20438,7 @@
         <v>44909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20545,7 +20547,7 @@
         <v>46153</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20650,7 +20652,7 @@
         <v>45938</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20760,7 +20762,7 @@
         <v>45950</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20865,7 +20867,7 @@
         <v>45645</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20975,7 +20977,7 @@
         <v>46160</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21080,7 +21082,7 @@
         <v>45385</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21185,7 +21187,7 @@
         <v>45316</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21299,7 +21301,7 @@
         <v>44645</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21409,7 +21411,7 @@
         <v>46009</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21523,7 +21525,7 @@
         <v>46178</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21628,7 +21630,7 @@
         <v>46069</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21738,7 +21740,7 @@
         <v>44847</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21843,7 +21845,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21952,7 +21954,7 @@
         <v>46106</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22057,7 +22059,7 @@
         <v>45314</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22162,7 +22164,7 @@
         <v>44831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22267,7 +22269,7 @@
         <v>44574</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22372,7 +22374,7 @@
         <v>44673</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22481,7 +22483,7 @@
         <v>46212</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22591,7 +22593,7 @@
         <v>45442</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22696,7 +22698,7 @@
         <v>46274</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22810,7 +22812,7 @@
         <v>46275</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22915,7 +22917,7 @@
         <v>46274</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23029,7 +23031,7 @@
         <v>45181</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23134,7 +23136,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23248,7 +23250,7 @@
         <v>44894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23358,7 +23360,7 @@
         <v>44980</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23467,7 +23469,7 @@
         <v>45173</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23572,7 +23574,7 @@
         <v>45583</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23686,7 +23688,7 @@
         <v>46141</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23791,7 +23793,7 @@
         <v>46141</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23896,7 +23898,7 @@
         <v>45757</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24001,7 +24003,7 @@
         <v>44917</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24111,7 +24113,7 @@
         <v>46280</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24216,7 +24218,7 @@
         <v>45335</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24326,7 +24328,7 @@
         <v>46261</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24436,7 +24438,7 @@
         <v>45098</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24541,7 +24543,7 @@
         <v>45736</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24651,7 +24653,7 @@
         <v>44630</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24756,7 +24758,7 @@
         <v>44678</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24870,7 +24872,7 @@
         <v>44984</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24975,7 +24977,7 @@
         <v>45994</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25085,7 +25087,7 @@
         <v>45994</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25195,7 +25197,7 @@
         <v>44583</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25273,7 +25275,7 @@
         <v>44602</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25346,7 +25348,7 @@
         <v>44602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25419,7 +25421,7 @@
         <v>44567</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25497,7 +25499,7 @@
         <v>44517</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25570,7 +25572,7 @@
         <v>44544</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25643,7 +25645,7 @@
         <v>44526</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25721,7 +25723,7 @@
         <v>44489</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25794,7 +25796,7 @@
         <v>44609</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25867,7 +25869,7 @@
         <v>44491</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25945,7 +25947,7 @@
         <v>44662</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -26023,7 +26025,7 @@
         <v>44569</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26101,7 +26103,7 @@
         <v>44486</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26174,7 +26176,7 @@
         <v>44572</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26252,7 +26254,7 @@
         <v>44659</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26325,7 +26327,7 @@
         <v>44494</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26403,7 +26405,7 @@
         <v>44603</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26476,7 +26478,7 @@
         <v>44700</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26549,7 +26551,7 @@
         <v>44839</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26622,7 +26624,7 @@
         <v>44784</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26695,7 +26697,7 @@
         <v>44612</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26768,7 +26770,7 @@
         <v>44886</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26846,7 +26848,7 @@
         <v>44883</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26924,7 +26926,7 @@
         <v>44598</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26997,7 +26999,7 @@
         <v>44610</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27075,7 +27077,7 @@
         <v>44865</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27148,7 +27150,7 @@
         <v>44704</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27221,7 +27223,7 @@
         <v>44533</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27294,7 +27296,7 @@
         <v>44764</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27372,7 +27374,7 @@
         <v>44609</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27450,7 +27452,7 @@
         <v>44490</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27523,7 +27525,7 @@
         <v>44512</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27596,7 +27598,7 @@
         <v>44740</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27674,7 +27676,7 @@
         <v>44816</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27747,7 +27749,7 @@
         <v>44722</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27825,7 +27827,7 @@
         <v>44705</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27898,7 +27900,7 @@
         <v>44705</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27971,7 +27973,7 @@
         <v>44692</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -28044,7 +28046,7 @@
         <v>44504</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28122,7 +28124,7 @@
         <v>44750</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28195,7 +28197,7 @@
         <v>44643</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28268,7 +28270,7 @@
         <v>44846</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28341,7 +28343,7 @@
         <v>44676</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28414,7 +28416,7 @@
         <v>44491</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28492,7 +28494,7 @@
         <v>44847</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28565,7 +28567,7 @@
         <v>44705</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28638,7 +28640,7 @@
         <v>44799</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28711,7 +28713,7 @@
         <v>44575</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28784,7 +28786,7 @@
         <v>44575</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28862,7 +28864,7 @@
         <v>44702</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28935,7 +28937,7 @@
         <v>44551</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -29008,7 +29010,7 @@
         <v>44571</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29081,7 +29083,7 @@
         <v>44634</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29154,7 +29156,7 @@
         <v>44698</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29232,7 +29234,7 @@
         <v>44599</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29305,7 +29307,7 @@
         <v>44865</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29378,7 +29380,7 @@
         <v>44593</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29451,7 +29453,7 @@
         <v>44543</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29524,7 +29526,7 @@
         <v>44495</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29597,7 +29599,7 @@
         <v>44522</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29670,7 +29672,7 @@
         <v>44847</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29743,7 +29745,7 @@
         <v>44750</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29821,7 +29823,7 @@
         <v>44685</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29899,7 +29901,7 @@
         <v>44733</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29977,7 +29979,7 @@
         <v>44711</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -30055,7 +30057,7 @@
         <v>44743</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30128,7 +30130,7 @@
         <v>44623</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30206,7 +30208,7 @@
         <v>44729</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30279,7 +30281,7 @@
         <v>44791</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30357,7 +30359,7 @@
         <v>44623</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30435,7 +30437,7 @@
         <v>44798</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30508,7 +30510,7 @@
         <v>44659</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30586,7 +30588,7 @@
         <v>44659</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30664,7 +30666,7 @@
         <v>44593</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30742,7 +30744,7 @@
         <v>44593</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30820,7 +30822,7 @@
         <v>45678</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30893,7 +30895,7 @@
         <v>44893</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30966,7 +30968,7 @@
         <v>45091</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -31039,7 +31041,7 @@
         <v>44581</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31117,7 +31119,7 @@
         <v>45695</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31195,7 +31197,7 @@
         <v>44637</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31268,7 +31270,7 @@
         <v>45615</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31341,7 +31343,7 @@
         <v>44637</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31419,7 +31421,7 @@
         <v>44599</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31492,7 +31494,7 @@
         <v>44519</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31565,7 +31567,7 @@
         <v>44608</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31638,7 +31640,7 @@
         <v>44993</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31711,7 +31713,7 @@
         <v>45756</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31784,7 +31786,7 @@
         <v>44816</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31862,7 +31864,7 @@
         <v>45694</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31935,7 +31937,7 @@
         <v>45351</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -32013,7 +32015,7 @@
         <v>44967</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32086,7 +32088,7 @@
         <v>44900</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32159,7 +32161,7 @@
         <v>44872</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32232,7 +32234,7 @@
         <v>45212</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32305,7 +32307,7 @@
         <v>44532</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32378,7 +32380,7 @@
         <v>44944</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32451,7 +32453,7 @@
         <v>45093</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32529,7 +32531,7 @@
         <v>45169</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32607,7 +32609,7 @@
         <v>44980</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32680,7 +32682,7 @@
         <v>45216</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32753,7 +32755,7 @@
         <v>45552</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32826,7 +32828,7 @@
         <v>45244</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32904,7 +32906,7 @@
         <v>45327</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32977,7 +32979,7 @@
         <v>44960</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33050,7 +33052,7 @@
         <v>45425</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33123,7 +33125,7 @@
         <v>45295</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33201,7 +33203,7 @@
         <v>44969</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33274,7 +33276,7 @@
         <v>44809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33347,7 +33349,7 @@
         <v>45369</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33420,7 +33422,7 @@
         <v>45733</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33493,7 +33495,7 @@
         <v>45363</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33571,7 +33573,7 @@
         <v>44617</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33644,7 +33646,7 @@
         <v>45107</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33717,7 +33719,7 @@
         <v>45107</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33790,7 +33792,7 @@
         <v>45300</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33863,7 +33865,7 @@
         <v>44949</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33936,7 +33938,7 @@
         <v>45149</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -34014,7 +34016,7 @@
         <v>44548</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34087,7 +34089,7 @@
         <v>45033</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34160,7 +34162,7 @@
         <v>45078</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34238,7 +34240,7 @@
         <v>44616</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34311,7 +34313,7 @@
         <v>45182</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34384,7 +34386,7 @@
         <v>45055</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34457,7 +34459,7 @@
         <v>44912</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34530,7 +34532,7 @@
         <v>45407</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34603,7 +34605,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34676,7 +34678,7 @@
         <v>44512</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34749,7 +34751,7 @@
         <v>45097</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34822,7 +34824,7 @@
         <v>44904</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34900,7 +34902,7 @@
         <v>44819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34978,7 +34980,7 @@
         <v>44883</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35051,7 +35053,7 @@
         <v>44600</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35129,7 +35131,7 @@
         <v>45694</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35202,7 +35204,7 @@
         <v>44806</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35275,7 +35277,7 @@
         <v>45236</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35348,7 +35350,7 @@
         <v>44799</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35421,7 +35423,7 @@
         <v>45338</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35494,7 +35496,7 @@
         <v>45164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35572,7 +35574,7 @@
         <v>45208</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35645,7 +35647,7 @@
         <v>45065</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35718,7 +35720,7 @@
         <v>45202</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35796,7 +35798,7 @@
         <v>44602</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35869,7 +35871,7 @@
         <v>44503</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35942,7 +35944,7 @@
         <v>45182</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -36015,7 +36017,7 @@
         <v>45699</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36088,7 +36090,7 @@
         <v>44967</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36161,7 +36163,7 @@
         <v>45188</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36239,7 +36241,7 @@
         <v>45000</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36312,7 +36314,7 @@
         <v>45177</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36385,7 +36387,7 @@
         <v>44699</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36463,7 +36465,7 @@
         <v>45300</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36536,7 +36538,7 @@
         <v>45188</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36609,7 +36611,7 @@
         <v>45208</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36682,7 +36684,7 @@
         <v>45721</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36755,7 +36757,7 @@
         <v>45194</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36833,7 +36835,7 @@
         <v>45231</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36906,7 +36908,7 @@
         <v>44886</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36979,7 +36981,7 @@
         <v>45520</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37052,7 +37054,7 @@
         <v>45201</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37125,7 +37127,7 @@
         <v>44810</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37198,7 +37200,7 @@
         <v>45729</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37271,7 +37273,7 @@
         <v>45882</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37344,7 +37346,7 @@
         <v>45939</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37417,7 +37419,7 @@
         <v>45966</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37495,7 +37497,7 @@
         <v>45699</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37568,7 +37570,7 @@
         <v>45940</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37641,7 +37643,7 @@
         <v>45391</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37714,7 +37716,7 @@
         <v>44832</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37787,7 +37789,7 @@
         <v>44593</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37865,7 +37867,7 @@
         <v>45317</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37938,7 +37940,7 @@
         <v>45839</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38011,7 +38013,7 @@
         <v>45695</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38089,7 +38091,7 @@
         <v>45763</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38162,7 +38164,7 @@
         <v>44935</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38235,7 +38237,7 @@
         <v>45216</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38308,7 +38310,7 @@
         <v>46051</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38386,7 +38388,7 @@
         <v>44678</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38464,7 +38466,7 @@
         <v>45769</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38537,7 +38539,7 @@
         <v>44501</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38615,7 +38617,7 @@
         <v>44588</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38688,7 +38690,7 @@
         <v>45259</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38761,7 +38763,7 @@
         <v>45231</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38834,7 +38836,7 @@
         <v>45705</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38907,7 +38909,7 @@
         <v>45259</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38985,7 +38987,7 @@
         <v>45890</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39063,7 +39065,7 @@
         <v>45882</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39136,7 +39138,7 @@
         <v>45390</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39209,7 +39211,7 @@
         <v>45852</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39287,7 +39289,7 @@
         <v>45054</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39360,7 +39362,7 @@
         <v>45863</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39433,7 +39435,7 @@
         <v>44575</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39506,7 +39508,7 @@
         <v>44994</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39579,7 +39581,7 @@
         <v>44679</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39657,7 +39659,7 @@
         <v>44733</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39730,7 +39732,7 @@
         <v>45691</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39803,7 +39805,7 @@
         <v>45293</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39876,7 +39878,7 @@
         <v>45838</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39949,7 +39951,7 @@
         <v>46141</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40027,7 +40029,7 @@
         <v>45903</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40105,7 +40107,7 @@
         <v>45905</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40178,7 +40180,7 @@
         <v>45049</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40251,7 +40253,7 @@
         <v>45202</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40329,7 +40331,7 @@
         <v>45259</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40407,7 +40409,7 @@
         <v>45867</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40480,7 +40482,7 @@
         <v>45912</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40558,7 +40560,7 @@
         <v>45915</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40636,7 +40638,7 @@
         <v>45267</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40714,7 +40716,7 @@
         <v>45916</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40787,7 +40789,7 @@
         <v>45918</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40860,7 +40862,7 @@
         <v>45758</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40933,7 +40935,7 @@
         <v>45922</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41006,7 +41008,7 @@
         <v>45923</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41084,7 +41086,7 @@
         <v>45923</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41162,7 +41164,7 @@
         <v>46146</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41235,7 +41237,7 @@
         <v>45113</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41308,7 +41310,7 @@
         <v>44964</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41381,7 +41383,7 @@
         <v>45926</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41459,7 +41461,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41532,7 +41534,7 @@
         <v>45926</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41610,7 +41612,7 @@
         <v>45926</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41688,7 +41690,7 @@
         <v>45929</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41766,7 +41768,7 @@
         <v>45929</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41844,7 +41846,7 @@
         <v>45113</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41917,7 +41919,7 @@
         <v>45926</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41995,7 +41997,7 @@
         <v>45926</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42073,7 +42075,7 @@
         <v>45926</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42151,7 +42153,7 @@
         <v>45931</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42229,7 +42231,7 @@
         <v>44788</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42302,7 +42304,7 @@
         <v>45098</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42375,7 +42377,7 @@
         <v>45931</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42453,7 +42455,7 @@
         <v>45932</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42526,7 +42528,7 @@
         <v>45932</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42604,7 +42606,7 @@
         <v>45932</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42682,7 +42684,7 @@
         <v>45361</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42760,7 +42762,7 @@
         <v>45938</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42838,7 +42840,7 @@
         <v>45937</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42911,7 +42913,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42984,7 +42986,7 @@
         <v>45460</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43062,7 +43064,7 @@
         <v>45763</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43135,7 +43137,7 @@
         <v>45940</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43208,7 +43210,7 @@
         <v>44816</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43281,7 +43283,7 @@
         <v>45308</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43354,7 +43356,7 @@
         <v>45942</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43427,7 +43429,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43500,7 +43502,7 @@
         <v>44535</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43573,7 +43575,7 @@
         <v>45898</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43646,7 +43648,7 @@
         <v>44629</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43724,7 +43726,7 @@
         <v>44608</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43802,7 +43804,7 @@
         <v>44497</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43875,7 +43877,7 @@
         <v>45946</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43948,7 +43950,7 @@
         <v>44946</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -44021,7 +44023,7 @@
         <v>45946</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44094,7 +44096,7 @@
         <v>44965</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44167,7 +44169,7 @@
         <v>44965</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44240,7 +44242,7 @@
         <v>45946</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44313,7 +44315,7 @@
         <v>44679</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44386,7 +44388,7 @@
         <v>45336</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44459,7 +44461,7 @@
         <v>45336</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44532,7 +44534,7 @@
         <v>45950</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44605,7 +44607,7 @@
         <v>45950</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44678,7 +44680,7 @@
         <v>45949</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44751,7 +44753,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44829,7 +44831,7 @@
         <v>45954</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44902,7 +44904,7 @@
         <v>46155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44980,7 +44982,7 @@
         <v>46155</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45058,7 +45060,7 @@
         <v>45954</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45131,7 +45133,7 @@
         <v>45954</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45204,7 +45206,7 @@
         <v>44614</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45282,7 +45284,7 @@
         <v>45958</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45360,7 +45362,7 @@
         <v>45259</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45433,7 +45435,7 @@
         <v>45958</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45511,7 +45513,7 @@
         <v>45958</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45589,7 +45591,7 @@
         <v>45958</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45667,7 +45669,7 @@
         <v>45959</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45745,7 +45747,7 @@
         <v>45958</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45823,7 +45825,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45901,7 +45903,7 @@
         <v>45958</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45979,7 +45981,7 @@
         <v>45589</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -46052,7 +46054,7 @@
         <v>45930</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46125,7 +46127,7 @@
         <v>45961</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46198,7 +46200,7 @@
         <v>46160</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46271,7 +46273,7 @@
         <v>45961</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46344,7 +46346,7 @@
         <v>45965</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46422,7 +46424,7 @@
         <v>45194</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46495,7 +46497,7 @@
         <v>45194</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46573,7 +46575,7 @@
         <v>45599</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46646,7 +46648,7 @@
         <v>46160</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46719,7 +46721,7 @@
         <v>44665</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46797,7 +46799,7 @@
         <v>45345</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46870,7 +46872,7 @@
         <v>46161</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46943,7 +46945,7 @@
         <v>45971</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -47021,7 +47023,7 @@
         <v>45971</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47094,7 +47096,7 @@
         <v>45972</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47167,7 +47169,7 @@
         <v>46112</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47240,7 +47242,7 @@
         <v>45154</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47313,7 +47315,7 @@
         <v>45443</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47391,7 +47393,7 @@
         <v>44599</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47464,7 +47466,7 @@
         <v>45975</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47537,7 +47539,7 @@
         <v>45975</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47615,7 +47617,7 @@
         <v>46163</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47688,7 +47690,7 @@
         <v>46137</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47766,7 +47768,7 @@
         <v>45310</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47839,7 +47841,7 @@
         <v>45327</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47912,7 +47914,7 @@
         <v>46162</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47990,7 +47992,7 @@
         <v>46162</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48068,7 +48070,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48141,7 +48143,7 @@
         <v>45981</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48214,7 +48216,7 @@
         <v>46167</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48287,7 +48289,7 @@
         <v>46167</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48365,7 +48367,7 @@
         <v>45981</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48443,7 +48445,7 @@
         <v>45981</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48516,7 +48518,7 @@
         <v>45981</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48594,7 +48596,7 @@
         <v>45321</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48667,7 +48669,7 @@
         <v>45958</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48745,7 +48747,7 @@
         <v>46167</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48818,7 +48820,7 @@
         <v>45982</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48891,7 +48893,7 @@
         <v>45983</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48964,7 +48966,7 @@
         <v>45554</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -49037,7 +49039,7 @@
         <v>46167</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49110,7 +49112,7 @@
         <v>45677</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49183,7 +49185,7 @@
         <v>45730</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49261,7 +49263,7 @@
         <v>45988</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49339,7 +49341,7 @@
         <v>44593</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49412,7 +49414,7 @@
         <v>45175</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49485,7 +49487,7 @@
         <v>44909</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49563,7 +49565,7 @@
         <v>45729</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49636,7 +49638,7 @@
         <v>45729</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49709,7 +49711,7 @@
         <v>45181</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49782,7 +49784,7 @@
         <v>45992</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49855,7 +49857,7 @@
         <v>45992</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49928,7 +49930,7 @@
         <v>45761</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -50001,7 +50003,7 @@
         <v>45190</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50074,7 +50076,7 @@
         <v>44550</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50152,7 +50154,7 @@
         <v>45995</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50225,7 +50227,7 @@
         <v>45995</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50298,7 +50300,7 @@
         <v>45048</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50371,7 +50373,7 @@
         <v>45107</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50444,7 +50446,7 @@
         <v>45987</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50517,7 +50519,7 @@
         <v>44928</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50595,7 +50597,7 @@
         <v>45061</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50668,7 +50670,7 @@
         <v>45644</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50741,7 +50743,7 @@
         <v>44977</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50814,7 +50816,7 @@
         <v>45167</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50887,7 +50889,7 @@
         <v>45468</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50960,7 +50962,7 @@
         <v>44679</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51038,7 +51040,7 @@
         <v>45119</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51111,7 +51113,7 @@
         <v>44531</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51184,7 +51186,7 @@
         <v>46171</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51257,7 +51259,7 @@
         <v>45981</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51330,7 +51332,7 @@
         <v>45344</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51408,7 +51410,7 @@
         <v>45694</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51481,7 +51483,7 @@
         <v>44508</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51559,7 +51561,7 @@
         <v>44644</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51637,7 +51639,7 @@
         <v>45426</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51710,7 +51712,7 @@
         <v>46013</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51783,7 +51785,7 @@
         <v>46014</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51856,7 +51858,7 @@
         <v>45187</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51934,7 +51936,7 @@
         <v>45222</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -52007,7 +52009,7 @@
         <v>46171</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52085,7 +52087,7 @@
         <v>44531</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52158,7 +52160,7 @@
         <v>46171</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52231,7 +52233,7 @@
         <v>44532</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52304,7 +52306,7 @@
         <v>45968</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52382,7 +52384,7 @@
         <v>44944</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52455,7 +52457,7 @@
         <v>46029</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52528,7 +52530,7 @@
         <v>45161</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52601,7 +52603,7 @@
         <v>45618</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52674,7 +52676,7 @@
         <v>45548</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52747,7 +52749,7 @@
         <v>46030</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52820,7 +52822,7 @@
         <v>46031</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52893,7 +52895,7 @@
         <v>44742</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52971,7 +52973,7 @@
         <v>46030</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53049,7 +53051,7 @@
         <v>44519</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53122,7 +53124,7 @@
         <v>44967</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53195,7 +53197,7 @@
         <v>46176</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53268,7 +53270,7 @@
         <v>45743</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53341,7 +53343,7 @@
         <v>46178</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53414,7 +53416,7 @@
         <v>44568</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53492,7 +53494,7 @@
         <v>45054</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53565,7 +53567,7 @@
         <v>44859</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53638,7 +53640,7 @@
         <v>44832</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53711,7 +53713,7 @@
         <v>45601</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53784,7 +53786,7 @@
         <v>45133</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53857,7 +53859,7 @@
         <v>44645</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53935,7 +53937,7 @@
         <v>45371</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -54013,7 +54015,7 @@
         <v>46051</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54086,7 +54088,7 @@
         <v>46051</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54159,7 +54161,7 @@
         <v>44616</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54237,7 +54239,7 @@
         <v>46055</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54315,7 +54317,7 @@
         <v>46055</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54388,7 +54390,7 @@
         <v>45042</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54461,7 +54463,7 @@
         <v>46181</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54539,7 +54541,7 @@
         <v>45047</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54612,7 +54614,7 @@
         <v>46057</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54685,7 +54687,7 @@
         <v>44624</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54763,7 +54765,7 @@
         <v>46184</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54841,7 +54843,7 @@
         <v>45050</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54914,7 +54916,7 @@
         <v>46062</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54992,7 +54994,7 @@
         <v>46062</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55070,7 +55072,7 @@
         <v>46062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55148,7 +55150,7 @@
         <v>45037</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55226,7 +55228,7 @@
         <v>46062</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55299,7 +55301,7 @@
         <v>46065</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55372,7 +55374,7 @@
         <v>46065</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55445,7 +55447,7 @@
         <v>46064</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55518,7 +55520,7 @@
         <v>45300</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55591,7 +55593,7 @@
         <v>44533</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55664,7 +55666,7 @@
         <v>46188</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55737,7 +55739,7 @@
         <v>45162</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55815,7 +55817,7 @@
         <v>45154</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55888,7 +55890,7 @@
         <v>46188</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55961,7 +55963,7 @@
         <v>44849</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -56034,7 +56036,7 @@
         <v>45677</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56107,7 +56109,7 @@
         <v>45757</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56180,7 +56182,7 @@
         <v>46076</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56258,7 +56260,7 @@
         <v>46188</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56331,7 +56333,7 @@
         <v>44977</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56409,7 +56411,7 @@
         <v>46185</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56482,7 +56484,7 @@
         <v>46188</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56555,7 +56557,7 @@
         <v>46080</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56628,7 +56630,7 @@
         <v>46065</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56701,7 +56703,7 @@
         <v>44993</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56774,7 +56776,7 @@
         <v>46085</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56847,7 +56849,7 @@
         <v>46090</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56920,7 +56922,7 @@
         <v>45068</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56993,7 +56995,7 @@
         <v>46090</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57066,7 +57068,7 @@
         <v>44929</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57139,7 +57141,7 @@
         <v>46091</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57212,7 +57214,7 @@
         <v>46091</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57285,7 +57287,7 @@
         <v>46091</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57358,7 +57360,7 @@
         <v>46091</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57431,7 +57433,7 @@
         <v>46191</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57509,7 +57511,7 @@
         <v>46091</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57582,7 +57584,7 @@
         <v>46091</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57655,7 +57657,7 @@
         <v>46094</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57728,7 +57730,7 @@
         <v>46094</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57801,7 +57803,7 @@
         <v>45601</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57879,7 +57881,7 @@
         <v>46094</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57952,7 +57954,7 @@
         <v>46094</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58025,7 +58027,7 @@
         <v>46191</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58103,7 +58105,7 @@
         <v>46093</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58176,7 +58178,7 @@
         <v>46094</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58249,7 +58251,7 @@
         <v>44544</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58322,7 +58324,7 @@
         <v>46094</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58395,7 +58397,7 @@
         <v>46191</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58473,7 +58475,7 @@
         <v>46191</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58551,7 +58553,7 @@
         <v>45159</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58624,7 +58626,7 @@
         <v>46191</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58697,7 +58699,7 @@
         <v>46097</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58770,7 +58772,7 @@
         <v>46098</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58843,7 +58845,7 @@
         <v>45127</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58916,7 +58918,7 @@
         <v>46195</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -58989,7 +58991,7 @@
         <v>45216</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59067,7 +59069,7 @@
         <v>45614</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59145,7 +59147,7 @@
         <v>45145</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59218,7 +59220,7 @@
         <v>44551</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59296,7 +59298,7 @@
         <v>46107</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59394,7 +59396,7 @@
         <v>46107</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59467,7 +59469,7 @@
         <v>46107</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59540,7 +59542,7 @@
         <v>46198</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59613,7 +59615,7 @@
         <v>46111</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59686,7 +59688,7 @@
         <v>46111</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59759,7 +59761,7 @@
         <v>46111</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59832,7 +59834,7 @@
         <v>46198</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59910,7 +59912,7 @@
         <v>45236</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59983,7 +59985,7 @@
         <v>45341</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60061,7 +60063,7 @@
         <v>46114</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60139,7 +60141,7 @@
         <v>45006</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60212,7 +60214,7 @@
         <v>45202</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60285,7 +60287,7 @@
         <v>44946</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60358,7 +60360,7 @@
         <v>46119</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60431,7 +60433,7 @@
         <v>46119</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60504,7 +60506,7 @@
         <v>46122</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60577,7 +60579,7 @@
         <v>46199</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60655,7 +60657,7 @@
         <v>44522</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60728,7 +60730,7 @@
         <v>45581</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60801,7 +60803,7 @@
         <v>44593</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60879,7 +60881,7 @@
         <v>45299</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60952,7 +60954,7 @@
         <v>46202</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61025,7 +61027,7 @@
         <v>46202</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61098,7 +61100,7 @@
         <v>45307</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61171,7 +61173,7 @@
         <v>45351</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61244,7 +61246,7 @@
         <v>45371</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61322,7 +61324,7 @@
         <v>46133</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61395,7 +61397,7 @@
         <v>46132</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61473,7 +61475,7 @@
         <v>46132</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61551,7 +61553,7 @@
         <v>46132</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61624,7 +61626,7 @@
         <v>46132</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61702,7 +61704,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61780,7 +61782,7 @@
         <v>44908</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61853,7 +61855,7 @@
         <v>45163</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61926,7 +61928,7 @@
         <v>45181</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -62004,7 +62006,7 @@
         <v>46135</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62077,7 +62079,7 @@
         <v>45134</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62155,7 +62157,7 @@
         <v>44866</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62228,7 +62230,7 @@
         <v>45152</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62301,7 +62303,7 @@
         <v>45901</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62379,7 +62381,7 @@
         <v>45456</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62452,7 +62454,7 @@
         <v>45942</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62525,7 +62527,7 @@
         <v>45876</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62598,7 +62600,7 @@
         <v>45341</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62671,7 +62673,7 @@
         <v>45446</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62749,7 +62751,7 @@
         <v>45880</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62822,7 +62824,7 @@
         <v>45524</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62900,7 +62902,7 @@
         <v>46206</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62973,7 +62975,7 @@
         <v>45757</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63046,7 +63048,7 @@
         <v>46206</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63124,7 +63126,7 @@
         <v>46206</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63202,7 +63204,7 @@
         <v>46206</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63280,7 +63282,7 @@
         <v>45344</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63358,7 +63360,7 @@
         <v>44817</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63431,7 +63433,7 @@
         <v>44629</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63504,7 +63506,7 @@
         <v>45958</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63582,7 +63584,7 @@
         <v>45096</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63655,7 +63657,7 @@
         <v>45580</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63728,7 +63730,7 @@
         <v>45757</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63801,7 +63803,7 @@
         <v>44560</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63874,7 +63876,7 @@
         <v>44594</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63947,7 +63949,7 @@
         <v>45426</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64020,7 +64022,7 @@
         <v>44912</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64093,7 +64095,7 @@
         <v>44967</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64166,7 +64168,7 @@
         <v>46217</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64239,7 +64241,7 @@
         <v>46218</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64317,7 +64319,7 @@
         <v>44614</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64390,7 +64392,7 @@
         <v>44930</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64463,7 +64465,7 @@
         <v>45254</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64536,7 +64538,7 @@
         <v>45098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64609,7 +64611,7 @@
         <v>45014</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64682,7 +64684,7 @@
         <v>45474</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64755,7 +64757,7 @@
         <v>46205</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64828,7 +64830,7 @@
         <v>45194</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64906,7 +64908,7 @@
         <v>46224</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -64984,7 +64986,7 @@
         <v>44819</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65057,7 +65059,7 @@
         <v>46202</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65130,7 +65132,7 @@
         <v>45341</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65208,7 +65210,7 @@
         <v>45254</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65281,7 +65283,7 @@
         <v>46272</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65354,7 +65356,7 @@
         <v>46275</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65432,7 +65434,7 @@
         <v>46273</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65510,7 +65512,7 @@
         <v>44914</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65583,7 +65585,7 @@
         <v>46274</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65661,7 +65663,7 @@
         <v>44984</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65739,7 +65741,7 @@
         <v>46274</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65817,7 +65819,7 @@
         <v>45524</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65895,7 +65897,7 @@
         <v>44623</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65973,7 +65975,7 @@
         <v>44960</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66046,7 +66048,7 @@
         <v>44960</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66119,7 +66121,7 @@
         <v>44532</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66192,7 +66194,7 @@
         <v>44820</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66270,7 +66272,7 @@
         <v>46276</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66348,7 +66350,7 @@
         <v>46276</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66426,7 +66428,7 @@
         <v>45352</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66499,7 +66501,7 @@
         <v>46281</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66577,7 +66579,7 @@
         <v>45358</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66650,7 +66652,7 @@
         <v>46234</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66723,7 +66725,7 @@
         <v>44944</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66796,7 +66798,7 @@
         <v>44504</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66869,7 +66871,7 @@
         <v>46237</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66947,7 +66949,7 @@
         <v>45225</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67020,7 +67022,7 @@
         <v>46237</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67098,7 +67100,7 @@
         <v>44603</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67171,7 +67173,7 @@
         <v>45513</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67249,7 +67251,7 @@
         <v>44848</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67322,7 +67324,7 @@
         <v>45379</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67395,7 +67397,7 @@
         <v>45323</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67473,7 +67475,7 @@
         <v>46283</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67546,7 +67548,7 @@
         <v>46240</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67619,7 +67621,7 @@
         <v>44588</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67692,7 +67694,7 @@
         <v>44883</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67770,7 +67772,7 @@
         <v>44553</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67843,7 +67845,7 @@
         <v>45096</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67916,7 +67918,7 @@
         <v>45148</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67989,7 +67991,7 @@
         <v>45104</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68062,7 +68064,7 @@
         <v>45478</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68140,7 +68142,7 @@
         <v>45096</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68213,7 +68215,7 @@
         <v>44977</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68286,7 +68288,7 @@
         <v>45231</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68359,7 +68361,7 @@
         <v>44609</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68437,7 +68439,7 @@
         <v>44888</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68515,7 +68517,7 @@
         <v>45110</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68588,7 +68590,7 @@
         <v>44623</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68666,7 +68668,7 @@
         <v>45644</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68739,7 +68741,7 @@
         <v>45075</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68812,7 +68814,7 @@
         <v>45148</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68885,7 +68887,7 @@
         <v>45148</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68958,7 +68960,7 @@
         <v>45182</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69031,7 +69033,7 @@
         <v>45266</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69104,7 +69106,7 @@
         <v>45089</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69177,7 +69179,7 @@
         <v>44652</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69250,7 +69252,7 @@
         <v>45694</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69323,7 +69325,7 @@
         <v>44624</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69401,7 +69403,7 @@
         <v>45685</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69474,7 +69476,7 @@
         <v>46290</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69547,7 +69549,7 @@
         <v>45097</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69620,7 +69622,7 @@
         <v>45435</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69698,7 +69700,7 @@
         <v>45317</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69771,7 +69773,7 @@
         <v>45180</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69849,7 +69851,7 @@
         <v>46251</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69927,7 +69929,7 @@
         <v>45611</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -70000,7 +70002,7 @@
         <v>46251</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70078,7 +70080,7 @@
         <v>46251</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70156,7 +70158,7 @@
         <v>45049</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70229,7 +70231,7 @@
         <v>45254</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70302,7 +70304,7 @@
         <v>45344</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70380,7 +70382,7 @@
         <v>45762</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70453,7 +70455,7 @@
         <v>44610</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70531,7 +70533,7 @@
         <v>46251</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70609,7 +70611,7 @@
         <v>46254</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70682,7 +70684,7 @@
         <v>46258</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70755,7 +70757,7 @@
         <v>45453</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70828,7 +70830,7 @@
         <v>45638</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70901,7 +70903,7 @@
         <v>45520</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70974,7 +70976,7 @@
         <v>45107</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71047,7 +71049,7 @@
         <v>45574</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71120,7 +71122,7 @@
         <v>46300</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71193,7 +71195,7 @@
         <v>45779</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71271,7 +71273,7 @@
         <v>46300</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71344,7 +71346,7 @@
         <v>46300</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71417,7 +71419,7 @@
         <v>45558</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71490,7 +71492,7 @@
         <v>44569</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71568,7 +71570,7 @@
         <v>45254</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71641,7 +71643,7 @@
         <v>45368</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71719,7 +71721,7 @@
         <v>46140</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71797,7 +71799,7 @@
         <v>45584</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71870,7 +71872,7 @@
         <v>46160</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71948,7 +71950,7 @@
         <v>46259</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -72021,7 +72023,7 @@
         <v>45091</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72099,7 +72101,7 @@
         <v>45371</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72172,7 +72174,7 @@
         <v>45684</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72245,7 +72247,7 @@
         <v>45562</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72318,7 +72320,7 @@
         <v>45177</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72396,7 +72398,7 @@
         <v>45329</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72469,7 +72471,7 @@
         <v>44569</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72547,7 +72549,7 @@
         <v>45583</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72625,7 +72627,7 @@
         <v>46260</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72703,7 +72705,7 @@
         <v>46303</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72781,7 +72783,7 @@
         <v>46302</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72854,7 +72856,7 @@
         <v>46303</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72932,7 +72934,7 @@
         <v>45490</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -73005,7 +73007,7 @@
         <v>46303</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73083,7 +73085,7 @@
         <v>45195</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73156,7 +73158,7 @@
         <v>46272</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73229,7 +73231,7 @@
         <v>46261</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73307,7 +73309,7 @@
         <v>46273</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73385,7 +73387,7 @@
         <v>45439</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73463,7 +73465,7 @@
         <v>45943</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73541,7 +73543,7 @@
         <v>45636</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73614,7 +73616,7 @@
         <v>45525</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73687,7 +73689,7 @@
         <v>45947</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73765,7 +73767,7 @@
         <v>46172</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73843,7 +73845,7 @@
         <v>45733</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73916,7 +73918,7 @@
         <v>45799</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73994,7 +73996,7 @@
         <v>45799</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74072,7 +74074,7 @@
         <v>45799</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74150,7 +74152,7 @@
         <v>45086</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74228,7 +74230,7 @@
         <v>46309</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74301,7 +74303,7 @@
         <v>45608</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74374,7 +74376,7 @@
         <v>45341</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74447,7 +74449,7 @@
         <v>45744</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74520,7 +74522,7 @@
         <v>46309</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74593,7 +74595,7 @@
         <v>46309</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74666,7 +74668,7 @@
         <v>45809</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74744,7 +74746,7 @@
         <v>45215</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74817,7 +74819,7 @@
         <v>46266</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74895,7 +74897,7 @@
         <v>45453</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74973,7 +74975,7 @@
         <v>45511</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -75046,7 +75048,7 @@
         <v>45812</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75119,7 +75121,7 @@
         <v>46311</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75192,7 +75194,7 @@
         <v>45721</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75265,7 +75267,7 @@
         <v>45817</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75338,7 +75340,7 @@
         <v>46267</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75411,7 +75413,7 @@
         <v>46265</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75489,7 +75491,7 @@
         <v>45817</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75567,7 +75569,7 @@
         <v>46267</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75645,7 +75647,7 @@
         <v>46311</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75718,7 +75720,7 @@
         <v>46311</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75791,7 +75793,7 @@
         <v>45821</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75864,7 +75866,7 @@
         <v>45821</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75937,7 +75939,7 @@
         <v>45831</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -76010,7 +76012,7 @@
         <v>45831</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76088,7 +76090,7 @@
         <v>45831</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76166,7 +76168,7 @@
         <v>45831</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76239,7 +76241,7 @@
         <v>45832</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76317,7 +76319,7 @@
         <v>45832</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76395,7 +76397,7 @@
         <v>45821</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76468,7 +76470,7 @@
         <v>45840</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76541,7 +76543,7 @@
         <v>45679</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76614,7 +76616,7 @@
         <v>45763</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76687,7 +76689,7 @@
         <v>45644</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76760,7 +76762,7 @@
         <v>45426</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76833,7 +76835,7 @@
         <v>45852</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76911,7 +76913,7 @@
         <v>45852</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76989,7 +76991,7 @@
         <v>45852</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -77062,7 +77064,7 @@
         <v>45856</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77140,7 +77142,7 @@
         <v>45349</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77213,7 +77215,7 @@
         <v>45831</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77286,7 +77288,7 @@
         <v>45874</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77359,7 +77361,7 @@
         <v>45881</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77432,7 +77434,7 @@
         <v>44602</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77510,7 +77512,7 @@
         <v>44606</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77588,7 +77590,7 @@
         <v>45315</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77666,7 +77668,7 @@
         <v>45173</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77739,7 +77741,7 @@
         <v>44985</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77812,7 +77814,7 @@
         <v>45398</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77890,7 +77892,7 @@
         <v>44645</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77968,7 +77970,7 @@
         <v>44609</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -78046,7 +78048,7 @@
         <v>44623</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78124,7 +78126,7 @@
         <v>46086</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78197,7 +78199,7 @@
         <v>46093</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
@@ -78270,7 +78272,7 @@
         <v>46089</v>
       </c>
       <c r="E923" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F923" t="inlineStr">
         <is>
@@ -78348,7 +78350,7 @@
         <v>46089</v>
       </c>
       <c r="E924" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F924" t="inlineStr">
         <is>
@@ -78426,7 +78428,7 @@
         <v>46129</v>
       </c>
       <c r="E925" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F925" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44792</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>45853</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46246</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45728</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46045</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>46303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>46155</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46303</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>46234</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>46199</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45803</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44532</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45316</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45442</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>44575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45196</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44726</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45715</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45736</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>46100</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45358</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>46171</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45989</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45985</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>46055</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45985</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>46234</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44791</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>46155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44720</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45961</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45961</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>46009</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45721</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44610</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44719</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44664</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44886</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45371</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46037</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>46003</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46155</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44855</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45167</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44495</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46191</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45687</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46234</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>46234</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45273</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>46093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>46311</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45035</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44516</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45293</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44963</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45904</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45960</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>45464</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45694</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45776</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45429</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45189</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>44967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45168</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45223</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45665</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44849</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44630</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44714</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44651</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45121</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>46160</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44574</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45938</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44831</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46178</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45385</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>46212</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46009</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44894</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45335</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>46141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46141</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45098</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45736</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>46280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46261</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44673</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46317</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>46275</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46147</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45645</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45442</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45757</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45181</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45173</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>44594</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45173</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45314</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44609</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>44569</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44662</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44572</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44659</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44603</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44494</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44839</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44612</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44886</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>44598</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>44883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44610</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44865</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>44704</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44533</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>44764</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44512</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44740</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44722</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44705</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44705</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44692</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44504</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44750</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44643</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>44846</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44676</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44847</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44705</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44799</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44575</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44575</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44702</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>44551</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44698</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44599</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>44865</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44593</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44543</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44495</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44522</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44847</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44750</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44685</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44733</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44711</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44743</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>44623</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44729</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44593</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>44928</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44593</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45839</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44819</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44616</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44560</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44600</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45371</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45212</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>44886</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45208</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>44859</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44832</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44742</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44883</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45903</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45341</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45905</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>46161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>46137</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45912</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44969</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46112</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46112</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45915</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44944</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>46162</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45601</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46162</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45154</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44652</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45678</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>44679</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45916</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45918</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46167</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>46167</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45694</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>46167</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44806</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>46167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45923</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45049</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45222</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44645</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44497</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45614</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45926</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45926</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45152</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45644</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45761</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45929</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45929</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>46171</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46171</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45932</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>44599</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45932</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45762</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45937</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45352</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45938</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>44944</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45940</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45259</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45942</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45096</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>44872</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45758</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44809</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>44810</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45898</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44551</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45946</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45513</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45049</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45336</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45946</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45950</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45949</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46178</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45954</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45954</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45954</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45958</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45169</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46185</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45244</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45435</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45958</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45958</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45958</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45958</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45763</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>45958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>46184</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45548</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>46188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44532</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45961</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46191</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44977</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45336</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>46191</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46191</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46191</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45971</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46195</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45972</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45110</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>45194</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45975</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45300</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45589</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>44609</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45975</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46198</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>44503</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>44624</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>46198</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46202</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45729</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45729</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45982</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>46202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45259</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45981</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45327</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45014</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44593</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45981</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45685</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45958</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45460</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45345</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44914</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45061</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44912</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45983</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46206</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>44967</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45075</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46206</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45988</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>46206</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>46206</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45699</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45733</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45426</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>45958</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45992</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45478</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45729</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45644</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45995</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46217</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45307</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45254</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>46218</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45327</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45300</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>44883</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45987</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>44849</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45107</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45520</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45574</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45779</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>46224</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>44569</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>46237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>45329</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45558</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45562</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45368</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>44569</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46237</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45684</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>46013</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>46014</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45968</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45371</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45583</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45584</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>46281</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>46234</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>46030</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>46030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>46240</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46031</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45525</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45636</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45490</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45439</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45799</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45733</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45799</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46290</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45799</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45086</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45744</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>46051</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>45341</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45608</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>46051</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46055</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46055</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45511</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45341</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45215</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>46057</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45809</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45453</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>46062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>46062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45812</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>46062</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>46064</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45721</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46065</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46065</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>45817</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45817</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45341</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>46251</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45821</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45821</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46251</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46251</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>46080</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45831</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45831</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>45832</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46085</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45831</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>45831</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46065</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46090</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>46090</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44935</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>46300</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>46091</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>46091</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>46091</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>46091</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>46093</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45821</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46094</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45840</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>46094</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53901,7 +53901,7 @@
         <v>46094</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53974,7 +53974,7 @@
         <v>46094</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>46251</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>46097</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>46094</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46094</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46254</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>46098</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>44504</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45679</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>44602</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45763</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>46300</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>46300</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>46302</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>46259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45644</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45426</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45852</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45852</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55444,7 +55444,7 @@
         <v>45852</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>46107</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>46107</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55668,7 +55668,7 @@
         <v>46107</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45856</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>46111</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46111</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>44977</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>46111</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>46303</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>46160</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>45349</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46114</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46119</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>46260</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45831</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>44624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>46303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>46303</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57125,7 +57125,7 @@
         <v>46122</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>45618</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>44637</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>46261</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45874</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45947</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>45881</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46132</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>46132</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45882</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57953,7 +57953,7 @@
         <v>45453</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46133</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>46132</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45524</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>44967</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>44599</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>44593</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>44593</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46132</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58635,7 +58635,7 @@
         <v>45344</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>46132</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>46172</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>44946</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45425</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45194</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45939</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>44608</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59239,7 +59239,7 @@
         <v>45202</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45882</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45757</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>46135</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>46309</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45552</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>45890</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46266</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>46051</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>44960</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>44960</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46267</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60213,7 +60213,7 @@
         <v>46267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>45863</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>46309</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46265</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45876</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>45699</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45940</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45695</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45769</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60880,7 +60880,7 @@
         <v>46314</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         <v>46311</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>46311</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46312</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>44553</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46311</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45231</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>44575</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45097</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61542,7 +61542,7 @@
         <v>45852</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45838</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>44893</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45456</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45369</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>44904</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>46315</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>45966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>44659</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45901</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>46272</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>45379</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>44912</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>44614</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62672,7 +62672,7 @@
         <v>45880</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62745,7 +62745,7 @@
         <v>45293</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45443</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62896,7 +62896,7 @@
         <v>44967</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45942</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45867</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63115,7 +63115,7 @@
         <v>45691</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46274</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>45202</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>46141</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>46275</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>46276</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>46276</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63656,7 +63656,7 @@
         <v>46274</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         <v>46273</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>44512</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>46273</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>45390</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>44617</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>46146</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>44977</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45446</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>45426</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64411,7 +64411,7 @@
         <v>44993</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64484,7 +64484,7 @@
         <v>44733</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         <v>44994</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64630,7 +64630,7 @@
         <v>44665</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64708,7 +64708,7 @@
         <v>45068</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64781,7 +64781,7 @@
         <v>45363</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>44967</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>46155</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>46155</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65088,7 +65088,7 @@
         <v>46155</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65166,7 +65166,7 @@
         <v>44929</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>45730</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65317,7 +65317,7 @@
         <v>45614</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65395,7 +65395,7 @@
         <v>45930</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65468,7 +65468,7 @@
         <v>46160</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>46160</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>45042</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>44608</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65760,7 +65760,7 @@
         <v>44909</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45107</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>45089</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65984,7 +65984,7 @@
         <v>45113</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66057,7 +66057,7 @@
         <v>45113</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45757</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>44644</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>44508</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>44519</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45098</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45694</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>44820</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45065</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>44532</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45054</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>45047</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>44888</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>45127</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>45048</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67172,7 +67172,7 @@
         <v>44848</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67245,7 +67245,7 @@
         <v>45259</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67318,7 +67318,7 @@
         <v>44993</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>44531</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67464,7 +67464,7 @@
         <v>44532</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67537,7 +67537,7 @@
         <v>45757</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67610,7 +67610,7 @@
         <v>45078</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45202</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>44900</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>45580</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>44944</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         <v>45295</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68058,7 +68058,7 @@
         <v>45554</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>44816</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>45763</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45317</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45307</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>45104</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45119</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44501</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>45756</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68720,7 +68720,7 @@
         <v>44548</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>44550</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68871,7 +68871,7 @@
         <v>44980</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68944,7 +68944,7 @@
         <v>45254</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69017,7 +69017,7 @@
         <v>45611</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>45344</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69168,7 +69168,7 @@
         <v>45107</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69241,7 +69241,7 @@
         <v>45107</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69314,7 +69314,7 @@
         <v>45107</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69387,7 +69387,7 @@
         <v>45344</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69465,7 +69465,7 @@
         <v>44816</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>45133</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>45096</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>45098</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>44544</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>44519</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>45163</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69981,7 +69981,7 @@
         <v>45096</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70054,7 +70054,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70127,7 +70127,7 @@
         <v>45161</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70200,7 +70200,7 @@
         <v>45524</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70278,7 +70278,7 @@
         <v>44629</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70356,7 +70356,7 @@
         <v>45468</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70429,7 +70429,7 @@
         <v>45037</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70507,7 +70507,7 @@
         <v>45134</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>44533</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>44535</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>44637</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>45162</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>45145</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>45201</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>45358</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>44522</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>44616</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71252,7 +71252,7 @@
         <v>45177</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71325,7 +71325,7 @@
         <v>45159</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71398,7 +71398,7 @@
         <v>44678</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71476,7 +71476,7 @@
         <v>44610</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71554,7 +71554,7 @@
         <v>45615</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71627,7 +71627,7 @@
         <v>45638</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45188</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71778,7 +71778,7 @@
         <v>44832</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71851,7 +71851,7 @@
         <v>45338</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71924,7 +71924,7 @@
         <v>45721</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71997,7 +71997,7 @@
         <v>45148</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72070,7 +72070,7 @@
         <v>45148</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72143,7 +72143,7 @@
         <v>45148</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72216,7 +72216,7 @@
         <v>44588</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72289,7 +72289,7 @@
         <v>45323</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72367,7 +72367,7 @@
         <v>45194</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72445,7 +72445,7 @@
         <v>45601</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72523,7 +72523,7 @@
         <v>44594</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72596,7 +72596,7 @@
         <v>45371</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>45677</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72747,7 +72747,7 @@
         <v>44629</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72820,7 +72820,7 @@
         <v>45351</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72898,7 +72898,7 @@
         <v>45054</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72971,7 +72971,7 @@
         <v>45194</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>44819</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73122,7 +73122,7 @@
         <v>45055</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73195,7 +73195,7 @@
         <v>45182</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73268,7 +73268,7 @@
         <v>45182</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73341,7 +73341,7 @@
         <v>45093</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73419,7 +73419,7 @@
         <v>45407</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73492,7 +73492,7 @@
         <v>45188</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73565,7 +73565,7 @@
         <v>45231</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73638,7 +73638,7 @@
         <v>45677</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73711,7 +73711,7 @@
         <v>45695</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>45216</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73862,7 +73862,7 @@
         <v>45216</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73940,7 +73940,7 @@
         <v>45694</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74013,7 +74013,7 @@
         <v>44588</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74086,7 +74086,7 @@
         <v>45208</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74159,7 +74159,7 @@
         <v>45705</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74232,7 +74232,7 @@
         <v>45180</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74310,7 +74310,7 @@
         <v>44614</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
         <v>44679</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74461,7 +74461,7 @@
         <v>45149</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74539,7 +74539,7 @@
         <v>45181</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74612,7 +74612,7 @@
         <v>44679</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74690,7 +74690,7 @@
         <v>45182</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74763,7 +74763,7 @@
         <v>45694</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74836,7 +74836,7 @@
         <v>44699</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>45225</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45259</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>45236</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75138,7 +75138,7 @@
         <v>45299</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75211,7 +75211,7 @@
         <v>45267</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75289,7 +75289,7 @@
         <v>45236</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
         <v>44799</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75435,7 +75435,7 @@
         <v>45321</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75508,7 +75508,7 @@
         <v>45317</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75581,7 +75581,7 @@
         <v>45361</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75659,7 +75659,7 @@
         <v>45164</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75737,7 +75737,7 @@
         <v>45351</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75810,7 +75810,7 @@
         <v>44930</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75883,7 +75883,7 @@
         <v>45310</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75956,7 +75956,7 @@
         <v>45091</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>44788</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76102,7 +76102,7 @@
         <v>44817</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76175,7 +76175,7 @@
         <v>45216</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76248,7 +76248,7 @@
         <v>45599</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76321,7 +76321,7 @@
         <v>44984</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76399,7 +76399,7 @@
         <v>45391</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76472,7 +76472,7 @@
         <v>45520</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76545,7 +76545,7 @@
         <v>44581</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76623,7 +76623,7 @@
         <v>44568</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76701,7 +76701,7 @@
         <v>44908</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76774,7 +76774,7 @@
         <v>44949</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76847,7 +76847,7 @@
         <v>44946</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76920,7 +76920,7 @@
         <v>45033</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76993,7 +76993,7 @@
         <v>44531</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77066,7 +77066,7 @@
         <v>44960</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77139,7 +77139,7 @@
         <v>44602</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77217,7 +77217,7 @@
         <v>44606</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77295,7 +77295,7 @@
         <v>44645</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77373,7 +77373,7 @@
         <v>44609</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>44623</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77529,7 +77529,7 @@
         <v>45315</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77607,7 +77607,7 @@
         <v>45173</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77680,7 +77680,7 @@
         <v>44985</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77753,7 +77753,7 @@
         <v>45398</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77831,7 +77831,7 @@
         <v>46086</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>46093</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77977,7 +77977,7 @@
         <v>46089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78055,7 +78055,7 @@
         <v>46089</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78133,7 +78133,7 @@
         <v>46129</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>

--- a/Översikt UPPSALA.xlsx
+++ b/Översikt UPPSALA.xlsx
@@ -599,7 +599,7 @@
         <v>44284</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>45603</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>45688</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>44160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>46289</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
         <v>44659</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>44792</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45827</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45082</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45849</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
         <v>45882</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>45960</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
         <v>45994</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>46063</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2631,7 +2631,7 @@
         <v>45250</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>46154</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>45853</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>46121</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>44623</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         <v>46246</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46009</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3543,7 +3543,7 @@
         <v>45457</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44006</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>45223</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3922,7 +3922,7 @@
         <v>45706</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45728</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>46045</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>46009</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>45803</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>46303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>46155</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>45715</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>46303</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>46099</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>44971</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         <v>46268</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>46234</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>45874</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>45092</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5970,7 +5970,7 @@
         <v>46199</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>45442</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>45803</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44532</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45316</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6599,7 +6599,7 @@
         <v>45202</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>46009</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45442</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         <v>44575</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7092,7 +7092,7 @@
         <v>45196</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44726</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>45715</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>45803</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>46003</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7830,7 +7830,7 @@
         <v>46261</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45736</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>45996</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8192,7 +8192,7 @@
         <v>44500</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8314,7 +8314,7 @@
         <v>45936</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>46100</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>45358</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>45989</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>46171</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9049,7 +9049,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46181</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>46198</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45803</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45989</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44497</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44740</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45985</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         <v>44574</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>46202</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>46055</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45985</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>46234</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45688</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         <v>44791</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>44614</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45097</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>46155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44974</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44966</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
         <v>44720</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45961</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>45961</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45820</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>46009</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>45909</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12191,7 +12191,7 @@
         <v>46167</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45107</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>45721</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>45994</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>44610</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44719</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>44664</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>44886</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45905</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45905</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45371</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>46001</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -13534,7 +13534,7 @@
         <v>45985</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>46037</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -13763,7 +13763,7 @@
         <v>46003</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>45726</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>46155</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -14108,7 +14108,7 @@
         <v>44855</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>45167</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>44495</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44804</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46191</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45090</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45687</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14999,7 +14999,7 @@
         <v>46234</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>46234</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45803</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45273</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>45679</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>46093</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>46311</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45831</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45035</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44516</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45293</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>44984</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -16433,7 +16433,7 @@
         <v>44963</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45904</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45947</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>45960</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>45464</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -16972,7 +16972,7 @@
         <v>44967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45694</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45776</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45429</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45189</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -17514,7 +17514,7 @@
         <v>46267</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>44967</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45168</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45223</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45665</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44849</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>44630</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>44714</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>44651</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44543</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>44517</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>45121</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>44886</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45896</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>46160</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45916</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>44574</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>44847</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45938</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -19686,7 +19686,7 @@
         <v>44831</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45950</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46178</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>45385</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>46212</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>46009</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44894</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44909</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
         <v>45335</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>46141</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46141</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>45098</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46069</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -21084,7 +21084,7 @@
         <v>45736</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -21194,7 +21194,7 @@
         <v>46280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>46106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>46261</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44909</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44673</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46317</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>46275</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46274</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46147</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>44645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>46153</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44958</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>45645</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>44980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45442</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45757</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44917</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>45107</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -23248,7 +23248,7 @@
         <v>45316</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45583</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45181</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45107</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45638</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45190</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45173</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>44594</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45173</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44917</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45314</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>44630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44678</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44984</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>45994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>44583</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>44602</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>44602</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>44517</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44567</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>44544</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>44526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>44609</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>44569</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44662</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44572</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>44659</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44603</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>44494</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44700</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44839</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44784</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44612</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>44886</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>44598</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>44883</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44610</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>44865</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>44704</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44533</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>44764</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>44609</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -27006,7 +27006,7 @@
         <v>44512</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>44740</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>44722</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44705</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>44705</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>44692</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>44504</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44750</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>44643</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>44846</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -27824,7 +27824,7 @@
         <v>44676</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>44847</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>44705</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         <v>44799</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>44575</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>44575</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>44702</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>44551</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -28413,7 +28413,7 @@
         <v>44571</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -28486,7 +28486,7 @@
         <v>44634</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -28559,7 +28559,7 @@
         <v>44698</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>44599</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         <v>44865</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -28783,7 +28783,7 @@
         <v>44593</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>44543</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -28929,7 +28929,7 @@
         <v>44495</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -29002,7 +29002,7 @@
         <v>44522</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -29075,7 +29075,7 @@
         <v>44847</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         <v>44750</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44685</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>44733</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -29382,7 +29382,7 @@
         <v>44711</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -29460,7 +29460,7 @@
         <v>44743</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -29533,7 +29533,7 @@
         <v>44623</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44729</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>44593</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>44928</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -29840,7 +29840,7 @@
         <v>44593</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -29918,7 +29918,7 @@
         <v>44659</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>44791</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45839</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -30147,7 +30147,7 @@
         <v>44623</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44798</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>44819</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -30376,7 +30376,7 @@
         <v>44616</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -30449,7 +30449,7 @@
         <v>45050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -30522,7 +30522,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -30600,7 +30600,7 @@
         <v>44560</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>44600</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -30751,7 +30751,7 @@
         <v>45371</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -30829,7 +30829,7 @@
         <v>44623</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -30907,7 +30907,7 @@
         <v>44623</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -31058,7 +31058,7 @@
         <v>44965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -31131,7 +31131,7 @@
         <v>44965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45308</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45212</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -31350,7 +31350,7 @@
         <v>44886</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45181</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45208</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -31574,7 +31574,7 @@
         <v>44859</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -31647,7 +31647,7 @@
         <v>44832</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>44742</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>44883</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44866</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45903</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -32027,7 +32027,7 @@
         <v>45341</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -32105,7 +32105,7 @@
         <v>45905</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>45300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>46161</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -32324,7 +32324,7 @@
         <v>46137</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45912</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>45097</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -32553,7 +32553,7 @@
         <v>44969</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>46112</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -32699,7 +32699,7 @@
         <v>46112</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>45915</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>44944</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -32923,7 +32923,7 @@
         <v>46162</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45601</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>46162</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45154</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -33225,7 +33225,7 @@
         <v>44652</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -33298,7 +33298,7 @@
         <v>45678</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -33371,7 +33371,7 @@
         <v>44679</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45916</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45918</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -33590,7 +33590,7 @@
         <v>46163</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -33663,7 +33663,7 @@
         <v>46167</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -33741,7 +33741,7 @@
         <v>46167</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -33814,7 +33814,7 @@
         <v>45694</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45922</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>46167</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>44806</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>46167</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -34179,7 +34179,7 @@
         <v>45923</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45049</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -34330,7 +34330,7 @@
         <v>45923</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -34408,7 +34408,7 @@
         <v>45222</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45926</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44645</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -34637,7 +34637,7 @@
         <v>44497</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>45926</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45926</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45926</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45614</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>45926</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45926</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -35173,7 +35173,7 @@
         <v>45152</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45644</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>44964</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>45761</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -35465,7 +35465,7 @@
         <v>45929</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>45929</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>46171</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46171</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46171</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45932</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45931</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45932</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>44599</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45931</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45932</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45000</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45762</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>45937</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45352</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>45938</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>44944</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>45940</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -36819,7 +36819,7 @@
         <v>45259</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>45942</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -36970,7 +36970,7 @@
         <v>45266</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45096</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>44872</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -37189,7 +37189,7 @@
         <v>45743</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45758</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>44809</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>44810</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45898</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -37627,7 +37627,7 @@
         <v>44551</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -37705,7 +37705,7 @@
         <v>45946</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -37778,7 +37778,7 @@
         <v>45513</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>45049</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>45336</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>45946</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45946</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45950</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45949</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46178</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45950</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -38518,7 +38518,7 @@
         <v>45954</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -38591,7 +38591,7 @@
         <v>45954</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45954</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -38737,7 +38737,7 @@
         <v>45958</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45169</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46185</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45244</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45435</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45958</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45958</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45958</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45958</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45763</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>45958</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>45958</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -39663,7 +39663,7 @@
         <v>46184</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -39741,7 +39741,7 @@
         <v>45548</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45959</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46188</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46188</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>46188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44532</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -40184,7 +40184,7 @@
         <v>45231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45961</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>45190</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -40476,7 +40476,7 @@
         <v>46188</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>46191</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>44977</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -40778,7 +40778,7 @@
         <v>46191</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -40856,7 +40856,7 @@
         <v>45336</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -40929,7 +40929,7 @@
         <v>46191</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>46191</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>46191</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -41158,7 +41158,7 @@
         <v>45971</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -41231,7 +41231,7 @@
         <v>46195</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -41304,7 +41304,7 @@
         <v>45971</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45972</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -41455,7 +41455,7 @@
         <v>45110</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -41528,7 +41528,7 @@
         <v>45194</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -41606,7 +41606,7 @@
         <v>45474</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -41679,7 +41679,7 @@
         <v>45975</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>46199</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45300</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -41903,7 +41903,7 @@
         <v>45589</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -41976,7 +41976,7 @@
         <v>44609</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -42054,7 +42054,7 @@
         <v>45975</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>45581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>46198</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
         <v>44503</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -42356,7 +42356,7 @@
         <v>44624</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>46198</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>46202</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -42580,7 +42580,7 @@
         <v>45729</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -42653,7 +42653,7 @@
         <v>45729</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -42726,7 +42726,7 @@
         <v>45982</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>46202</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45259</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45259</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45981</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -43091,7 +43091,7 @@
         <v>45327</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45014</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44593</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>45981</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45981</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>45685</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45958</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45460</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>45345</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45981</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44914</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45061</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44912</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45983</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>46206</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>44967</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45075</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46206</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -44435,7 +44435,7 @@
         <v>45988</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -44513,7 +44513,7 @@
         <v>46206</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>46206</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45699</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -44737,7 +44737,7 @@
         <v>45733</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -44810,7 +44810,7 @@
         <v>45426</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>45958</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45992</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>45478</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45992</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>45154</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>45729</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45175</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -45404,7 +45404,7 @@
         <v>45644</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -45477,7 +45477,7 @@
         <v>45995</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>45006</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>46217</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45995</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>45307</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -45842,7 +45842,7 @@
         <v>45254</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -45915,7 +45915,7 @@
         <v>46218</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -45993,7 +45993,7 @@
         <v>45327</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -46066,7 +46066,7 @@
         <v>45300</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -46139,7 +46139,7 @@
         <v>44883</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -46212,7 +46212,7 @@
         <v>46205</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -46285,7 +46285,7 @@
         <v>45987</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -46358,7 +46358,7 @@
         <v>44849</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45107</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -46504,7 +46504,7 @@
         <v>45520</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45574</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>45779</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -46728,7 +46728,7 @@
         <v>46224</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>45254</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>45981</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46202</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>44569</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>46237</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>45329</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>45177</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -47332,7 +47332,7 @@
         <v>45558</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>45562</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -47478,7 +47478,7 @@
         <v>45368</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -47556,7 +47556,7 @@
         <v>44569</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -47634,7 +47634,7 @@
         <v>46237</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45684</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -47785,7 +47785,7 @@
         <v>46013</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -47858,7 +47858,7 @@
         <v>45254</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -47931,7 +47931,7 @@
         <v>46014</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -48004,7 +48004,7 @@
         <v>45968</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45371</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45091</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>45583</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -48311,7 +48311,7 @@
         <v>45584</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>46281</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>46234</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -48535,7 +48535,7 @@
         <v>46030</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -48613,7 +48613,7 @@
         <v>46030</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -48686,7 +48686,7 @@
         <v>46029</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>46240</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46031</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -48905,7 +48905,7 @@
         <v>46283</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45525</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>45195</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -49124,7 +49124,7 @@
         <v>45636</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -49197,7 +49197,7 @@
         <v>45490</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45439</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -49348,7 +49348,7 @@
         <v>45799</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -49426,7 +49426,7 @@
         <v>45733</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -49499,7 +49499,7 @@
         <v>45799</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -49577,7 +49577,7 @@
         <v>46290</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -49650,7 +49650,7 @@
         <v>45799</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -49728,7 +49728,7 @@
         <v>45086</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -49806,7 +49806,7 @@
         <v>45744</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -49879,7 +49879,7 @@
         <v>46051</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>45341</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45608</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>46051</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -50171,7 +50171,7 @@
         <v>46055</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -50244,7 +50244,7 @@
         <v>46055</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -50322,7 +50322,7 @@
         <v>45511</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>45341</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>45215</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -50546,7 +50546,7 @@
         <v>46057</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -50619,7 +50619,7 @@
         <v>45809</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -50697,7 +50697,7 @@
         <v>45453</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -50775,7 +50775,7 @@
         <v>46062</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>46062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -50926,7 +50926,7 @@
         <v>46062</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -51004,7 +51004,7 @@
         <v>45812</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -51077,7 +51077,7 @@
         <v>46062</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -51155,7 +51155,7 @@
         <v>46064</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -51228,7 +51228,7 @@
         <v>45721</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -51301,7 +51301,7 @@
         <v>46065</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -51374,7 +51374,7 @@
         <v>46065</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -51447,7 +51447,7 @@
         <v>45817</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -51520,7 +51520,7 @@
         <v>45817</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -51598,7 +51598,7 @@
         <v>45341</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>46251</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>46076</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -51827,7 +51827,7 @@
         <v>45821</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -51900,7 +51900,7 @@
         <v>45821</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46251</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -52051,7 +52051,7 @@
         <v>46251</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -52129,7 +52129,7 @@
         <v>46080</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -52202,7 +52202,7 @@
         <v>45831</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -52275,7 +52275,7 @@
         <v>45831</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -52353,7 +52353,7 @@
         <v>45832</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -52431,7 +52431,7 @@
         <v>46085</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45831</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45832</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>45831</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>46065</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46090</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -52879,7 +52879,7 @@
         <v>46091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>46091</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -53025,7 +53025,7 @@
         <v>46090</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -53098,7 +53098,7 @@
         <v>44935</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
         <v>46300</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -53244,7 +53244,7 @@
         <v>46091</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -53317,7 +53317,7 @@
         <v>46091</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -53390,7 +53390,7 @@
         <v>46091</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -53463,7 +53463,7 @@
         <v>46091</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -53536,7 +53536,7 @@
         <v>46093</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -53609,7 +53609,7 @@
         <v>45821</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -53682,7 +53682,7 @@
         <v>46094</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -53755,7 +53755,7 @@
         <v>45840</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
         <v>46094</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -53901,7 +53901,7 @@
         <v>46094</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -53974,7 +53974,7 @@
         <v>46094</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -54047,7 +54047,7 @@
         <v>46251</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -54125,7 +54125,7 @@
         <v>46097</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -54198,7 +54198,7 @@
         <v>46094</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46094</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
         <v>46254</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>46098</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -54490,7 +54490,7 @@
         <v>44504</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -54563,7 +54563,7 @@
         <v>45679</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -54636,7 +54636,7 @@
         <v>44602</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -54709,7 +54709,7 @@
         <v>45763</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -54782,7 +54782,7 @@
         <v>46300</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -54855,7 +54855,7 @@
         <v>46300</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -54928,7 +54928,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -55001,7 +55001,7 @@
         <v>46302</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -55074,7 +55074,7 @@
         <v>46259</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -55147,7 +55147,7 @@
         <v>45644</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -55220,7 +55220,7 @@
         <v>45426</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -55293,7 +55293,7 @@
         <v>45852</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -55371,7 +55371,7 @@
         <v>45852</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -55444,7 +55444,7 @@
         <v>45852</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -55522,7 +55522,7 @@
         <v>46107</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -55595,7 +55595,7 @@
         <v>46107</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -55668,7 +55668,7 @@
         <v>46107</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -55766,7 +55766,7 @@
         <v>45856</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -55844,7 +55844,7 @@
         <v>46111</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -55917,7 +55917,7 @@
         <v>46111</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -55990,7 +55990,7 @@
         <v>44977</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -56063,7 +56063,7 @@
         <v>46111</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -56136,7 +56136,7 @@
         <v>46303</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -56214,7 +56214,7 @@
         <v>46272</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -56287,7 +56287,7 @@
         <v>46160</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -56365,7 +56365,7 @@
         <v>46140</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -56443,7 +56443,7 @@
         <v>45349</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -56516,7 +56516,7 @@
         <v>46114</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -56594,7 +56594,7 @@
         <v>46119</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -56667,7 +56667,7 @@
         <v>46260</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -56745,7 +56745,7 @@
         <v>46119</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -56818,7 +56818,7 @@
         <v>45831</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -56891,7 +56891,7 @@
         <v>44624</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -56969,7 +56969,7 @@
         <v>46303</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -57047,7 +57047,7 @@
         <v>46303</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -57125,7 +57125,7 @@
         <v>46122</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -57198,7 +57198,7 @@
         <v>45618</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -57271,7 +57271,7 @@
         <v>44637</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -57349,7 +57349,7 @@
         <v>46261</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -57427,7 +57427,7 @@
         <v>45874</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -57500,7 +57500,7 @@
         <v>45947</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -57578,7 +57578,7 @@
         <v>45943</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>45881</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>46132</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -57807,7 +57807,7 @@
         <v>46132</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -57880,7 +57880,7 @@
         <v>45882</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -57953,7 +57953,7 @@
         <v>45453</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -58026,7 +58026,7 @@
         <v>46133</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -58099,7 +58099,7 @@
         <v>46132</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -58177,7 +58177,7 @@
         <v>45524</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -58255,7 +58255,7 @@
         <v>44967</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -58328,7 +58328,7 @@
         <v>44599</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>44593</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>44593</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -58557,7 +58557,7 @@
         <v>46132</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -58635,7 +58635,7 @@
         <v>45344</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -58713,7 +58713,7 @@
         <v>46132</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -58791,7 +58791,7 @@
         <v>46172</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>44946</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45425</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45194</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45939</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>44608</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -59239,7 +59239,7 @@
         <v>45202</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>45882</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45757</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>46135</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>46309</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45552</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>46309</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>45890</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46266</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>46051</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>44960</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -60062,7 +60062,7 @@
         <v>44960</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -60135,7 +60135,7 @@
         <v>46267</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -60213,7 +60213,7 @@
         <v>46267</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -60286,7 +60286,7 @@
         <v>45863</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -60359,7 +60359,7 @@
         <v>46309</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -60432,7 +60432,7 @@
         <v>46265</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -60510,7 +60510,7 @@
         <v>45876</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -60583,7 +60583,7 @@
         <v>45699</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>45940</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>45695</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -60807,7 +60807,7 @@
         <v>45769</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -60880,7 +60880,7 @@
         <v>46314</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -60958,7 +60958,7 @@
         <v>46311</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -61031,7 +61031,7 @@
         <v>46311</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -61104,7 +61104,7 @@
         <v>46312</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -61177,7 +61177,7 @@
         <v>44553</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -61250,7 +61250,7 @@
         <v>46311</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -61323,7 +61323,7 @@
         <v>45231</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -61396,7 +61396,7 @@
         <v>44575</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -61469,7 +61469,7 @@
         <v>45097</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -61542,7 +61542,7 @@
         <v>45852</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -61620,7 +61620,7 @@
         <v>46314</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -61698,7 +61698,7 @@
         <v>45838</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -61771,7 +61771,7 @@
         <v>44893</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -61844,7 +61844,7 @@
         <v>45456</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -61917,7 +61917,7 @@
         <v>45369</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -61990,7 +61990,7 @@
         <v>44904</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -62068,7 +62068,7 @@
         <v>46315</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -62141,7 +62141,7 @@
         <v>45966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -62219,7 +62219,7 @@
         <v>44659</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -62297,7 +62297,7 @@
         <v>45901</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>46272</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>45379</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>44912</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>44614</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -62672,7 +62672,7 @@
         <v>45880</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -62745,7 +62745,7 @@
         <v>45293</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45443</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -62896,7 +62896,7 @@
         <v>44967</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -62969,7 +62969,7 @@
         <v>45942</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -63042,7 +63042,7 @@
         <v>45867</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -63115,7 +63115,7 @@
         <v>45691</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46274</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>45202</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -63344,7 +63344,7 @@
         <v>46141</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -63422,7 +63422,7 @@
         <v>46275</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -63500,7 +63500,7 @@
         <v>46276</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -63578,7 +63578,7 @@
         <v>46276</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -63656,7 +63656,7 @@
         <v>46274</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -63734,7 +63734,7 @@
         <v>46273</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>44512</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>46273</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>45390</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>44617</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>46146</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>44977</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -64260,7 +64260,7 @@
         <v>45446</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>45426</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -64411,7 +64411,7 @@
         <v>44993</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -64484,7 +64484,7 @@
         <v>44733</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -64557,7 +64557,7 @@
         <v>44994</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -64630,7 +64630,7 @@
         <v>44665</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -64708,7 +64708,7 @@
         <v>45068</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -64781,7 +64781,7 @@
         <v>45363</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -64859,7 +64859,7 @@
         <v>44967</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -64932,7 +64932,7 @@
         <v>46155</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -65010,7 +65010,7 @@
         <v>46155</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -65088,7 +65088,7 @@
         <v>46155</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -65166,7 +65166,7 @@
         <v>44929</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>45730</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -65317,7 +65317,7 @@
         <v>45614</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -65395,7 +65395,7 @@
         <v>45930</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -65468,7 +65468,7 @@
         <v>46160</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -65541,7 +65541,7 @@
         <v>46160</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>45042</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>44608</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -65760,7 +65760,7 @@
         <v>44909</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -65838,7 +65838,7 @@
         <v>45107</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -65911,7 +65911,7 @@
         <v>45089</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -65984,7 +65984,7 @@
         <v>45113</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -66057,7 +66057,7 @@
         <v>45113</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -66130,7 +66130,7 @@
         <v>45757</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -66203,7 +66203,7 @@
         <v>44644</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -66281,7 +66281,7 @@
         <v>44508</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -66359,7 +66359,7 @@
         <v>44519</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -66432,7 +66432,7 @@
         <v>45098</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -66505,7 +66505,7 @@
         <v>45694</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -66578,7 +66578,7 @@
         <v>44820</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -66656,7 +66656,7 @@
         <v>45065</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -66729,7 +66729,7 @@
         <v>44532</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -66802,7 +66802,7 @@
         <v>45054</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -66875,7 +66875,7 @@
         <v>45047</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -66948,7 +66948,7 @@
         <v>44888</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -67026,7 +67026,7 @@
         <v>45127</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -67099,7 +67099,7 @@
         <v>45048</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -67172,7 +67172,7 @@
         <v>44848</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -67245,7 +67245,7 @@
         <v>45259</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -67318,7 +67318,7 @@
         <v>44993</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -67391,7 +67391,7 @@
         <v>44531</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -67464,7 +67464,7 @@
         <v>44532</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -67537,7 +67537,7 @@
         <v>45757</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -67610,7 +67610,7 @@
         <v>45078</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -67688,7 +67688,7 @@
         <v>45202</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -67761,7 +67761,7 @@
         <v>44900</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -67834,7 +67834,7 @@
         <v>45580</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -67907,7 +67907,7 @@
         <v>44944</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -67980,7 +67980,7 @@
         <v>45295</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -68058,7 +68058,7 @@
         <v>45554</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -68131,7 +68131,7 @@
         <v>44816</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -68204,7 +68204,7 @@
         <v>45763</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         <v>45317</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -68350,7 +68350,7 @@
         <v>45307</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -68423,7 +68423,7 @@
         <v>45104</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -68496,7 +68496,7 @@
         <v>45119</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -68569,7 +68569,7 @@
         <v>44501</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -68647,7 +68647,7 @@
         <v>45756</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -68720,7 +68720,7 @@
         <v>44548</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -68793,7 +68793,7 @@
         <v>44550</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -68871,7 +68871,7 @@
         <v>44980</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -68944,7 +68944,7 @@
         <v>45254</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -69017,7 +69017,7 @@
         <v>45611</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -69090,7 +69090,7 @@
         <v>45344</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -69168,7 +69168,7 @@
         <v>45107</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -69241,7 +69241,7 @@
         <v>45107</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -69314,7 +69314,7 @@
         <v>45107</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -69387,7 +69387,7 @@
         <v>45344</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -69465,7 +69465,7 @@
         <v>44816</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -69543,7 +69543,7 @@
         <v>45133</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -69616,7 +69616,7 @@
         <v>45096</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -69689,7 +69689,7 @@
         <v>45098</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -69762,7 +69762,7 @@
         <v>44544</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -69835,7 +69835,7 @@
         <v>44519</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>45163</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -69981,7 +69981,7 @@
         <v>45096</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -70054,7 +70054,7 @@
         <v>44603</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -70127,7 +70127,7 @@
         <v>45161</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -70200,7 +70200,7 @@
         <v>45524</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -70278,7 +70278,7 @@
         <v>44629</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -70356,7 +70356,7 @@
         <v>45468</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -70429,7 +70429,7 @@
         <v>45037</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -70507,7 +70507,7 @@
         <v>45134</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -70585,7 +70585,7 @@
         <v>44533</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -70658,7 +70658,7 @@
         <v>44535</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -70731,7 +70731,7 @@
         <v>44637</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -70804,7 +70804,7 @@
         <v>45162</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -70882,7 +70882,7 @@
         <v>45145</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -70955,7 +70955,7 @@
         <v>45201</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -71028,7 +71028,7 @@
         <v>45358</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -71101,7 +71101,7 @@
         <v>44522</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -71174,7 +71174,7 @@
         <v>44616</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -71252,7 +71252,7 @@
         <v>45177</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -71325,7 +71325,7 @@
         <v>45159</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -71398,7 +71398,7 @@
         <v>44678</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -71476,7 +71476,7 @@
         <v>44610</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -71554,7 +71554,7 @@
         <v>45615</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -71627,7 +71627,7 @@
         <v>45638</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -71700,7 +71700,7 @@
         <v>45188</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -71778,7 +71778,7 @@
         <v>44832</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -71851,7 +71851,7 @@
         <v>45338</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -71924,7 +71924,7 @@
         <v>45721</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -71997,7 +71997,7 @@
         <v>45148</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -72070,7 +72070,7 @@
         <v>45148</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -72143,7 +72143,7 @@
         <v>45148</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -72216,7 +72216,7 @@
         <v>44588</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -72289,7 +72289,7 @@
         <v>45323</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -72367,7 +72367,7 @@
         <v>45194</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -72445,7 +72445,7 @@
         <v>45601</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -72523,7 +72523,7 @@
         <v>44594</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -72596,7 +72596,7 @@
         <v>45371</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -72674,7 +72674,7 @@
         <v>45677</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -72747,7 +72747,7 @@
         <v>44629</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -72820,7 +72820,7 @@
         <v>45351</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -72898,7 +72898,7 @@
         <v>45054</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -72971,7 +72971,7 @@
         <v>45194</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -73049,7 +73049,7 @@
         <v>44819</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -73122,7 +73122,7 @@
         <v>45055</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -73195,7 +73195,7 @@
         <v>45182</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -73268,7 +73268,7 @@
         <v>45182</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -73341,7 +73341,7 @@
         <v>45093</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -73419,7 +73419,7 @@
         <v>45407</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -73492,7 +73492,7 @@
         <v>45188</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -73565,7 +73565,7 @@
         <v>45231</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -73638,7 +73638,7 @@
         <v>45677</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -73711,7 +73711,7 @@
         <v>45695</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -73789,7 +73789,7 @@
         <v>45216</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -73862,7 +73862,7 @@
         <v>45216</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -73940,7 +73940,7 @@
         <v>45694</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -74013,7 +74013,7 @@
         <v>44588</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -74086,7 +74086,7 @@
         <v>45208</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -74159,7 +74159,7 @@
         <v>45705</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -74232,7 +74232,7 @@
         <v>45180</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -74310,7 +74310,7 @@
         <v>44614</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -74383,7 +74383,7 @@
         <v>44679</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -74461,7 +74461,7 @@
         <v>45149</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -74539,7 +74539,7 @@
         <v>45181</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -74612,7 +74612,7 @@
         <v>44679</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -74690,7 +74690,7 @@
         <v>45182</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -74763,7 +74763,7 @@
         <v>45694</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -74836,7 +74836,7 @@
         <v>44699</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -74914,7 +74914,7 @@
         <v>45225</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -74987,7 +74987,7 @@
         <v>45259</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -75065,7 +75065,7 @@
         <v>45236</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -75138,7 +75138,7 @@
         <v>45299</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -75211,7 +75211,7 @@
         <v>45267</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -75289,7 +75289,7 @@
         <v>45236</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -75362,7 +75362,7 @@
         <v>44799</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -75435,7 +75435,7 @@
         <v>45321</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -75508,7 +75508,7 @@
         <v>45317</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -75581,7 +75581,7 @@
         <v>45361</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -75659,7 +75659,7 @@
         <v>45164</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -75737,7 +75737,7 @@
         <v>45351</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -75810,7 +75810,7 @@
         <v>44930</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -75883,7 +75883,7 @@
         <v>45310</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -75956,7 +75956,7 @@
         <v>45091</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -76029,7 +76029,7 @@
         <v>44788</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -76102,7 +76102,7 @@
         <v>44817</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -76175,7 +76175,7 @@
         <v>45216</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -76248,7 +76248,7 @@
         <v>45599</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -76321,7 +76321,7 @@
         <v>44984</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -76399,7 +76399,7 @@
         <v>45391</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -76472,7 +76472,7 @@
         <v>45520</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -76545,7 +76545,7 @@
         <v>44581</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -76623,7 +76623,7 @@
         <v>44568</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -76701,7 +76701,7 @@
         <v>44908</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -76774,7 +76774,7 @@
         <v>44949</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -76847,7 +76847,7 @@
         <v>44946</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -76920,7 +76920,7 @@
         <v>45033</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -76993,7 +76993,7 @@
         <v>44531</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
@@ -77066,7 +77066,7 @@
         <v>44960</v>
       </c>
       <c r="E908" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -77139,7 +77139,7 @@
         <v>44602</v>
       </c>
       <c r="E909" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -77217,7 +77217,7 @@
         <v>44606</v>
       </c>
       <c r="E910" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
@@ -77295,7 +77295,7 @@
         <v>44645</v>
       </c>
       <c r="E911" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F911" t="inlineStr">
         <is>
@@ -77373,7 +77373,7 @@
         <v>44609</v>
       </c>
       <c r="E912" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F912" t="inlineStr">
         <is>
@@ -77451,7 +77451,7 @@
         <v>44623</v>
       </c>
       <c r="E913" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F913" t="inlineStr">
         <is>
@@ -77529,7 +77529,7 @@
         <v>45315</v>
       </c>
       <c r="E914" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F914" t="inlineStr">
         <is>
@@ -77607,7 +77607,7 @@
         <v>45173</v>
       </c>
       <c r="E915" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F915" t="inlineStr">
         <is>
@@ -77680,7 +77680,7 @@
         <v>44985</v>
       </c>
       <c r="E916" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F916" t="inlineStr">
         <is>
@@ -77753,7 +77753,7 @@
         <v>45398</v>
       </c>
       <c r="E917" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F917" t="inlineStr">
         <is>
@@ -77831,7 +77831,7 @@
         <v>46086</v>
       </c>
       <c r="E918" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F918" t="inlineStr">
         <is>
@@ -77904,7 +77904,7 @@
         <v>46093</v>
       </c>
       <c r="E919" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F919" t="inlineStr">
         <is>
@@ -77977,7 +77977,7 @@
         <v>46089</v>
       </c>
       <c r="E920" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F920" t="inlineStr">
         <is>
@@ -78055,7 +78055,7 @@
         <v>46089</v>
       </c>
       <c r="E921" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F921" t="inlineStr">
         <is>
@@ -78133,7 +78133,7 @@
         <v>46129</v>
       </c>
       <c r="E922" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F922" t="inlineStr">
         <is>
